--- a/tame_output/ON/bt/strategyON_20240929.xlsx
+++ b/tame_output/ON/bt/strategyON_20240929.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.5%</t>
+          <t>122.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.4%</t>
+          <t>421.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-576.7%</t>
+          <t>-577.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-52.1%</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-301.9%</t>
+          <t>-300.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>118.9%</t>
+          <t>117.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389351</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814668</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.79829678423181</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077642</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833461</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.82103066007763</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147912</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735284</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496557</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108859</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013429</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498971</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.6700487028001</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660853</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791152</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620438</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285651</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399472</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600701003</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687016</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.8014649832554</v>
+        <v>-4.776402619668749</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.990802131461955</v>
+        <v>2.000827076896615</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9471568828219231</v>
+        <v>0.9472559297650114</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.480038678771017</v>
+        <v>4.48009810693687</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790806</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.852875405576108</v>
+        <v>-4.827813041989457</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.96802365965961</v>
+        <v>1.978048605094271</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9471568828219231</v>
+        <v>0.9472559297650114</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.477824375896955</v>
+        <v>4.477883804062809</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.704757949437334</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.93229485678386</v>
+        <v>-4.907232493197209</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.936159007250799</v>
+        <v>1.946183952685459</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9471568828219231</v>
+        <v>0.9472559297650114</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.477727503971245</v>
+        <v>4.477786932137098</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298402</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.027757854701077</v>
+        <v>-5.002695491114427</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.897967701641955</v>
+        <v>1.907992647076615</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9471568828219231</v>
+        <v>0.9472559297650114</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.477721397529288</v>
+        <v>4.477780825695141</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960218004</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.963381943850362</v>
+        <v>-4.938319580263712</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.921814462544852</v>
+        <v>1.931839407979512</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.011532793672638</v>
+        <v>1.011631840615727</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.514443340602328</v>
+        <v>4.51450276876818</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.73608941335354</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.018751105982556</v>
+        <v>-4.993688742395905</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.905400615439701</v>
+        <v>1.915425560874361</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.011532793672638</v>
+        <v>1.011631840615727</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.520177158350054</v>
+        <v>4.520236586515907</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113283</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.036969572980165</v>
+        <v>-5.011907209393514</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.897651591983589</v>
+        <v>1.90767653741825</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.986426356416796</v>
+        <v>0.9865254033598844</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.504651659339482</v>
+        <v>4.504711087505334</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113692</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.948762738832587</v>
+        <v>-4.923700375245936</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.952808718492939</v>
+        <v>1.9628336639276</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.986426356416796</v>
+        <v>0.9865254033598844</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.5245260521898</v>
+        <v>4.524585480355653</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016443</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.842727743627277</v>
+        <v>-4.817665380040626</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.978923417099791</v>
+        <v>1.988948362534451</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.986426356416796</v>
+        <v>0.9865254033598844</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.508226752714528</v>
+        <v>4.508286180880381</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307674</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.659516080494182</v>
+        <v>-4.634453716907531</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.054639031817075</v>
+        <v>2.064663977251735</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.986426356416796</v>
+        <v>0.9865254033598844</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.510657702178573</v>
+        <v>4.510717130344426</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863555</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.587794633480331</v>
+        <v>-4.56273226989368</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.066272016701992</v>
+        <v>2.076296962136652</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.058147803430647</v>
+        <v>1.058246850373735</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.536634976466261</v>
+        <v>4.536694404632113</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394116</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.565421607872625</v>
+        <v>-4.540359244285974</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.022136972866246</v>
+        <v>2.032161918300907</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.069403554543548</v>
+        <v>1.069502601486636</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.490304173055174</v>
+        <v>4.490363601221026</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456733</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.59843790378337</v>
+        <v>-4.573375540196719</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.194128659387304</v>
+        <v>2.204153604821964</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9999661778767968</v>
+        <v>1.000065224819885</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.633839951940478</v>
+        <v>4.633899380106331</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883682</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.586910268133761</v>
+        <v>-4.56184790454711</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.190660939475396</v>
+        <v>2.200685884910056</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.058966836078159</v>
+        <v>1.059065883021247</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.661161572689545</v>
+        <v>4.661221000855397</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236302</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.68425176947613</v>
+        <v>-4.659189405889479</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.155392451460237</v>
+        <v>2.165417396894898</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.014546653912671</v>
+        <v>1.014645700855759</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.63817757591204</v>
+        <v>4.638237004077893</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427688</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.770107798816096</v>
+        <v>-4.745045435229446</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.122301121917089</v>
+        <v>2.132326067351749</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9721705846865358</v>
+        <v>0.972269631629624</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.614003016569197</v>
+        <v>4.61406244473505</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610385</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.778944596232216</v>
+        <v>-4.753882232645565</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.101185604771143</v>
+        <v>2.111210550205803</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9647284120451851</v>
+        <v>0.9648274589882733</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.591956914804888</v>
+        <v>4.592016342970742</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667459</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.870327158797674</v>
+        <v>-4.845264795211023</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.074797090790009</v>
+        <v>2.084822036224669</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9281635273258404</v>
+        <v>0.9282625742689286</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.580182495018331</v>
+        <v>4.580241923184184</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889196</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.858620440810668</v>
+        <v>-4.833558077224017</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.18160803580908</v>
+        <v>2.19163298124374</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.9398702453128468</v>
+        <v>0.939969292255935</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.689334783634803</v>
+        <v>4.689394211800656</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.929532514552946</v>
+        <v>-4.904470150966295</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.156275545043573</v>
+        <v>2.166300490478234</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.9398702453128468</v>
+        <v>0.939969292255935</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.692367122366208</v>
+        <v>4.692426550532061</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452575</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.939848612719298</v>
+        <v>-4.914786249132647</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.365053939055091</v>
+        <v>2.375078884489751</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.9398702453128468</v>
+        <v>0.939969292255935</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.905271955644266</v>
+        <v>4.905331383810119</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762292</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.939754644701925</v>
+        <v>-4.914692281115275</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.364270193174129</v>
+        <v>2.374295138608789</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.904672539364746</v>
+        <v>4.9047319675306</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988022</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.08812087235807</v>
+        <v>-5.063058508771419</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.299155688056025</v>
+        <v>2.309180633490686</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.8989045253091</v>
+        <v>4.898963953474953</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740926</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.087172449240032</v>
+        <v>-5.062110085653381</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.29953505730324</v>
+        <v>2.309560002737901</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.8989045253091</v>
+        <v>4.898963953474953</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663629</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.187442267199053</v>
+        <v>-5.162379903612402</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.272154738100724</v>
+        <v>2.282179683535384</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.911632133290192</v>
+        <v>4.911691561456045</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424773</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.181450020410241</v>
+        <v>-5.156387656823591</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.276497635240637</v>
+        <v>2.286522580675297</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.91357813171458</v>
+        <v>4.913637559880433</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149221</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.092892059279474</v>
+        <v>-5.067829695692823</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.305574955710712</v>
+        <v>2.315599901145373</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.907232267732349</v>
+        <v>4.907291695898202</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.73530072138309</v>
+        <v>3.735300721383093</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.0751329817764</v>
+        <v>-5.050070618189749</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.311987264150938</v>
+        <v>2.322012209585598</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.906540945171344</v>
+        <v>4.906600373337198</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720999</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.975502830727332</v>
+        <v>-4.950440467140681</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.364621510479152</v>
+        <v>2.374646455913812</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.039870257709232</v>
+        <v>1.03996930465232</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.979101221709372</v>
+        <v>4.979160649875225</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.77535709745527</v>
+        <v>3.775357097455274</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.024902339416343</v>
+        <v>-4.999839975829692</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.534015972502274</v>
+        <v>2.544040917936934</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.050129091140977</v>
+        <v>1.050228138084065</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.174410787267146</v>
+        <v>5.174470215432998</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963131</v>
+        <v>3.749078058963135</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.818217865773967</v>
+        <v>-4.793155502187316</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.603878435062086</v>
+        <v>2.613903380496747</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.256813564783353</v>
+        <v>1.256912611726441</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.285610144555433</v>
+        <v>5.285669572721286</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162541</v>
+        <v>3.740284389162546</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.852374760771493</v>
+        <v>-4.827312397184842</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.59221719071718</v>
+        <v>2.602242136151841</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.17322979524254</v>
+        <v>1.173328842185628</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.237461396485051</v>
+        <v>5.237520824650903</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.782482115652386</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.759785281710037</v>
+        <v>-4.734722918123386</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.982750096331431</v>
+        <v>2.992775041766091</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.17322979524254</v>
+        <v>1.173328842185628</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.590958510474717</v>
+        <v>5.591017938640571</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108676</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.819673909533587</v>
+        <v>-4.794611545946936</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.963357756769113</v>
+        <v>2.973382702203774</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.159107880555076</v>
+        <v>1.159206927498164</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.587048473229342</v>
+        <v>5.587107901395195</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.835202441103568</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.767457599737245</v>
+        <v>-4.742395236150594</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.034074222011178</v>
+        <v>3.044099167445838</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.159107880555076</v>
+        <v>1.159206927498164</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.63687841455287</v>
+        <v>5.636937842718723</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047744</v>
+        <v>3.821827147047749</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.735560082651999</v>
+        <v>-4.710497719065349</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.055647199055287</v>
+        <v>3.065672144489947</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.191005397640321</v>
+        <v>1.19110444458341</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.664830895014028</v>
+        <v>5.664890323179881</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650752</v>
+        <v>3.825268416650759</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.75031540685214</v>
+        <v>-4.725253043265489</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.045382653414427</v>
+        <v>3.055407598849088</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.191005397640321</v>
+        <v>1.19110444458341</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.660468479053224</v>
+        <v>5.660527907219078</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135747</v>
+        <v>3.845044666135753</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.700850783482228</v>
+        <v>-4.675788419895578</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.056093006178672</v>
+        <v>3.066117951613332</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.240470021010233</v>
+        <v>1.240569067953321</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.681071756491452</v>
+        <v>5.681131184657304</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.82593179047922</v>
+        <v>3.825931790479227</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.537742791328613</v>
+        <v>-4.512680427741962</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.117743870755053</v>
+        <v>3.127768816189713</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.403578013163848</v>
+        <v>1.403677060106936</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.775344219498555</v>
+        <v>5.775403647664408</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844245</v>
+        <v>3.847096478844248</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.404935165831446</v>
+        <v>-4.379872802244796</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.179913957645048</v>
+        <v>3.189938903079708</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.403578013163848</v>
+        <v>1.403677060106936</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.784391256189684</v>
+        <v>5.784450684355536</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790948</v>
+        <v>3.832425987790952</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.467643082306004</v>
+        <v>-4.442580718719354</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.155688256041346</v>
+        <v>3.165713201476006</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.340870096689291</v>
+        <v>1.340969143632379</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.747623971291071</v>
+        <v>5.747683399456923</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578995</v>
+        <v>3.861579399578998</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.419634958462312</v>
+        <v>-4.394572594875661</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.137800922369175</v>
+        <v>3.147825867803836</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.340870096689291</v>
+        <v>1.340969143632379</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.710533388081423</v>
+        <v>5.710592816247275</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629883</v>
+        <v>3.872253907629887</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.340809301278721</v>
+        <v>-4.315746937692071</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.173263438800562</v>
+        <v>3.183288384235222</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.419695753872881</v>
+        <v>1.419794800815969</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.761761035949528</v>
+        <v>5.76182046411538</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.627846383746895</v>
+        <v>3.918909441617055</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.151511023096893</v>
+        <v>-4.156927014508167</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.24388184268033</v>
+        <v>3.241715446115821</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.419695753872881</v>
+        <v>1.419794800815969</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.756660128556565</v>
+        <v>5.756719556722417</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240929.xlsx
+++ b/tame_output/ON/bt/strategyON_20240929.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.4%</t>
+          <t>122.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.7%</t>
+          <t>422.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-577.3%</t>
+          <t>-586.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-52.1%</t>
+          <t>-55.5%</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-300.4%</t>
+          <t>-301.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>117.9%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.297643323067692</v>
+        <v>-4.392680730016242</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.169199530295509</v>
+        <v>1.131184567516089</v>
       </c>
       <c r="F1930" t="n">
         <v>0.2320049794710608</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.177470239703194</v>
+        <v>-4.272507646651743</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.21841460808161</v>
+        <v>1.180399645302191</v>
       </c>
       <c r="F1931" t="n">
         <v>0.3521780628355597</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.042216878373217</v>
+        <v>-4.137254285321766</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.282604055175041</v>
+        <v>1.244589092395621</v>
       </c>
       <c r="F1932" t="n">
         <v>0.4874314241655369</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.102091705730909</v>
+        <v>-4.197129112679458</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24469161563339</v>
+        <v>1.20667665285397</v>
       </c>
       <c r="F1933" t="n">
         <v>0.4275565968078447</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.982271474820072</v>
+        <v>-4.077308881768621</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.307908877231933</v>
+        <v>1.269893914452513</v>
       </c>
       <c r="F1934" t="n">
         <v>0.4275565968078447</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.984741181281878</v>
+        <v>-4.079778588230427</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.214565193969652</v>
+        <v>1.176550231190233</v>
       </c>
       <c r="F1935" t="n">
         <v>0.4250868903460386</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.053111367605887</v>
+        <v>-4.148148774554437</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10647898092535</v>
+        <v>1.06846401814593</v>
       </c>
       <c r="F1936" t="n">
         <v>0.4343625893822535</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.164983647232038</v>
+        <v>-4.260021054180588</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.052166777706781</v>
+        <v>1.014151814927361</v>
       </c>
       <c r="F1937" t="n">
         <v>0.4343625893822535</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.14900898174577</v>
+        <v>-4.24404638869432</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.025131168825316</v>
+        <v>0.9871162060458956</v>
       </c>
       <c r="F1938" t="n">
         <v>0.4343625893822535</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.973534721953301</v>
+        <v>-4.068572128901851</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.099888104734091</v>
+        <v>1.061873141954671</v>
       </c>
       <c r="F1939" t="n">
         <v>0.4343625893822535</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.965610347368387</v>
+        <v>-4.060647754316936</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.078799883329264</v>
+        <v>1.040784920549844</v>
       </c>
       <c r="F1940" t="n">
         <v>0.4343625893822535</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.959332144798538</v>
+        <v>-4.054369551747087</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.009849477758653</v>
+        <v>0.9718345149792333</v>
       </c>
       <c r="F1941" t="n">
         <v>0.4406407919521026</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.899479525594815</v>
+        <v>-3.994516932543364</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.043962911872275</v>
+        <v>1.005947949092855</v>
       </c>
       <c r="F1942" t="n">
         <v>0.4406407919521026</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.813236062568437</v>
+        <v>-3.908273469516987</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.073406567656686</v>
+        <v>1.035391604877266</v>
       </c>
       <c r="F1943" t="n">
         <v>0.4406407919521026</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.858542881967417</v>
+        <v>-3.953580288915966</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.04705961534162</v>
+        <v>1.0090446525622</v>
       </c>
       <c r="F1944" t="n">
         <v>0.3998306289428718</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.887575986669719</v>
+        <v>-3.982613393618268</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.0359982464938</v>
+        <v>0.9979832837143809</v>
       </c>
       <c r="F1945" t="n">
         <v>0.3998306289428718</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.79476550521886</v>
+        <v>-3.889802912167409</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.00239513096551</v>
+        <v>0.9643801681860902</v>
       </c>
       <c r="F1946" t="n">
         <v>0.4926411103937312</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.839154974548287</v>
+        <v>-3.934192381496836</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9865128191583397</v>
+        <v>0.9484978563789199</v>
       </c>
       <c r="F1947" t="n">
         <v>0.4482516410643035</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.81865128066279</v>
+        <v>-3.913688687611339</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9897900052242616</v>
+        <v>0.9517750424448419</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4687553349498008</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.902323377375122</v>
+        <v>-3.997360784323671</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.961812462369996</v>
+        <v>0.9237974995905764</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4687553349498008</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.930103775276475</v>
+        <v>-4.025141182225024</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9621975049779938</v>
+        <v>0.9241825421985741</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4409749370484478</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.048484448006613</v>
+        <v>-4.143521854955162</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7532009558865917</v>
+        <v>0.715185993107172</v>
       </c>
       <c r="F1951" t="n">
         <v>0.3737570848974716</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.157098526449944</v>
+        <v>-4.252135933398494</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.829904985228465</v>
+        <v>0.7918900224490453</v>
       </c>
       <c r="F1952" t="n">
         <v>0.3737570848974716</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.121689488201802</v>
+        <v>-4.216726895150351</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.858581626630045</v>
+        <v>0.8205666638506255</v>
       </c>
       <c r="F1953" t="n">
         <v>0.3737570848974716</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.130150656857262</v>
+        <v>-4.225188063805811</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8526166005102294</v>
+        <v>0.8146016377308098</v>
       </c>
       <c r="F1954" t="n">
         <v>0.3652959162420105</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.953034326822096</v>
+        <v>-4.048071733770645</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9201921613695982</v>
+        <v>0.8821771985901785</v>
       </c>
       <c r="F1955" t="n">
         <v>0.3652959162420105</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.998126571655642</v>
+        <v>-4.093163978604191</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9028386551980931</v>
+        <v>0.8648236924186734</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3033998730726207</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.818751150416874</v>
+        <v>-3.913788557365423</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9683757990000146</v>
+        <v>0.9303608362205948</v>
       </c>
       <c r="F1957" t="n">
         <v>0.4601766312433394</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.86376536393748</v>
+        <v>-3.95880277088603</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9311775689233617</v>
+        <v>0.8931626061439422</v>
       </c>
       <c r="F1958" t="n">
         <v>0.4298277359287348</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.951776550496178</v>
+        <v>-4.046813957444726</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9016646566388287</v>
+        <v>0.8636496938594092</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3643512280695618</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.052974331933351</v>
+        <v>-4.148011738881899</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8603894659604607</v>
+        <v>0.8223745031810414</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2959424145242426</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.046463365319038</v>
+        <v>-4.141500772267587</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8605938141605025</v>
+        <v>0.8225788513810832</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2959424145242426</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.027425237611741</v>
+        <v>-4.122462644560289</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8647337844516665</v>
+        <v>0.8267188216722472</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2377588031930481</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.079941039886561</v>
+        <v>-4.17497844683511</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9630218651759286</v>
+        <v>0.9250069023965093</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2377588031930481</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.083349351321141</v>
+        <v>-4.178386758269689</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9624918695882303</v>
+        <v>0.924476906808811</v>
       </c>
       <c r="F1964" t="n">
         <v>0.2702753722024255</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.063993215427294</v>
+        <v>-4.159030622375842</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9762428543426951</v>
+        <v>0.9382278915632758</v>
       </c>
       <c r="F1965" t="n">
         <v>0.2702753722024255</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.137322744165386</v>
+        <v>-4.232360151113935</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8448612641246576</v>
+        <v>0.8068463013452383</v>
       </c>
       <c r="F1966" t="n">
         <v>0.2706700346220474</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.221143965440085</v>
+        <v>-4.316181372388633</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8141263971462591</v>
+        <v>0.7761114343668398</v>
       </c>
       <c r="F1967" t="n">
         <v>0.2706700346220474</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.2149912593873</v>
+        <v>-4.310028666335849</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8172498279590312</v>
+        <v>0.7792348651796119</v>
       </c>
       <c r="F1968" t="n">
         <v>0.2768227406748317</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.231800557537802</v>
+        <v>-4.326837964486351</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8096065854389407</v>
+        <v>0.7715916226595214</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2600134425243301</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.16950255876168</v>
+        <v>-4.264539965710228</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9008613387462105</v>
+        <v>0.8628463759667913</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3053077067987721</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.967712361096522</v>
+        <v>-4.06274976804507</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7838694195264009</v>
+        <v>0.7458544567469816</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5033258989679266</v>
@@ -46907,10 +46907,10 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.018599073782717</v>
+        <v>-4.113636480731265</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8338049667740981</v>
+        <v>0.7957900039946788</v>
       </c>
       <c r="F1972" t="n">
         <v>0.452439186281732</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.93198833113291</v>
+        <v>-4.027025738081458</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8830769999500647</v>
+        <v>0.8450620371706452</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5310649174868902</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.992197629138194</v>
+        <v>-4.087235036086743</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8575292615726227</v>
+        <v>0.8195142987932029</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4708556194816057</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.943010980453843</v>
+        <v>-4.038048387402392</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8756955390862917</v>
+        <v>0.837680576306872</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4708556194816057</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.898637848815274</v>
+        <v>-3.993675255763823</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8933076591771554</v>
+        <v>0.8552926963977356</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5152287511201743</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.863906527496773</v>
+        <v>-3.958943934445322</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9015939818431462</v>
+        <v>0.8635790190637267</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5152287511201743</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.816250796935718</v>
+        <v>-3.911288203884267</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.927038031095373</v>
+        <v>0.8890230683159535</v>
       </c>
       <c r="F1978" t="n">
         <v>0.56288448168123</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.715732638436963</v>
+        <v>-3.810770045385512</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9721376678695997</v>
+        <v>0.9341227050901801</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6634026401799845</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.69982730900461</v>
+        <v>-3.794864715953159</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9652544721184131</v>
+        <v>0.9272395093389934</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5842899794707457</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.654988907396212</v>
+        <v>-3.750026314344761</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9872875353724009</v>
+        <v>0.9492725725929811</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5888334124156152</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.67448736363822</v>
+        <v>-3.76952477058677</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9836490925066754</v>
+        <v>0.9456341297272559</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5407487711357108</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.63028452655232</v>
+        <v>-3.725321933500869</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.007209829868873</v>
+        <v>0.9691948670894532</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5849516082216113</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.637844192389367</v>
+        <v>-3.732881599337916</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.002595964003302</v>
+        <v>0.964581001223882</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6397550122314306</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.479552774850095</v>
+        <v>-3.574590181798644</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.11716029620205</v>
+        <v>1.07914533342263</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6397550122314306</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.271910771215619</v>
+        <v>-3.366948178164168</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.198657802250094</v>
+        <v>1.160642839470674</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8473970158659068</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.220878678493091</v>
+        <v>-3.31591608544164</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.214018867577375</v>
+        <v>1.176003904797955</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8984291085884347</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.155654497365885</v>
+        <v>-3.250691904314434</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.257295944120962</v>
+        <v>1.219280981341543</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9636532897156403</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.118227477294751</v>
+        <v>-3.2132648842433</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.268227724448696</v>
+        <v>1.230212761669276</v>
       </c>
       <c r="F1989" t="n">
         <v>0.968904827744822</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992655</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.116869492321205</v>
+        <v>-3.211906899269755</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.270027710769355</v>
+        <v>1.232012747989935</v>
       </c>
       <c r="F1990" t="n">
         <v>1.043242953282641</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.088456229221322</v>
+        <v>-3.183493636169871</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.441950787030519</v>
+        <v>1.403935824251099</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9842673905362118</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.013673968196309</v>
+        <v>-3.108711375144858</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.591976600658341</v>
+        <v>1.553961637878921</v>
       </c>
       <c r="F1992" t="n">
         <v>1.059049651561224</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.987589883932501</v>
+        <v>-3.08262729088105</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.594118210377723</v>
+        <v>1.556103247598304</v>
       </c>
       <c r="F1993" t="n">
         <v>1.059049651561224</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.899711970823381</v>
+        <v>-2.99474937777193</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.627462571205151</v>
+        <v>1.589447608425731</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174975293984576</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.890819509430098</v>
+        <v>-2.985856916378647</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.648573961489256</v>
+        <v>1.610558998709836</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174975293984576</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.059295626399976</v>
+        <v>-3.154333033348525</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.573038562105888</v>
+        <v>1.535023599326469</v>
       </c>
       <c r="F1996" t="n">
         <v>1.147027458267995</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.613039433770536</v>
+        <v>-2.708076840719085</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.732810736345526</v>
+        <v>1.694795773566107</v>
       </c>
       <c r="F1997" t="n">
         <v>1.052308788598362</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.590318330087383</v>
+        <v>-2.685355737035932</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.732563200315692</v>
+        <v>1.694548237536272</v>
       </c>
       <c r="F1998" t="n">
         <v>1.052308788598362</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.719520143381426</v>
+        <v>-2.814557550329975</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.839788600849244</v>
+        <v>1.801773638069824</v>
       </c>
       <c r="F1999" t="n">
         <v>0.92310697530432</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.745394541855451</v>
+        <v>-2.840431948804</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.86651666395328</v>
+        <v>1.82850170117386</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9680185840160611</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.738339851640278</v>
+        <v>-2.833377258588827</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.866013896028895</v>
+        <v>1.827998933249475</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9750732742312349</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.71138862731379</v>
+        <v>-2.806426034262339</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.886800539404231</v>
+        <v>1.848785576624812</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9899536202589541</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.732932855144577</v>
+        <v>-2.827970262093126</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.062285980416876</v>
+        <v>2.024271017637457</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9899536202589541</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.755340972949449</v>
+        <v>-2.850378379897998</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.045439428197921</v>
+        <v>2.007424465418501</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9899536202589541</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.783565208527049</v>
+        <v>-2.878602615475598</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.036203733516518</v>
+        <v>1.998188770737098</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007930372710263</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.793006134415579</v>
+        <v>-2.888043541364128</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.088681080882953</v>
+        <v>2.050666118103534</v>
       </c>
       <c r="F2006" t="n">
         <v>1.130357490253654</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.881882765584053</v>
+        <v>-2.976920172532602</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.056021522960864</v>
+        <v>2.018006560181445</v>
       </c>
       <c r="F2007" t="n">
         <v>1.04148085908518</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.958212743184959</v>
+        <v>-3.053250150133508</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.023601344814277</v>
+        <v>1.985586382034858</v>
       </c>
       <c r="F2008" t="n">
         <v>1.04148085908518</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.113169528585088</v>
+        <v>-3.208206935533637</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.956438860257088</v>
+        <v>1.918423897477668</v>
       </c>
       <c r="F2009" t="n">
         <v>0.886524073685051</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343068</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.274737954112343</v>
+        <v>-3.369775361060892</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.890245500256338</v>
+        <v>1.852230537476918</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7597411498871717</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389351</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.383038615982463</v>
+        <v>-3.478076022931012</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.859998642374209</v>
+        <v>1.821983679594789</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7597411498871717</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.400842587703207</v>
+        <v>-3.495879994651756</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.844882250468851</v>
+        <v>1.806867287689432</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6892065269819705</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.42874337481268</v>
+        <v>-3.523780781761229</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.832245976752064</v>
+        <v>1.794231013972644</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6546096028390357</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.551269477515574</v>
+        <v>-3.646306884464123</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.779999979648105</v>
+        <v>1.741985016868686</v>
       </c>
       <c r="F2014" t="n">
         <v>0.5320835001361418</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.781783973701162</v>
+        <v>-3.876821380649711</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.754500140764374</v>
+        <v>1.716485177984954</v>
       </c>
       <c r="F2015" t="n">
         <v>0.3015690039505531</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814668</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.130529058925606</v>
+        <v>-4.225566465874155</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.755313825676443</v>
+        <v>1.717298862897024</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1928210500316553</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.284515476701746</v>
+        <v>-4.379552883650295</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.762699527711627</v>
+        <v>1.724684564932207</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1928210500316553</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.489114911564755</v>
+        <v>-4.584152318513304</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.666910955886544</v>
+        <v>1.628895993107125</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1928210500316553</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609755</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.741590065572479</v>
+        <v>-4.836627472521029</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.577791383338868</v>
+        <v>1.539776420559449</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1928210500316553</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.034485822051892</v>
+        <v>-5.129523229000441</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.461843615266047</v>
+        <v>1.423828652486628</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1928210500316553</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.2211499501867</v>
+        <v>-5.316187357135249</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.391299706239446</v>
+        <v>1.353284743460026</v>
       </c>
       <c r="F2021" t="n">
         <v>0.1660820792070954</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.367170637100662</v>
+        <v>-5.462208044049211</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.32796928421005</v>
+        <v>1.28995432143063</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1569989874132384</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.458884646210247</v>
+        <v>-5.553922053158797</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.45348773726526</v>
+        <v>1.41547277448584</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1569989874132384</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.490536305270217</v>
+        <v>-5.585573712218766</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.435673711605086</v>
+        <v>1.397658748825667</v>
       </c>
       <c r="F2024" t="n">
         <v>0.1518305301687982</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.559602359843153</v>
+        <v>-5.654639766791703</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.418276707344403</v>
+        <v>1.380261744564983</v>
       </c>
       <c r="F2025" t="n">
         <v>0.08945965267518818</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.661578482091561</v>
+        <v>-5.75661588904011</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.386411896900942</v>
+        <v>1.348396934121523</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.01251646957321939</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.79829678423181</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.551572198614339</v>
+        <v>-5.646609605562888</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.422567297536006</v>
+        <v>1.384552334756587</v>
       </c>
       <c r="F2027" t="n">
         <v>0.01068810234405582</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.408512622873413</v>
+        <v>-5.503550029821962</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.484041138554351</v>
+        <v>1.446026175774931</v>
       </c>
       <c r="F2028" t="n">
         <v>0.01870152893403509</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.107065897401576</v>
+        <v>-5.202103304350125</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.611880711625622</v>
+        <v>1.573865748846202</v>
       </c>
       <c r="F2029" t="n">
         <v>0.3201482544058724</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679626</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.13165614163676</v>
+        <v>-5.226693548585309</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.603015791684259</v>
+        <v>1.565000828904839</v>
       </c>
       <c r="F2030" t="n">
         <v>0.3201482544058724</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.080617765630239</v>
+        <v>-5.175655172578788</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.624274046466623</v>
+        <v>1.586259083687203</v>
       </c>
       <c r="F2031" t="n">
         <v>0.3201482544058724</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.051769088806779</v>
+        <v>-5.146806495755328</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.654851616070152</v>
+        <v>1.616836653290733</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3489969312293326</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700479</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.955134176788139</v>
+        <v>-5.050171583736688</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.509689577001543</v>
+        <v>1.471674614222123</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4456318432479726</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077642</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.886096165839671</v>
+        <v>-4.98113357278822</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.540806825454894</v>
+        <v>1.502791862675474</v>
       </c>
       <c r="F2034" t="n">
         <v>0.5146698541964406</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833461</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.721599831648709</v>
+        <v>-4.816637238597258</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.591032178207361</v>
+        <v>1.553017215427942</v>
       </c>
       <c r="F2035" t="n">
         <v>0.6791661883874025</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.82103066007763</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.644501230106837</v>
+        <v>-4.739538637055386</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.62105932926054</v>
+        <v>1.58304436648112</v>
       </c>
       <c r="F2036" t="n">
         <v>0.6791661883874025</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147912</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.654886424996726</v>
+        <v>-4.749923831945275</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.626774030429657</v>
+        <v>1.588759067650237</v>
       </c>
       <c r="F2037" t="n">
         <v>0.6687809934975132</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735284</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.673474583718951</v>
+        <v>-4.7685119906675</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.690175772717192</v>
+        <v>1.652160809937772</v>
       </c>
       <c r="F2038" t="n">
         <v>0.6501928347752879</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496557</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.673773130414987</v>
+        <v>-4.768810537363536</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.686925364857076</v>
+        <v>1.648910402077656</v>
       </c>
       <c r="F2039" t="n">
         <v>0.649894288079252</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108859</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.572949996724559</v>
+        <v>-4.667987403673108</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.731785513272639</v>
+        <v>1.693770550493219</v>
       </c>
       <c r="F2040" t="n">
         <v>0.6623585035636058</v>
@@ -48488,16 +48488,16 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.382168635972151</v>
+        <v>-4.477206042920701</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.808227311052145</v>
+        <v>1.770212348272725</v>
       </c>
       <c r="F2041" t="n">
         <v>0.8531398643160132</v>
@@ -48511,16 +48511,16 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.27520527812273</v>
+        <v>-4.370242685071279</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.83084949992951</v>
+        <v>1.792834537150091</v>
       </c>
       <c r="F2042" t="n">
         <v>0.9116044722758146</v>
@@ -48534,16 +48534,16 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912987</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.219874690220967</v>
+        <v>-4.314912097169517</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.887948671702274</v>
+        <v>1.849933708922854</v>
       </c>
       <c r="F2043" t="n">
         <v>0.9669350601775768</v>
@@ -48557,16 +48557,16 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539896</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.207820563308005</v>
+        <v>-4.302857970256554</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.886456890368897</v>
+        <v>1.848441927589477</v>
       </c>
       <c r="F2044" t="n">
         <v>0.9789891870905396</v>
@@ -48580,16 +48580,16 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.248975682876226</v>
+        <v>-4.344013089824775</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.871875472725744</v>
+        <v>1.833860509946324</v>
       </c>
       <c r="F2045" t="n">
         <v>0.9378340675223187</v>
@@ -48603,16 +48603,16 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.180927120184696</v>
+        <v>-4.275964527133245</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.911945923680238</v>
+        <v>1.873930960900819</v>
       </c>
       <c r="F2046" t="n">
         <v>1.005882630213848</v>
@@ -48626,16 +48626,16 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013429</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.412527513354196</v>
+        <v>-4.507564920302745</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.839508436586032</v>
+        <v>1.801493473806613</v>
       </c>
       <c r="F2047" t="n">
         <v>1.005882630213848</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498971</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.462579058883415</v>
+        <v>-4.557616465831964</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.803094054441227</v>
+        <v>1.765079091661807</v>
       </c>
       <c r="F2048" t="n">
         <v>1.005882630213848</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.6700487028001</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.63768589145986</v>
+        <v>-4.732723298408409</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.693303235004116</v>
+        <v>1.655288272224696</v>
       </c>
       <c r="F2049" t="n">
         <v>1.005882630213848</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660853</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.441585738029337</v>
+        <v>-4.536623144977886</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.778765915373265</v>
+        <v>1.740750952593845</v>
       </c>
       <c r="F2050" t="n">
         <v>1.201982783644371</v>
@@ -48718,16 +48718,16 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73057047339509</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.288560345916053</v>
+        <v>-4.383597752864602</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.939147071791483</v>
+        <v>1.901132109012063</v>
       </c>
       <c r="F2051" t="n">
         <v>1.355008175757655</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791152</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.316867659789323</v>
+        <v>-4.411905066737872</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.115290371150468</v>
+        <v>2.077275408371047</v>
       </c>
       <c r="F2052" t="n">
         <v>1.355008175757655</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620438</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.483460884902845</v>
+        <v>-4.578498291851394</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.018056032459141</v>
+        <v>1.980041069679721</v>
       </c>
       <c r="F2053" t="n">
         <v>1.188414950644133</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285651</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.460425091541279</v>
+        <v>-4.555462498489828</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.030946752465485</v>
+        <v>1.992931789686065</v>
       </c>
       <c r="F2054" t="n">
         <v>1.188414950644133</v>
@@ -48810,16 +48810,16 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399472</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.431179111085583</v>
+        <v>-4.526216518034132</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.040263199771259</v>
+        <v>2.002248236991839</v>
       </c>
       <c r="F2055" t="n">
         <v>1.188414950644133</v>
@@ -48833,16 +48833,16 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256374</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.538104658963434</v>
+        <v>-4.633142065911983</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.994786219777754</v>
+        <v>1.956771256998334</v>
       </c>
       <c r="F2056" t="n">
         <v>1.081489402766282</v>
@@ -48856,16 +48856,16 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701003</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.683123217470682</v>
+        <v>-4.778160624419232</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.938207598518089</v>
+        <v>1.900192635738669</v>
       </c>
       <c r="F2057" t="n">
         <v>0.936470844259033</v>
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687016</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.776402619668749</v>
+        <v>-4.896502390203949</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.000827076896615</v>
+        <v>1.952787168682535</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9472559297650114</v>
+        <v>0.9471568828219231</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.48009810693687</v>
+        <v>4.480038678771017</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790806</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.827813041989457</v>
+        <v>-4.947912812524657</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.978048605094271</v>
+        <v>1.930008696880191</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9472559297650114</v>
+        <v>0.9471568828219231</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.477883804062809</v>
+        <v>4.477824375896955</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437334</v>
+        <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.907232493197209</v>
+        <v>-5.027332263732409</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.946183952685459</v>
+        <v>1.898144044471379</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9472559297650114</v>
+        <v>0.9471568828219231</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.477786932137098</v>
+        <v>4.477727503971245</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298402</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.002695491114427</v>
+        <v>-5.122795261649626</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.907992647076615</v>
+        <v>1.859952738862535</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9472559297650114</v>
+        <v>0.9471568828219231</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.477780825695141</v>
+        <v>4.477721397529288</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218004</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.938319580263712</v>
+        <v>-5.058419350798911</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.931839407979512</v>
+        <v>1.883799499765432</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.011631840615727</v>
+        <v>1.011532793672638</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.51450276876818</v>
+        <v>4.514443340602328</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73608941335354</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.993688742395905</v>
+        <v>-5.113788512931105</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.915425560874361</v>
+        <v>1.867385652660281</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.011631840615727</v>
+        <v>1.011532793672638</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.520236586515907</v>
+        <v>4.520177158350054</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113283</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.011907209393514</v>
+        <v>-5.132006979928714</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.90767653741825</v>
+        <v>1.85963662920417</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9865254033598844</v>
+        <v>0.986426356416796</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.504711087505334</v>
+        <v>4.504651659339482</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113692</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.923700375245936</v>
+        <v>-5.043800145781136</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.9628336639276</v>
+        <v>1.91479375571352</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9865254033598844</v>
+        <v>0.986426356416796</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.524585480355653</v>
+        <v>4.5245260521898</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016443</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.817665380040626</v>
+        <v>-4.937765150575826</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.988948362534451</v>
+        <v>1.940908454320371</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9865254033598844</v>
+        <v>0.986426356416796</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.508286180880381</v>
+        <v>4.508226752714528</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307674</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.634453716907531</v>
+        <v>-4.754553487442731</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.064663977251735</v>
+        <v>2.016624069037655</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9865254033598844</v>
+        <v>0.986426356416796</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.510717130344426</v>
+        <v>4.510657702178573</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863555</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.56273226989368</v>
+        <v>-4.68283204042888</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.076296962136652</v>
+        <v>2.028257053922572</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.058246850373735</v>
+        <v>1.058147803430647</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.536694404632113</v>
+        <v>4.536634976466261</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394116</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.540359244285974</v>
+        <v>-4.660459014821174</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.032161918300907</v>
+        <v>1.984122010086827</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.069502601486636</v>
+        <v>1.069403554543548</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.490363601221026</v>
+        <v>4.490304173055174</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456733</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.573375540196719</v>
+        <v>-4.693475310731919</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.204153604821964</v>
+        <v>2.156113696607884</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.000065224819885</v>
+        <v>0.9999661778767968</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.633899380106331</v>
+        <v>4.633839951940478</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883682</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.56184790454711</v>
+        <v>-4.68194767508231</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.200685884910056</v>
+        <v>2.152645976695977</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.059065883021247</v>
+        <v>1.058966836078159</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.661221000855397</v>
+        <v>4.661161572689545</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236302</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.659189405889479</v>
+        <v>-4.779289176424679</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.165417396894898</v>
+        <v>2.117377488680818</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.014645700855759</v>
+        <v>1.014546653912671</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.638237004077893</v>
+        <v>4.63817757591204</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427688</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.745045435229446</v>
+        <v>-4.865145205764645</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.132326067351749</v>
+        <v>2.084286159137669</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.972269631629624</v>
+        <v>0.9721705846865358</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.61406244473505</v>
+        <v>4.614003016569197</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610385</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.753882232645565</v>
+        <v>-4.873982003180765</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.111210550205803</v>
+        <v>2.063170641991723</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9648274589882733</v>
+        <v>0.9647284120451851</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.592016342970742</v>
+        <v>4.591956914804888</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667459</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.845264795211023</v>
+        <v>-4.965364565746223</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.084822036224669</v>
+        <v>2.036782128010589</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9282625742689286</v>
+        <v>0.9281635273258404</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.580241923184184</v>
+        <v>4.580182495018331</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889196</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.833558077224017</v>
+        <v>-4.953657847759217</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.19163298124374</v>
+        <v>2.14359307302966</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.939969292255935</v>
+        <v>0.9398702453128468</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.689394211800656</v>
+        <v>4.689334783634803</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409572</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.904470150966295</v>
+        <v>-5.024569921501495</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.166300490478234</v>
+        <v>2.118260582264154</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.939969292255935</v>
+        <v>0.9398702453128468</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.692426550532061</v>
+        <v>4.692367122366208</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452575</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.914786249132647</v>
+        <v>-5.034886019667847</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.375078884489751</v>
+        <v>2.327038976275671</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.939969292255935</v>
+        <v>0.9398702453128468</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.905331383810119</v>
+        <v>4.905271955644266</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762292</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.914692281115275</v>
+        <v>-5.034792051650474</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.374295138608789</v>
+        <v>2.32625523039471</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.9047319675306</v>
+        <v>4.904672539364746</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988022</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.063058508771419</v>
+        <v>-5.183158279306619</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.309180633490686</v>
+        <v>2.261140725276606</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.898963953474953</v>
+        <v>4.8989045253091</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740926</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.062110085653381</v>
+        <v>-5.182209856188581</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.309560002737901</v>
+        <v>2.261520094523821</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.898963953474953</v>
+        <v>4.8989045253091</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663629</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.162379903612402</v>
+        <v>-5.282479674147602</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.282179683535384</v>
+        <v>2.234139775321304</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.911691561456045</v>
+        <v>4.911632133290192</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424773</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.156387656823591</v>
+        <v>-5.276487427358791</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.286522580675297</v>
+        <v>2.238482672461217</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.913637559880433</v>
+        <v>4.91357813171458</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149221</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.067829695692823</v>
+        <v>-5.187929466228023</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.315599901145373</v>
+        <v>2.267559992931293</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.907291695898202</v>
+        <v>4.907232267732349</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383093</v>
+        <v>3.73530072138309</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.050070618189749</v>
+        <v>-5.170170388724949</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.322012209585598</v>
+        <v>2.273972301371518</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.906600373337198</v>
+        <v>4.906540945171344</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720999</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.950440467140681</v>
+        <v>-5.070540237675881</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.374646455913812</v>
+        <v>2.326606547699732</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.03996930465232</v>
+        <v>1.039870257709232</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.979160649875225</v>
+        <v>4.979101221709372</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455274</v>
+        <v>3.77535709745527</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.999839975829692</v>
+        <v>-5.119939746364892</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.544040917936934</v>
+        <v>2.496001009722854</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.050228138084065</v>
+        <v>1.050129091140977</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.174470215432998</v>
+        <v>5.174410787267146</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963135</v>
+        <v>3.749078058963131</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.793155502187316</v>
+        <v>-4.913255272722516</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.613903380496747</v>
+        <v>2.565863472282667</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.256912611726441</v>
+        <v>1.256813564783353</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.285669572721286</v>
+        <v>5.285610144555433</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162546</v>
+        <v>3.740284389162541</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.827312397184842</v>
+        <v>-4.947412167720042</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.602242136151841</v>
+        <v>2.554202227937761</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.173328842185628</v>
+        <v>1.17322979524254</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.237520824650903</v>
+        <v>5.237461396485051</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652386</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.734722918123386</v>
+        <v>-4.854822688658586</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.992775041766091</v>
+        <v>2.944735133552011</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.173328842185628</v>
+        <v>1.17322979524254</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.591017938640571</v>
+        <v>5.590958510474717</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108676</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.794611545946936</v>
+        <v>-4.914711316482136</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.973382702203774</v>
+        <v>2.925342793989694</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.159206927498164</v>
+        <v>1.159107880555076</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.587107901395195</v>
+        <v>5.587048473229342</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103568</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.742395236150594</v>
+        <v>-4.862495006685794</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.044099167445838</v>
+        <v>2.996059259231759</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.159206927498164</v>
+        <v>1.159107880555076</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.636937842718723</v>
+        <v>5.63687841455287</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047749</v>
+        <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.710497719065349</v>
+        <v>-4.830597489600549</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.065672144489947</v>
+        <v>3.017632236275867</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.19110444458341</v>
+        <v>1.191005397640321</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.664890323179881</v>
+        <v>5.664830895014028</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650759</v>
+        <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.725253043265489</v>
+        <v>-4.845352813800689</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.055407598849088</v>
+        <v>3.007367690635008</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.19110444458341</v>
+        <v>1.191005397640321</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.660527907219078</v>
+        <v>5.660468479053224</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135753</v>
+        <v>3.845044666135747</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.675788419895578</v>
+        <v>-4.795888190430778</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.066117951613332</v>
+        <v>3.018078043399253</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.240569067953321</v>
+        <v>1.240470021010233</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.681131184657304</v>
+        <v>5.681071756491452</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479227</v>
+        <v>3.82593179047922</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.512680427741962</v>
+        <v>-4.632780198277162</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.127768816189713</v>
+        <v>3.079728907975634</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.403677060106936</v>
+        <v>1.403578013163848</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.775403647664408</v>
+        <v>5.775344219498555</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844248</v>
+        <v>3.847096478844245</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.379872802244796</v>
+        <v>-4.499972572779996</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.189938903079708</v>
+        <v>3.141898994865628</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.403677060106936</v>
+        <v>1.403578013163848</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.784450684355536</v>
+        <v>5.784391256189684</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790952</v>
+        <v>3.832425987790948</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.442580718719354</v>
+        <v>-4.562680489254554</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.165713201476006</v>
+        <v>3.117673293261927</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.340969143632379</v>
+        <v>1.340870096689291</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.747683399456923</v>
+        <v>5.747623971291071</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578998</v>
+        <v>3.861579399578995</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.394572594875661</v>
+        <v>-4.514672365410861</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.147825867803836</v>
+        <v>3.099785959589756</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.340969143632379</v>
+        <v>1.340870096689291</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.710592816247275</v>
+        <v>5.710533388081423</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629887</v>
+        <v>3.872253907629883</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.315746937692071</v>
+        <v>-4.43584670822727</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.183288384235222</v>
+        <v>3.135248476021142</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.419794800815969</v>
+        <v>1.419695753872881</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.76182046411538</v>
+        <v>5.761761035949528</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.918909441617055</v>
+        <v>3.826998233414551</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.156927014508167</v>
+        <v>-4.243911906973397</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.241715446115821</v>
+        <v>3.206921489129729</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.419794800815969</v>
+        <v>1.419695753872881</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.756719556722417</v>
+        <v>5.756660128556565</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240929.xlsx
+++ b/tame_output/ON/bt/strategyON_20240929.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.5%</t>
+          <t>421.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-586.0%</t>
+          <t>-576.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-55.5%</t>
+          <t>-51.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-301.9%</t>
+          <t>-300.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>118.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.392680730016242</v>
+        <v>-4.297643323067692</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.131184567516089</v>
+        <v>1.169199530295509</v>
       </c>
       <c r="F1930" t="n">
         <v>0.2320049794710608</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.272507646651743</v>
+        <v>-4.177470239703194</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.180399645302191</v>
+        <v>1.21841460808161</v>
       </c>
       <c r="F1931" t="n">
         <v>0.3521780628355597</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.137254285321766</v>
+        <v>-4.042216878373217</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.244589092395621</v>
+        <v>1.282604055175041</v>
       </c>
       <c r="F1932" t="n">
         <v>0.4874314241655369</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.197129112679458</v>
+        <v>-4.102091705730909</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.20667665285397</v>
+        <v>1.24469161563339</v>
       </c>
       <c r="F1933" t="n">
         <v>0.4275565968078447</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.077308881768621</v>
+        <v>-3.982271474820072</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.269893914452513</v>
+        <v>1.307908877231933</v>
       </c>
       <c r="F1934" t="n">
         <v>0.4275565968078447</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.079778588230427</v>
+        <v>-3.984741181281878</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.176550231190233</v>
+        <v>1.214565193969652</v>
       </c>
       <c r="F1935" t="n">
         <v>0.4250868903460386</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.148148774554437</v>
+        <v>-4.053111367605887</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.06846401814593</v>
+        <v>1.10647898092535</v>
       </c>
       <c r="F1936" t="n">
         <v>0.4343625893822535</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.260021054180588</v>
+        <v>-4.164983647232038</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.014151814927361</v>
+        <v>1.052166777706781</v>
       </c>
       <c r="F1937" t="n">
         <v>0.4343625893822535</v>
@@ -46125,10 +46125,10 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.24404638869432</v>
+        <v>-4.14900898174577</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9871162060458956</v>
+        <v>1.025131168825316</v>
       </c>
       <c r="F1938" t="n">
         <v>0.4343625893822535</v>
@@ -46148,10 +46148,10 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.068572128901851</v>
+        <v>-3.973534721953301</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.061873141954671</v>
+        <v>1.099888104734091</v>
       </c>
       <c r="F1939" t="n">
         <v>0.4343625893822535</v>
@@ -46171,10 +46171,10 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.060647754316936</v>
+        <v>-3.965610347368387</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.040784920549844</v>
+        <v>1.078799883329264</v>
       </c>
       <c r="F1940" t="n">
         <v>0.4343625893822535</v>
@@ -46194,10 +46194,10 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.054369551747087</v>
+        <v>-3.959332144798538</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9718345149792333</v>
+        <v>1.009849477758653</v>
       </c>
       <c r="F1941" t="n">
         <v>0.4406407919521026</v>
@@ -46217,10 +46217,10 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.994516932543364</v>
+        <v>-3.899479525594815</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.005947949092855</v>
+        <v>1.043962911872275</v>
       </c>
       <c r="F1942" t="n">
         <v>0.4406407919521026</v>
@@ -46240,10 +46240,10 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.908273469516987</v>
+        <v>-3.813236062568437</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.035391604877266</v>
+        <v>1.073406567656686</v>
       </c>
       <c r="F1943" t="n">
         <v>0.4406407919521026</v>
@@ -46263,10 +46263,10 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.953580288915966</v>
+        <v>-3.858542881967417</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.0090446525622</v>
+        <v>1.04705961534162</v>
       </c>
       <c r="F1944" t="n">
         <v>0.3998306289428718</v>
@@ -46286,10 +46286,10 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.982613393618268</v>
+        <v>-3.887575986669719</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9979832837143809</v>
+        <v>1.0359982464938</v>
       </c>
       <c r="F1945" t="n">
         <v>0.3998306289428718</v>
@@ -46309,10 +46309,10 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.889802912167409</v>
+        <v>-3.79476550521886</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9643801681860902</v>
+        <v>1.00239513096551</v>
       </c>
       <c r="F1946" t="n">
         <v>0.4926411103937312</v>
@@ -46332,10 +46332,10 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.934192381496836</v>
+        <v>-3.839154974548287</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9484978563789199</v>
+        <v>0.9865128191583397</v>
       </c>
       <c r="F1947" t="n">
         <v>0.4482516410643035</v>
@@ -46355,10 +46355,10 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.913688687611339</v>
+        <v>-3.81865128066279</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9517750424448419</v>
+        <v>0.9897900052242616</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4687553349498008</v>
@@ -46378,10 +46378,10 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.997360784323671</v>
+        <v>-3.902323377375122</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9237974995905764</v>
+        <v>0.961812462369996</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4687553349498008</v>
@@ -46401,10 +46401,10 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.025141182225024</v>
+        <v>-3.930103775276475</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9241825421985741</v>
+        <v>0.9621975049779938</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4409749370484478</v>
@@ -46424,10 +46424,10 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.143521854955162</v>
+        <v>-4.048484448006613</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.715185993107172</v>
+        <v>0.7532009558865917</v>
       </c>
       <c r="F1951" t="n">
         <v>0.3737570848974716</v>
@@ -46447,10 +46447,10 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.252135933398494</v>
+        <v>-4.157098526449944</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7918900224490453</v>
+        <v>0.829904985228465</v>
       </c>
       <c r="F1952" t="n">
         <v>0.3737570848974716</v>
@@ -46470,10 +46470,10 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.216726895150351</v>
+        <v>-4.121689488201802</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8205666638506255</v>
+        <v>0.858581626630045</v>
       </c>
       <c r="F1953" t="n">
         <v>0.3737570848974716</v>
@@ -46493,10 +46493,10 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.225188063805811</v>
+        <v>-4.130150656857262</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8146016377308098</v>
+        <v>0.8526166005102294</v>
       </c>
       <c r="F1954" t="n">
         <v>0.3652959162420105</v>
@@ -46516,10 +46516,10 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.048071733770645</v>
+        <v>-3.953034326822096</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8821771985901785</v>
+        <v>0.9201921613695982</v>
       </c>
       <c r="F1955" t="n">
         <v>0.3652959162420105</v>
@@ -46539,10 +46539,10 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.093163978604191</v>
+        <v>-3.998126571655642</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8648236924186734</v>
+        <v>0.9028386551980931</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3033998730726207</v>
@@ -46562,10 +46562,10 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.913788557365423</v>
+        <v>-3.818751150416874</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9303608362205948</v>
+        <v>0.9683757990000146</v>
       </c>
       <c r="F1957" t="n">
         <v>0.4601766312433394</v>
@@ -46585,10 +46585,10 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.95880277088603</v>
+        <v>-3.86376536393748</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8931626061439422</v>
+        <v>0.9311775689233617</v>
       </c>
       <c r="F1958" t="n">
         <v>0.4298277359287348</v>
@@ -46608,10 +46608,10 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.046813957444726</v>
+        <v>-3.951776550496178</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8636496938594092</v>
+        <v>0.9016646566388287</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3643512280695618</v>
@@ -46631,10 +46631,10 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.148011738881899</v>
+        <v>-4.052974331933351</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8223745031810414</v>
+        <v>0.8603894659604607</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2959424145242426</v>
@@ -46654,10 +46654,10 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.141500772267587</v>
+        <v>-4.046463365319038</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8225788513810832</v>
+        <v>0.8605938141605025</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2959424145242426</v>
@@ -46677,10 +46677,10 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.122462644560289</v>
+        <v>-4.027425237611741</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8267188216722472</v>
+        <v>0.8647337844516665</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2377588031930481</v>
@@ -46700,10 +46700,10 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.17497844683511</v>
+        <v>-4.079941039886561</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9250069023965093</v>
+        <v>0.9630218651759286</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2377588031930481</v>
@@ -46723,10 +46723,10 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.178386758269689</v>
+        <v>-4.083349351321141</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.924476906808811</v>
+        <v>0.9624918695882303</v>
       </c>
       <c r="F1964" t="n">
         <v>0.2702753722024255</v>
@@ -46746,10 +46746,10 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.159030622375842</v>
+        <v>-4.063993215427294</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9382278915632758</v>
+        <v>0.9762428543426951</v>
       </c>
       <c r="F1965" t="n">
         <v>0.2702753722024255</v>
@@ -46769,10 +46769,10 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.232360151113935</v>
+        <v>-4.137322744165386</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8068463013452383</v>
+        <v>0.8448612641246576</v>
       </c>
       <c r="F1966" t="n">
         <v>0.2706700346220474</v>
@@ -46792,10 +46792,10 @@
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.316181372388633</v>
+        <v>-4.221143965440085</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7761114343668398</v>
+        <v>0.8141263971462591</v>
       </c>
       <c r="F1967" t="n">
         <v>0.2706700346220474</v>
@@ -46815,10 +46815,10 @@
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.310028666335849</v>
+        <v>-4.2149912593873</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7792348651796119</v>
+        <v>0.8172498279590312</v>
       </c>
       <c r="F1968" t="n">
         <v>0.2768227406748317</v>
@@ -46838,10 +46838,10 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.326837964486351</v>
+        <v>-4.231800557537802</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7715916226595214</v>
+        <v>0.8096065854389407</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2600134425243301</v>
@@ -46861,10 +46861,10 @@
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.264539965710228</v>
+        <v>-4.16950255876168</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8628463759667913</v>
+        <v>0.9008613387462105</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3053077067987721</v>
@@ -46884,10 +46884,10 @@
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.06274976804507</v>
+        <v>-3.967712361096522</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7458544567469816</v>
+        <v>0.7838694195264009</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5033258989679266</v>
@@ -46907,10 +46907,10 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.113636480731265</v>
+        <v>-4.018599073782717</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7957900039946788</v>
+        <v>0.8338049667740981</v>
       </c>
       <c r="F1972" t="n">
         <v>0.452439186281732</v>
@@ -46930,10 +46930,10 @@
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.027025738081458</v>
+        <v>-3.93198833113291</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8450620371706452</v>
+        <v>0.8830769999500647</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5310649174868902</v>
@@ -46953,10 +46953,10 @@
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.087235036086743</v>
+        <v>-3.992197629138194</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8195142987932029</v>
+        <v>0.8575292615726227</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4708556194816057</v>
@@ -46976,10 +46976,10 @@
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.038048387402392</v>
+        <v>-3.943010980453843</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.837680576306872</v>
+        <v>0.8756955390862917</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4708556194816057</v>
@@ -46999,10 +46999,10 @@
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.993675255763823</v>
+        <v>-3.898637848815274</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8552926963977356</v>
+        <v>0.8933076591771554</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5152287511201743</v>
@@ -47022,10 +47022,10 @@
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.958943934445322</v>
+        <v>-3.863906527496773</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8635790190637267</v>
+        <v>0.9015939818431462</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5152287511201743</v>
@@ -47045,10 +47045,10 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.911288203884267</v>
+        <v>-3.816250796935718</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8890230683159535</v>
+        <v>0.927038031095373</v>
       </c>
       <c r="F1978" t="n">
         <v>0.56288448168123</v>
@@ -47068,10 +47068,10 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.810770045385512</v>
+        <v>-3.715732638436963</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9341227050901801</v>
+        <v>0.9721376678695997</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6634026401799845</v>
@@ -47091,10 +47091,10 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.794864715953159</v>
+        <v>-3.69982730900461</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9272395093389934</v>
+        <v>0.9652544721184131</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5842899794707457</v>
@@ -47114,10 +47114,10 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.750026314344761</v>
+        <v>-3.654988907396212</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9492725725929811</v>
+        <v>0.9872875353724009</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5888334124156152</v>
@@ -47137,10 +47137,10 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.76952477058677</v>
+        <v>-3.67448736363822</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9456341297272559</v>
+        <v>0.9836490925066754</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5407487711357108</v>
@@ -47160,10 +47160,10 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.725321933500869</v>
+        <v>-3.63028452655232</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9691948670894532</v>
+        <v>1.007209829868873</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5849516082216113</v>
@@ -47183,10 +47183,10 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.732881599337916</v>
+        <v>-3.637844192389367</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.964581001223882</v>
+        <v>1.002595964003302</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6397550122314306</v>
@@ -47206,10 +47206,10 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.574590181798644</v>
+        <v>-3.479552774850095</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.07914533342263</v>
+        <v>1.11716029620205</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6397550122314306</v>
@@ -47229,10 +47229,10 @@
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.366948178164168</v>
+        <v>-3.271910771215619</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.160642839470674</v>
+        <v>1.198657802250094</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8473970158659068</v>
@@ -47252,10 +47252,10 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.31591608544164</v>
+        <v>-3.220878678493091</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.176003904797955</v>
+        <v>1.214018867577375</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8984291085884347</v>
@@ -47275,10 +47275,10 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.250691904314434</v>
+        <v>-3.155654497365885</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.219280981341543</v>
+        <v>1.257295944120962</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9636532897156403</v>
@@ -47298,10 +47298,10 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.2132648842433</v>
+        <v>-3.118227477294751</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.230212761669276</v>
+        <v>1.268227724448696</v>
       </c>
       <c r="F1989" t="n">
         <v>0.968904827744822</v>
@@ -47321,10 +47321,10 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.211906899269755</v>
+        <v>-3.116869492321205</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.232012747989935</v>
+        <v>1.270027710769355</v>
       </c>
       <c r="F1990" t="n">
         <v>1.043242953282641</v>
@@ -47344,10 +47344,10 @@
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.183493636169871</v>
+        <v>-3.088456229221322</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.403935824251099</v>
+        <v>1.441950787030519</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9842673905362118</v>
@@ -47367,10 +47367,10 @@
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.108711375144858</v>
+        <v>-3.013673968196309</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.553961637878921</v>
+        <v>1.591976600658341</v>
       </c>
       <c r="F1992" t="n">
         <v>1.059049651561224</v>
@@ -47390,10 +47390,10 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.08262729088105</v>
+        <v>-2.987589883932501</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.556103247598304</v>
+        <v>1.594118210377723</v>
       </c>
       <c r="F1993" t="n">
         <v>1.059049651561224</v>
@@ -47413,10 +47413,10 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.99474937777193</v>
+        <v>-2.899711970823381</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.589447608425731</v>
+        <v>1.627462571205151</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174975293984576</v>
@@ -47436,10 +47436,10 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.985856916378647</v>
+        <v>-2.890819509430098</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.610558998709836</v>
+        <v>1.648573961489256</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174975293984576</v>
@@ -47459,10 +47459,10 @@
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.154333033348525</v>
+        <v>-3.059295626399976</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.535023599326469</v>
+        <v>1.573038562105888</v>
       </c>
       <c r="F1996" t="n">
         <v>1.147027458267995</v>
@@ -47482,10 +47482,10 @@
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.708076840719085</v>
+        <v>-2.613039433770536</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.694795773566107</v>
+        <v>1.732810736345526</v>
       </c>
       <c r="F1997" t="n">
         <v>1.052308788598362</v>
@@ -47505,10 +47505,10 @@
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.685355737035932</v>
+        <v>-2.590318330087383</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.694548237536272</v>
+        <v>1.732563200315692</v>
       </c>
       <c r="F1998" t="n">
         <v>1.052308788598362</v>
@@ -47528,10 +47528,10 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.814557550329975</v>
+        <v>-2.719520143381426</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.801773638069824</v>
+        <v>1.839788600849244</v>
       </c>
       <c r="F1999" t="n">
         <v>0.92310697530432</v>
@@ -47551,10 +47551,10 @@
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.840431948804</v>
+        <v>-2.745394541855451</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.82850170117386</v>
+        <v>1.86651666395328</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9680185840160611</v>
@@ -47574,10 +47574,10 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.833377258588827</v>
+        <v>-2.738339851640278</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.827998933249475</v>
+        <v>1.866013896028895</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9750732742312349</v>
@@ -47597,10 +47597,10 @@
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.806426034262339</v>
+        <v>-2.71138862731379</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.848785576624812</v>
+        <v>1.886800539404231</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9899536202589541</v>
@@ -47620,10 +47620,10 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.827970262093126</v>
+        <v>-2.732932855144577</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.024271017637457</v>
+        <v>2.062285980416876</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9899536202589541</v>
@@ -47643,10 +47643,10 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.850378379897998</v>
+        <v>-2.755340972949449</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.007424465418501</v>
+        <v>2.045439428197921</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9899536202589541</v>
@@ -47666,10 +47666,10 @@
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.878602615475598</v>
+        <v>-2.783565208527049</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.998188770737098</v>
+        <v>2.036203733516518</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007930372710263</v>
@@ -47689,10 +47689,10 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.888043541364128</v>
+        <v>-2.793006134415579</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.050666118103534</v>
+        <v>2.088681080882953</v>
       </c>
       <c r="F2006" t="n">
         <v>1.130357490253654</v>
@@ -47712,10 +47712,10 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.976920172532602</v>
+        <v>-2.881882765584053</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.018006560181445</v>
+        <v>2.056021522960864</v>
       </c>
       <c r="F2007" t="n">
         <v>1.04148085908518</v>
@@ -47735,10 +47735,10 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.053250150133508</v>
+        <v>-2.958212743184959</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.985586382034858</v>
+        <v>2.023601344814277</v>
       </c>
       <c r="F2008" t="n">
         <v>1.04148085908518</v>
@@ -47758,10 +47758,10 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.208206935533637</v>
+        <v>-3.113169528585088</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.918423897477668</v>
+        <v>1.956438860257088</v>
       </c>
       <c r="F2009" t="n">
         <v>0.886524073685051</v>
@@ -47781,10 +47781,10 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.369775361060892</v>
+        <v>-3.274737954112343</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.852230537476918</v>
+        <v>1.890245500256338</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7597411498871717</v>
@@ -47804,10 +47804,10 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.478076022931012</v>
+        <v>-3.383038615982463</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.821983679594789</v>
+        <v>1.859998642374209</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7597411498871717</v>
@@ -47827,10 +47827,10 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.495879994651756</v>
+        <v>-3.400842587703207</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.806867287689432</v>
+        <v>1.844882250468851</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6892065269819705</v>
@@ -47850,10 +47850,10 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.523780781761229</v>
+        <v>-3.42874337481268</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.794231013972644</v>
+        <v>1.832245976752064</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6546096028390357</v>
@@ -47873,10 +47873,10 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.646306884464123</v>
+        <v>-3.551269477515574</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.741985016868686</v>
+        <v>1.779999979648105</v>
       </c>
       <c r="F2014" t="n">
         <v>0.5320835001361418</v>
@@ -47896,10 +47896,10 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.876821380649711</v>
+        <v>-3.781783973701162</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.716485177984954</v>
+        <v>1.754500140764374</v>
       </c>
       <c r="F2015" t="n">
         <v>0.3015690039505531</v>
@@ -47919,10 +47919,10 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.225566465874155</v>
+        <v>-4.130529058925606</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.717298862897024</v>
+        <v>1.755313825676443</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1928210500316553</v>
@@ -47942,10 +47942,10 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.379552883650295</v>
+        <v>-4.284515476701746</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.724684564932207</v>
+        <v>1.762699527711627</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1928210500316553</v>
@@ -47965,10 +47965,10 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.584152318513304</v>
+        <v>-4.489114911564755</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.628895993107125</v>
+        <v>1.666910955886544</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1928210500316553</v>
@@ -47988,10 +47988,10 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.836627472521029</v>
+        <v>-4.741590065572479</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.539776420559449</v>
+        <v>1.577791383338868</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1928210500316553</v>
@@ -48011,10 +48011,10 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.129523229000441</v>
+        <v>-5.034485822051892</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.423828652486628</v>
+        <v>1.461843615266047</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1928210500316553</v>
@@ -48034,10 +48034,10 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.316187357135249</v>
+        <v>-5.2211499501867</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.353284743460026</v>
+        <v>1.391299706239446</v>
       </c>
       <c r="F2021" t="n">
         <v>0.1660820792070954</v>
@@ -48057,10 +48057,10 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.462208044049211</v>
+        <v>-5.367170637100662</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.28995432143063</v>
+        <v>1.32796928421005</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1569989874132384</v>
@@ -48080,10 +48080,10 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.553922053158797</v>
+        <v>-5.458884646210247</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.41547277448584</v>
+        <v>1.45348773726526</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1569989874132384</v>
@@ -48103,10 +48103,10 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.585573712218766</v>
+        <v>-5.490536305270217</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.397658748825667</v>
+        <v>1.435673711605086</v>
       </c>
       <c r="F2024" t="n">
         <v>0.1518305301687982</v>
@@ -48126,10 +48126,10 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.654639766791703</v>
+        <v>-5.559602359843153</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.380261744564983</v>
+        <v>1.418276707344403</v>
       </c>
       <c r="F2025" t="n">
         <v>0.08945965267518818</v>
@@ -48149,10 +48149,10 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.75661588904011</v>
+        <v>-5.661578482091561</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.348396934121523</v>
+        <v>1.386411896900942</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.01251646957321939</v>
@@ -48172,10 +48172,10 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.646609605562888</v>
+        <v>-5.551572198614339</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.384552334756587</v>
+        <v>1.422567297536006</v>
       </c>
       <c r="F2027" t="n">
         <v>0.01068810234405582</v>
@@ -48195,10 +48195,10 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.503550029821962</v>
+        <v>-5.408512622873413</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.446026175774931</v>
+        <v>1.484041138554351</v>
       </c>
       <c r="F2028" t="n">
         <v>0.01870152893403509</v>
@@ -48218,10 +48218,10 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.202103304350125</v>
+        <v>-5.107065897401576</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.573865748846202</v>
+        <v>1.611880711625622</v>
       </c>
       <c r="F2029" t="n">
         <v>0.3201482544058724</v>
@@ -48241,10 +48241,10 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.226693548585309</v>
+        <v>-5.13165614163676</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.565000828904839</v>
+        <v>1.603015791684259</v>
       </c>
       <c r="F2030" t="n">
         <v>0.3201482544058724</v>
@@ -48264,10 +48264,10 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.175655172578788</v>
+        <v>-5.080617765630239</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.586259083687203</v>
+        <v>1.624274046466623</v>
       </c>
       <c r="F2031" t="n">
         <v>0.3201482544058724</v>
@@ -48287,10 +48287,10 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.146806495755328</v>
+        <v>-5.051769088806779</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.616836653290733</v>
+        <v>1.654851616070152</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3489969312293326</v>
@@ -48310,10 +48310,10 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.050171583736688</v>
+        <v>-4.955134176788139</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.471674614222123</v>
+        <v>1.509689577001543</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4456318432479726</v>
@@ -48333,10 +48333,10 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.98113357278822</v>
+        <v>-4.886096165839671</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.502791862675474</v>
+        <v>1.540806825454894</v>
       </c>
       <c r="F2034" t="n">
         <v>0.5146698541964406</v>
@@ -48356,10 +48356,10 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.816637238597258</v>
+        <v>-4.721599831648709</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.553017215427942</v>
+        <v>1.591032178207361</v>
       </c>
       <c r="F2035" t="n">
         <v>0.6791661883874025</v>
@@ -48379,10 +48379,10 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.739538637055386</v>
+        <v>-4.644501230106837</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.58304436648112</v>
+        <v>1.62105932926054</v>
       </c>
       <c r="F2036" t="n">
         <v>0.6791661883874025</v>
@@ -48402,10 +48402,10 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.749923831945275</v>
+        <v>-4.654886424996726</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.588759067650237</v>
+        <v>1.626774030429657</v>
       </c>
       <c r="F2037" t="n">
         <v>0.6687809934975132</v>
@@ -48425,10 +48425,10 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.7685119906675</v>
+        <v>-4.673474583718951</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.652160809937772</v>
+        <v>1.690175772717192</v>
       </c>
       <c r="F2038" t="n">
         <v>0.6501928347752879</v>
@@ -48448,10 +48448,10 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.768810537363536</v>
+        <v>-4.673773130414987</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.648910402077656</v>
+        <v>1.686925364857076</v>
       </c>
       <c r="F2039" t="n">
         <v>0.649894288079252</v>
@@ -48471,10 +48471,10 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.667987403673108</v>
+        <v>-4.572949996724559</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.693770550493219</v>
+        <v>1.731785513272639</v>
       </c>
       <c r="F2040" t="n">
         <v>0.6623585035636058</v>
@@ -48494,10 +48494,10 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.477206042920701</v>
+        <v>-4.382168635972151</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.770212348272725</v>
+        <v>1.808227311052145</v>
       </c>
       <c r="F2041" t="n">
         <v>0.8531398643160132</v>
@@ -48517,10 +48517,10 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.370242685071279</v>
+        <v>-4.27520527812273</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.792834537150091</v>
+        <v>1.83084949992951</v>
       </c>
       <c r="F2042" t="n">
         <v>0.9116044722758146</v>
@@ -48540,10 +48540,10 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.314912097169517</v>
+        <v>-4.219874690220967</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.849933708922854</v>
+        <v>1.887948671702274</v>
       </c>
       <c r="F2043" t="n">
         <v>0.9669350601775768</v>
@@ -48563,10 +48563,10 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.302857970256554</v>
+        <v>-4.207820563308005</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.848441927589477</v>
+        <v>1.886456890368897</v>
       </c>
       <c r="F2044" t="n">
         <v>0.9789891870905396</v>
@@ -48586,10 +48586,10 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.344013089824775</v>
+        <v>-4.248975682876226</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.833860509946324</v>
+        <v>1.871875472725744</v>
       </c>
       <c r="F2045" t="n">
         <v>0.9378340675223187</v>
@@ -48609,10 +48609,10 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.275964527133245</v>
+        <v>-4.180927120184696</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.873930960900819</v>
+        <v>1.911945923680238</v>
       </c>
       <c r="F2046" t="n">
         <v>1.005882630213848</v>
@@ -48632,10 +48632,10 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.507564920302745</v>
+        <v>-4.412527513354196</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.801493473806613</v>
+        <v>1.839508436586032</v>
       </c>
       <c r="F2047" t="n">
         <v>1.005882630213848</v>
@@ -48655,10 +48655,10 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.557616465831964</v>
+        <v>-4.462579058883415</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.765079091661807</v>
+        <v>1.803094054441227</v>
       </c>
       <c r="F2048" t="n">
         <v>1.005882630213848</v>
@@ -48678,10 +48678,10 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.732723298408409</v>
+        <v>-4.63768589145986</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.655288272224696</v>
+        <v>1.693303235004116</v>
       </c>
       <c r="F2049" t="n">
         <v>1.005882630213848</v>
@@ -48701,10 +48701,10 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.536623144977886</v>
+        <v>-4.441585738029337</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.740750952593845</v>
+        <v>1.778765915373265</v>
       </c>
       <c r="F2050" t="n">
         <v>1.201982783644371</v>
@@ -48724,10 +48724,10 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.383597752864602</v>
+        <v>-4.288560345916053</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.901132109012063</v>
+        <v>1.939147071791483</v>
       </c>
       <c r="F2051" t="n">
         <v>1.355008175757655</v>
@@ -48747,10 +48747,10 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.411905066737872</v>
+        <v>-4.316867659789323</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.077275408371047</v>
+        <v>2.115290371150468</v>
       </c>
       <c r="F2052" t="n">
         <v>1.355008175757655</v>
@@ -48770,10 +48770,10 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.578498291851394</v>
+        <v>-4.483460884902845</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.980041069679721</v>
+        <v>2.018056032459141</v>
       </c>
       <c r="F2053" t="n">
         <v>1.188414950644133</v>
@@ -48793,10 +48793,10 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.555462498489828</v>
+        <v>-4.460425091541279</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.992931789686065</v>
+        <v>2.030946752465485</v>
       </c>
       <c r="F2054" t="n">
         <v>1.188414950644133</v>
@@ -48816,10 +48816,10 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.526216518034132</v>
+        <v>-4.431179111085583</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.002248236991839</v>
+        <v>2.040263199771259</v>
       </c>
       <c r="F2055" t="n">
         <v>1.188414950644133</v>
@@ -48839,10 +48839,10 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.633142065911983</v>
+        <v>-4.538104658963434</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.956771256998334</v>
+        <v>1.994786219777754</v>
       </c>
       <c r="F2056" t="n">
         <v>1.081489402766282</v>
@@ -48862,10 +48862,10 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.778160624419232</v>
+        <v>-4.683123217470682</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.900192635738669</v>
+        <v>1.938207598518089</v>
       </c>
       <c r="F2057" t="n">
         <v>0.936470844259033</v>
@@ -48885,10 +48885,10 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.896502390203949</v>
+        <v>-4.8014649832554</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.952787168682535</v>
+        <v>1.990802131461955</v>
       </c>
       <c r="F2058" t="n">
         <v>0.9471568828219231</v>
@@ -48908,10 +48908,10 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.947912812524657</v>
+        <v>-4.852875405576108</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.930008696880191</v>
+        <v>1.96802365965961</v>
       </c>
       <c r="F2059" t="n">
         <v>0.9471568828219231</v>
@@ -48931,10 +48931,10 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.027332263732409</v>
+        <v>-4.93229485678386</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.898144044471379</v>
+        <v>1.936159007250799</v>
       </c>
       <c r="F2060" t="n">
         <v>0.9471568828219231</v>
@@ -48954,10 +48954,10 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.122795261649626</v>
+        <v>-5.027757854701077</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.859952738862535</v>
+        <v>1.897967701641955</v>
       </c>
       <c r="F2061" t="n">
         <v>0.9471568828219231</v>
@@ -48977,10 +48977,10 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.058419350798911</v>
+        <v>-4.963381943850362</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.883799499765432</v>
+        <v>1.921814462544852</v>
       </c>
       <c r="F2062" t="n">
         <v>1.011532793672638</v>
@@ -49000,10 +49000,10 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.113788512931105</v>
+        <v>-5.018751105982556</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.867385652660281</v>
+        <v>1.905400615439701</v>
       </c>
       <c r="F2063" t="n">
         <v>1.011532793672638</v>
@@ -49023,10 +49023,10 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.132006979928714</v>
+        <v>-5.036969572980165</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.85963662920417</v>
+        <v>1.897651591983589</v>
       </c>
       <c r="F2064" t="n">
         <v>0.986426356416796</v>
@@ -49046,10 +49046,10 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.043800145781136</v>
+        <v>-4.948762738832587</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.91479375571352</v>
+        <v>1.952808718492939</v>
       </c>
       <c r="F2065" t="n">
         <v>0.986426356416796</v>
@@ -49069,10 +49069,10 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.937765150575826</v>
+        <v>-4.842727743627277</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.940908454320371</v>
+        <v>1.978923417099791</v>
       </c>
       <c r="F2066" t="n">
         <v>0.986426356416796</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.754553487442731</v>
+        <v>-4.659516080494182</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.016624069037655</v>
+        <v>2.054639031817075</v>
       </c>
       <c r="F2067" t="n">
         <v>0.986426356416796</v>
@@ -49115,10 +49115,10 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.68283204042888</v>
+        <v>-4.587794633480331</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.028257053922572</v>
+        <v>2.066272016701992</v>
       </c>
       <c r="F2068" t="n">
         <v>1.058147803430647</v>
@@ -49138,10 +49138,10 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.660459014821174</v>
+        <v>-4.565421607872625</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.984122010086827</v>
+        <v>2.022136972866246</v>
       </c>
       <c r="F2069" t="n">
         <v>1.069403554543548</v>
@@ -49161,10 +49161,10 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.693475310731919</v>
+        <v>-4.59843790378337</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.156113696607884</v>
+        <v>2.194128659387304</v>
       </c>
       <c r="F2070" t="n">
         <v>0.9999661778767968</v>
@@ -49184,10 +49184,10 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.68194767508231</v>
+        <v>-4.586910268133761</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.152645976695977</v>
+        <v>2.190660939475396</v>
       </c>
       <c r="F2071" t="n">
         <v>1.058966836078159</v>
@@ -49207,10 +49207,10 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.779289176424679</v>
+        <v>-4.68425176947613</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.117377488680818</v>
+        <v>2.155392451460237</v>
       </c>
       <c r="F2072" t="n">
         <v>1.014546653912671</v>
@@ -49230,10 +49230,10 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.865145205764645</v>
+        <v>-4.770107798816096</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.084286159137669</v>
+        <v>2.122301121917089</v>
       </c>
       <c r="F2073" t="n">
         <v>0.9721705846865358</v>
@@ -49253,10 +49253,10 @@
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.873982003180765</v>
+        <v>-4.778944596232216</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.063170641991723</v>
+        <v>2.101185604771143</v>
       </c>
       <c r="F2074" t="n">
         <v>0.9647284120451851</v>
@@ -49276,10 +49276,10 @@
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.965364565746223</v>
+        <v>-4.870327158797674</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.036782128010589</v>
+        <v>2.074797090790009</v>
       </c>
       <c r="F2075" t="n">
         <v>0.9281635273258404</v>
@@ -49299,10 +49299,10 @@
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.953657847759217</v>
+        <v>-4.858620440810668</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.14359307302966</v>
+        <v>2.18160803580908</v>
       </c>
       <c r="F2076" t="n">
         <v>0.9398702453128468</v>
@@ -49322,10 +49322,10 @@
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.024569921501495</v>
+        <v>-4.929532514552946</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.118260582264154</v>
+        <v>2.156275545043573</v>
       </c>
       <c r="F2077" t="n">
         <v>0.9398702453128468</v>
@@ -49345,10 +49345,10 @@
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.034886019667847</v>
+        <v>-4.939848612719298</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.327038976275671</v>
+        <v>2.365053939055091</v>
       </c>
       <c r="F2078" t="n">
         <v>0.9398702453128468</v>
@@ -49368,10 +49368,10 @@
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.034792051650474</v>
+        <v>-4.939754644701925</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.32625523039471</v>
+        <v>2.364270193174129</v>
       </c>
       <c r="F2079" t="n">
         <v>0.9402401066601648</v>
@@ -49391,10 +49391,10 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.183158279306619</v>
+        <v>-5.08812087235807</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.261140725276606</v>
+        <v>2.299155688056025</v>
       </c>
       <c r="F2080" t="n">
         <v>0.9402401066601648</v>
@@ -49414,10 +49414,10 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.182209856188581</v>
+        <v>-5.087172449240032</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.261520094523821</v>
+        <v>2.29953505730324</v>
       </c>
       <c r="F2081" t="n">
         <v>0.9402401066601648</v>
@@ -49437,10 +49437,10 @@
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.282479674147602</v>
+        <v>-5.187442267199053</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.234139775321304</v>
+        <v>2.272154738100724</v>
       </c>
       <c r="F2082" t="n">
         <v>0.9402401066601648</v>
@@ -49460,10 +49460,10 @@
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.276487427358791</v>
+        <v>-5.181450020410241</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.238482672461217</v>
+        <v>2.276497635240637</v>
       </c>
       <c r="F2083" t="n">
         <v>0.9402401066601648</v>
@@ -49483,10 +49483,10 @@
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.187929466228023</v>
+        <v>-5.092892059279474</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.267559992931293</v>
+        <v>2.305574955710712</v>
       </c>
       <c r="F2084" t="n">
         <v>0.9402401066601648</v>
@@ -49506,10 +49506,10 @@
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.170170388724949</v>
+        <v>-5.0751329817764</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.273972301371518</v>
+        <v>2.311987264150938</v>
       </c>
       <c r="F2085" t="n">
         <v>0.9402401066601648</v>
@@ -49529,10 +49529,10 @@
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.070540237675881</v>
+        <v>-4.975502830727332</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.326606547699732</v>
+        <v>2.364621510479152</v>
       </c>
       <c r="F2086" t="n">
         <v>1.039870257709232</v>
@@ -49552,10 +49552,10 @@
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.119939746364892</v>
+        <v>-5.024902339416343</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.496001009722854</v>
+        <v>2.534015972502274</v>
       </c>
       <c r="F2087" t="n">
         <v>1.050129091140977</v>
@@ -49575,10 +49575,10 @@
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.913255272722516</v>
+        <v>-4.818217865773967</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.565863472282667</v>
+        <v>2.603878435062086</v>
       </c>
       <c r="F2088" t="n">
         <v>1.256813564783353</v>
@@ -49592,16 +49592,16 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162541</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.947412167720042</v>
+        <v>-4.852374760771493</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.554202227937761</v>
+        <v>2.59221719071718</v>
       </c>
       <c r="F2089" t="n">
         <v>1.17322979524254</v>
@@ -49621,10 +49621,10 @@
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.854822688658586</v>
+        <v>-4.759785281710037</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.944735133552011</v>
+        <v>2.982750096331431</v>
       </c>
       <c r="F2090" t="n">
         <v>1.17322979524254</v>
@@ -49644,10 +49644,10 @@
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.914711316482136</v>
+        <v>-4.819673909533587</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.925342793989694</v>
+        <v>2.963357756769113</v>
       </c>
       <c r="F2091" t="n">
         <v>1.159107880555076</v>
@@ -49667,10 +49667,10 @@
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.862495006685794</v>
+        <v>-4.767457599737245</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.996059259231759</v>
+        <v>3.034074222011178</v>
       </c>
       <c r="F2092" t="n">
         <v>1.159107880555076</v>
@@ -49690,10 +49690,10 @@
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.830597489600549</v>
+        <v>-4.735560082651999</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.017632236275867</v>
+        <v>3.055647199055287</v>
       </c>
       <c r="F2093" t="n">
         <v>1.191005397640321</v>
@@ -49713,10 +49713,10 @@
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.845352813800689</v>
+        <v>-4.75031540685214</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.007367690635008</v>
+        <v>3.045382653414427</v>
       </c>
       <c r="F2094" t="n">
         <v>1.191005397640321</v>
@@ -49736,10 +49736,10 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.795888190430778</v>
+        <v>-4.700850783482228</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.018078043399253</v>
+        <v>3.056093006178672</v>
       </c>
       <c r="F2095" t="n">
         <v>1.240470021010233</v>
@@ -49759,10 +49759,10 @@
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.632780198277162</v>
+        <v>-4.537742791328613</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.079728907975634</v>
+        <v>3.117743870755053</v>
       </c>
       <c r="F2096" t="n">
         <v>1.403578013163848</v>
@@ -49782,10 +49782,10 @@
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.499972572779996</v>
+        <v>-4.404935165831446</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.141898994865628</v>
+        <v>3.179913957645048</v>
       </c>
       <c r="F2097" t="n">
         <v>1.403578013163848</v>
@@ -49805,10 +49805,10 @@
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.562680489254554</v>
+        <v>-4.467643082306004</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.117673293261927</v>
+        <v>3.155688256041346</v>
       </c>
       <c r="F2098" t="n">
         <v>1.340870096689291</v>
@@ -49828,10 +49828,10 @@
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.514672365410861</v>
+        <v>-4.419634958462312</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.099785959589756</v>
+        <v>3.137800922369175</v>
       </c>
       <c r="F2099" t="n">
         <v>1.340870096689291</v>
@@ -49851,10 +49851,10 @@
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.43584670822727</v>
+        <v>-4.340809301278721</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.135248476021142</v>
+        <v>3.173263438800562</v>
       </c>
       <c r="F2100" t="n">
         <v>1.419695753872881</v>
@@ -49868,16 +49868,16 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.826998233414551</v>
+        <v>3.877919040828481</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.243911906973397</v>
+        <v>-4.148874500024847</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.206921489129729</v>
+        <v>3.244936451909148</v>
       </c>
       <c r="F2101" t="n">
         <v>1.419695753872881</v>

--- a/tame_output/ON/bt/strategyON_20240929.xlsx
+++ b/tame_output/ON/bt/strategyON_20240929.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>112.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>178.9%</t>
+          <t>175.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.5%</t>
+          <t>122.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.7%</t>
+          <t>422.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-576.5%</t>
+          <t>-584.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-54.7%</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-300.6%</t>
+          <t>-301.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129.6%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>118.0%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>129.6%</t>
+          <t>40.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2101"/>
+  <dimension ref="A1:G2102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.297643323067692</v>
+        <v>-4.397768626119182</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.169199530295509</v>
+        <v>1.129149409074913</v>
       </c>
       <c r="F1930" t="n">
         <v>0.2320049794710608</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.177470239703194</v>
+        <v>-4.277595542754683</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.21841460808161</v>
+        <v>1.178364486861015</v>
       </c>
       <c r="F1931" t="n">
         <v>0.3521780628355597</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.042216878373217</v>
+        <v>-4.142342181424706</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.282604055175041</v>
+        <v>1.242553933954445</v>
       </c>
       <c r="F1932" t="n">
         <v>0.4874314241655369</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.102091705730909</v>
+        <v>-4.202217008782398</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24469161563339</v>
+        <v>1.204641494412794</v>
       </c>
       <c r="F1933" t="n">
         <v>0.4275565968078447</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.982271474820072</v>
+        <v>-4.082396777871561</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.307908877231933</v>
+        <v>1.267858756011337</v>
       </c>
       <c r="F1934" t="n">
         <v>0.4275565968078447</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.984741181281878</v>
+        <v>-4.084866484333367</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.214565193969652</v>
+        <v>1.174515072749057</v>
       </c>
       <c r="F1935" t="n">
         <v>0.4250868903460386</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.053111367605887</v>
+        <v>-4.153236670657377</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.10647898092535</v>
+        <v>1.066428859704754</v>
       </c>
       <c r="F1936" t="n">
         <v>0.4343625893822535</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.164983647232038</v>
+        <v>-4.265108950283528</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.052166777706781</v>
+        <v>1.012116656486185</v>
       </c>
       <c r="F1937" t="n">
         <v>0.4343625893822535</v>
@@ -46125,10 +46125,10 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.14900898174577</v>
+        <v>-4.24913428479726</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.025131168825316</v>
+        <v>0.9850810476047196</v>
       </c>
       <c r="F1938" t="n">
         <v>0.4343625893822535</v>
@@ -46148,10 +46148,10 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.973534721953301</v>
+        <v>-4.073660025004791</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.099888104734091</v>
+        <v>1.059837983513495</v>
       </c>
       <c r="F1939" t="n">
         <v>0.4343625893822535</v>
@@ -46171,10 +46171,10 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.965610347368387</v>
+        <v>-4.065735650419877</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.078799883329264</v>
+        <v>1.038749762108668</v>
       </c>
       <c r="F1940" t="n">
         <v>0.4343625893822535</v>
@@ -46194,10 +46194,10 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.959332144798538</v>
+        <v>-4.059457447850028</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.009849477758653</v>
+        <v>0.9697993565380569</v>
       </c>
       <c r="F1941" t="n">
         <v>0.4406407919521026</v>
@@ -46217,10 +46217,10 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.899479525594815</v>
+        <v>-3.999604828646305</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.043962911872275</v>
+        <v>1.003912790651678</v>
       </c>
       <c r="F1942" t="n">
         <v>0.4406407919521026</v>
@@ -46240,10 +46240,10 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.813236062568437</v>
+        <v>-3.913361365619927</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.073406567656686</v>
+        <v>1.03335644643609</v>
       </c>
       <c r="F1943" t="n">
         <v>0.4406407919521026</v>
@@ -46263,10 +46263,10 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.858542881967417</v>
+        <v>-3.958668185018907</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.04705961534162</v>
+        <v>1.007009494121024</v>
       </c>
       <c r="F1944" t="n">
         <v>0.3998306289428718</v>
@@ -46286,10 +46286,10 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.887575986669719</v>
+        <v>-3.987701289721209</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.0359982464938</v>
+        <v>0.9959481252732045</v>
       </c>
       <c r="F1945" t="n">
         <v>0.3998306289428718</v>
@@ -46309,10 +46309,10 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.79476550521886</v>
+        <v>-3.89489080827035</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.00239513096551</v>
+        <v>0.9623450097449138</v>
       </c>
       <c r="F1946" t="n">
         <v>0.4926411103937312</v>
@@ -46332,10 +46332,10 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.839154974548287</v>
+        <v>-3.939280277599777</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9865128191583397</v>
+        <v>0.9464626979377437</v>
       </c>
       <c r="F1947" t="n">
         <v>0.4482516410643035</v>
@@ -46355,10 +46355,10 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.81865128066279</v>
+        <v>-3.91877658371428</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9897900052242616</v>
+        <v>0.9497398840036655</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4687553349498008</v>
@@ -46378,10 +46378,10 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.902323377375122</v>
+        <v>-4.002448680426612</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.961812462369996</v>
+        <v>0.9217623411494</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4687553349498008</v>
@@ -46401,10 +46401,10 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.930103775276475</v>
+        <v>-4.030229078327965</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9621975049779938</v>
+        <v>0.9221473837573979</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4409749370484478</v>
@@ -46424,10 +46424,10 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.048484448006613</v>
+        <v>-4.148609751058103</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7532009558865917</v>
+        <v>0.7131508346659958</v>
       </c>
       <c r="F1951" t="n">
         <v>0.3737570848974716</v>
@@ -46447,10 +46447,10 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.157098526449944</v>
+        <v>-4.257223829501434</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.829904985228465</v>
+        <v>0.7898548640078689</v>
       </c>
       <c r="F1952" t="n">
         <v>0.3737570848974716</v>
@@ -46470,10 +46470,10 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.121689488201802</v>
+        <v>-4.221814791253292</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.858581626630045</v>
+        <v>0.8185315054094491</v>
       </c>
       <c r="F1953" t="n">
         <v>0.3737570848974716</v>
@@ -46493,10 +46493,10 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.130150656857262</v>
+        <v>-4.230275959908752</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8526166005102294</v>
+        <v>0.8125664792896334</v>
       </c>
       <c r="F1954" t="n">
         <v>0.3652959162420105</v>
@@ -46516,10 +46516,10 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.953034326822096</v>
+        <v>-4.053159629873586</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9201921613695982</v>
+        <v>0.8801420401490023</v>
       </c>
       <c r="F1955" t="n">
         <v>0.3652959162420105</v>
@@ -46539,10 +46539,10 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.998126571655642</v>
+        <v>-4.098251874707132</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9028386551980931</v>
+        <v>0.862788533977497</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3033998730726207</v>
@@ -46562,10 +46562,10 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.818751150416874</v>
+        <v>-3.918876453468364</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9683757990000146</v>
+        <v>0.9283256777794184</v>
       </c>
       <c r="F1957" t="n">
         <v>0.4601766312433394</v>
@@ -46585,10 +46585,10 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.86376536393748</v>
+        <v>-3.96389066698897</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9311775689233617</v>
+        <v>0.8911274477027658</v>
       </c>
       <c r="F1958" t="n">
         <v>0.4298277359287348</v>
@@ -46608,10 +46608,10 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.951776550496178</v>
+        <v>-4.051901853547667</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9016646566388287</v>
+        <v>0.8616145354182327</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3643512280695618</v>
@@ -46631,10 +46631,10 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.052974331933351</v>
+        <v>-4.15309963498484</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8603894659604607</v>
+        <v>0.8203393447398653</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2959424145242426</v>
@@ -46654,10 +46654,10 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.046463365319038</v>
+        <v>-4.146588668370527</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8605938141605025</v>
+        <v>0.820543692939907</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2959424145242426</v>
@@ -46677,10 +46677,10 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.027425237611741</v>
+        <v>-4.12755054066323</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8647337844516665</v>
+        <v>0.8246836632310708</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2377588031930481</v>
@@ -46700,10 +46700,10 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.079941039886561</v>
+        <v>-4.18006634293805</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9630218651759286</v>
+        <v>0.9229717439553329</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2377588031930481</v>
@@ -46723,10 +46723,10 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.083349351321141</v>
+        <v>-4.18347465437263</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9624918695882303</v>
+        <v>0.9224417483676346</v>
       </c>
       <c r="F1964" t="n">
         <v>0.2702753722024255</v>
@@ -46746,10 +46746,10 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.063993215427294</v>
+        <v>-4.164118518478783</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9762428543426951</v>
+        <v>0.9361927331220996</v>
       </c>
       <c r="F1965" t="n">
         <v>0.2702753722024255</v>
@@ -46769,10 +46769,10 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.137322744165386</v>
+        <v>-4.237448047216875</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8448612641246576</v>
+        <v>0.8048111429040619</v>
       </c>
       <c r="F1966" t="n">
         <v>0.2706700346220474</v>
@@ -46792,10 +46792,10 @@
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.221143965440085</v>
+        <v>-4.321269268491574</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8141263971462591</v>
+        <v>0.7740762759256636</v>
       </c>
       <c r="F1967" t="n">
         <v>0.2706700346220474</v>
@@ -46815,10 +46815,10 @@
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.2149912593873</v>
+        <v>-4.315116562438789</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8172498279590312</v>
+        <v>0.7771997067384357</v>
       </c>
       <c r="F1968" t="n">
         <v>0.2768227406748317</v>
@@ -46838,10 +46838,10 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.231800557537802</v>
+        <v>-4.331925860589291</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8096065854389407</v>
+        <v>0.7695564642183452</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2600134425243301</v>
@@ -46861,10 +46861,10 @@
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.16950255876168</v>
+        <v>-4.269627861813169</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9008613387462105</v>
+        <v>0.8608112175256148</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3053077067987721</v>
@@ -46884,10 +46884,10 @@
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.967712361096522</v>
+        <v>-4.067837664148011</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7838694195264009</v>
+        <v>0.7438192983058052</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5033258989679266</v>
@@ -46907,10 +46907,10 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.018599073782717</v>
+        <v>-4.118724376834206</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8338049667740981</v>
+        <v>0.7937548455535026</v>
       </c>
       <c r="F1972" t="n">
         <v>0.452439186281732</v>
@@ -46930,10 +46930,10 @@
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.93198833113291</v>
+        <v>-4.032113634184399</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8830769999500647</v>
+        <v>0.8430268787294688</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5310649174868902</v>
@@ -46953,10 +46953,10 @@
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.992197629138194</v>
+        <v>-4.092322932189684</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8575292615726227</v>
+        <v>0.8174791403520265</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4708556194816057</v>
@@ -46976,10 +46976,10 @@
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.943010980453843</v>
+        <v>-4.043136283505333</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8756955390862917</v>
+        <v>0.8356454178656958</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4708556194816057</v>
@@ -46999,10 +46999,10 @@
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.898637848815274</v>
+        <v>-3.998763151866764</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8933076591771554</v>
+        <v>0.8532575379565595</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5152287511201743</v>
@@ -47022,10 +47022,10 @@
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.863906527496773</v>
+        <v>-3.964031830548263</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9015939818431462</v>
+        <v>0.8615438606225503</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5152287511201743</v>
@@ -47045,10 +47045,10 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.816250796935718</v>
+        <v>-3.916376099987207</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.927038031095373</v>
+        <v>0.886987909874777</v>
       </c>
       <c r="F1978" t="n">
         <v>0.56288448168123</v>
@@ -47068,10 +47068,10 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.715732638436963</v>
+        <v>-3.815857941488453</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9721376678695997</v>
+        <v>0.9320875466490037</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6634026401799845</v>
@@ -47091,10 +47091,10 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.69982730900461</v>
+        <v>-3.7999526120561</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9652544721184131</v>
+        <v>0.9252043508978169</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5842899794707457</v>
@@ -47114,10 +47114,10 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.654988907396212</v>
+        <v>-3.755114210447702</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9872875353724009</v>
+        <v>0.9472374141518047</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5888334124156152</v>
@@ -47137,10 +47137,10 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.67448736363822</v>
+        <v>-3.77461266668971</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9836490925066754</v>
+        <v>0.9435989712860795</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5407487711357108</v>
@@ -47160,10 +47160,10 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.63028452655232</v>
+        <v>-3.73040982960381</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.007209829868873</v>
+        <v>0.9671597086482768</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5849516082216113</v>
@@ -47183,10 +47183,10 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.637844192389367</v>
+        <v>-3.737969495440857</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.002595964003302</v>
+        <v>0.9625458427827056</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6397550122314306</v>
@@ -47206,10 +47206,10 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.479552774850095</v>
+        <v>-3.579678077901585</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.11716029620205</v>
+        <v>1.077110174981454</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6397550122314306</v>
@@ -47229,10 +47229,10 @@
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.271910771215619</v>
+        <v>-3.372036074267108</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.198657802250094</v>
+        <v>1.158607681029498</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8473970158659068</v>
@@ -47252,10 +47252,10 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.220878678493091</v>
+        <v>-3.32100398154458</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.214018867577375</v>
+        <v>1.173968746356779</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8984291085884347</v>
@@ -47275,10 +47275,10 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.155654497365885</v>
+        <v>-3.255779800417375</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.257295944120962</v>
+        <v>1.217245822900366</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9636532897156403</v>
@@ -47298,10 +47298,10 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.118227477294751</v>
+        <v>-3.218352780346241</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.268227724448696</v>
+        <v>1.2281776032281</v>
       </c>
       <c r="F1989" t="n">
         <v>0.968904827744822</v>
@@ -47321,10 +47321,10 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.116869492321205</v>
+        <v>-3.216994795372695</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.270027710769355</v>
+        <v>1.229977589548759</v>
       </c>
       <c r="F1990" t="n">
         <v>1.043242953282641</v>
@@ -47344,10 +47344,10 @@
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.088456229221322</v>
+        <v>-3.188581532272812</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.441950787030519</v>
+        <v>1.401900665809923</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9842673905362118</v>
@@ -47367,10 +47367,10 @@
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.013673968196309</v>
+        <v>-3.113799271247799</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.591976600658341</v>
+        <v>1.551926479437745</v>
       </c>
       <c r="F1992" t="n">
         <v>1.059049651561224</v>
@@ -47390,10 +47390,10 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.987589883932501</v>
+        <v>-3.087715186983991</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.594118210377723</v>
+        <v>1.554068089157127</v>
       </c>
       <c r="F1993" t="n">
         <v>1.059049651561224</v>
@@ -47413,10 +47413,10 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.899711970823381</v>
+        <v>-2.999837273874871</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.627462571205151</v>
+        <v>1.587412449984555</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174975293984576</v>
@@ -47436,10 +47436,10 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.890819509430098</v>
+        <v>-2.990944812481588</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.648573961489256</v>
+        <v>1.60852384026866</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174975293984576</v>
@@ -47459,10 +47459,10 @@
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.059295626399976</v>
+        <v>-3.159420929451465</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.573038562105888</v>
+        <v>1.532988440885292</v>
       </c>
       <c r="F1996" t="n">
         <v>1.147027458267995</v>
@@ -47482,10 +47482,10 @@
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.613039433770536</v>
+        <v>-2.713164736822026</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.732810736345526</v>
+        <v>1.69276061512493</v>
       </c>
       <c r="F1997" t="n">
         <v>1.052308788598362</v>
@@ -47505,10 +47505,10 @@
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.590318330087383</v>
+        <v>-2.690443633138873</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.732563200315692</v>
+        <v>1.692513079095096</v>
       </c>
       <c r="F1998" t="n">
         <v>1.052308788598362</v>
@@ -47528,10 +47528,10 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.719520143381426</v>
+        <v>-2.819645446432915</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.839788600849244</v>
+        <v>1.799738479628648</v>
       </c>
       <c r="F1999" t="n">
         <v>0.92310697530432</v>
@@ -47551,10 +47551,10 @@
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.745394541855451</v>
+        <v>-2.845519844906941</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.86651666395328</v>
+        <v>1.826466542732684</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9680185840160611</v>
@@ -47574,10 +47574,10 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.738339851640278</v>
+        <v>-2.838465154691768</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.866013896028895</v>
+        <v>1.825963774808299</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9750732742312349</v>
@@ -47597,10 +47597,10 @@
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.71138862731379</v>
+        <v>-2.81151393036528</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.886800539404231</v>
+        <v>1.846750418183635</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9899536202589541</v>
@@ -47620,10 +47620,10 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.732932855144577</v>
+        <v>-2.833058158196067</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.062285980416876</v>
+        <v>2.022235859196281</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9899536202589541</v>
@@ -47643,10 +47643,10 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.755340972949449</v>
+        <v>-2.855466276000939</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.045439428197921</v>
+        <v>2.005389306977325</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9899536202589541</v>
@@ -47666,10 +47666,10 @@
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.783565208527049</v>
+        <v>-2.883690511578539</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.036203733516518</v>
+        <v>1.996153612295922</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007930372710263</v>
@@ -47689,10 +47689,10 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.793006134415579</v>
+        <v>-2.893131437467069</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.088681080882953</v>
+        <v>2.048630959662357</v>
       </c>
       <c r="F2006" t="n">
         <v>1.130357490253654</v>
@@ -47712,10 +47712,10 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.881882765584053</v>
+        <v>-2.982008068635543</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.056021522960864</v>
+        <v>2.015971401740268</v>
       </c>
       <c r="F2007" t="n">
         <v>1.04148085908518</v>
@@ -47735,10 +47735,10 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.958212743184959</v>
+        <v>-3.058338046236449</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.023601344814277</v>
+        <v>1.983551223593681</v>
       </c>
       <c r="F2008" t="n">
         <v>1.04148085908518</v>
@@ -47758,10 +47758,10 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.113169528585088</v>
+        <v>-3.213294831636578</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.956438860257088</v>
+        <v>1.916388739036492</v>
       </c>
       <c r="F2009" t="n">
         <v>0.886524073685051</v>
@@ -47781,10 +47781,10 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.274737954112343</v>
+        <v>-3.374863257163833</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.890245500256338</v>
+        <v>1.850195379035742</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7597411498871717</v>
@@ -47804,10 +47804,10 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.383038615982463</v>
+        <v>-3.483163919033953</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.859998642374209</v>
+        <v>1.819948521153613</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7597411498871717</v>
@@ -47827,10 +47827,10 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.400842587703207</v>
+        <v>-3.500967890754697</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.844882250468851</v>
+        <v>1.804832129248255</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6892065269819705</v>
@@ -47850,10 +47850,10 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.42874337481268</v>
+        <v>-3.52886867786417</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.832245976752064</v>
+        <v>1.792195855531468</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6546096028390357</v>
@@ -47873,10 +47873,10 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.551269477515574</v>
+        <v>-3.651394780567064</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.779999979648105</v>
+        <v>1.739949858427509</v>
       </c>
       <c r="F2014" t="n">
         <v>0.5320835001361418</v>
@@ -47896,10 +47896,10 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.781783973701162</v>
+        <v>-3.881909276752652</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.754500140764374</v>
+        <v>1.714450019543778</v>
       </c>
       <c r="F2015" t="n">
         <v>0.3015690039505531</v>
@@ -47919,10 +47919,10 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.130529058925606</v>
+        <v>-4.230654361977096</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.755313825676443</v>
+        <v>1.715263704455847</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1928210500316553</v>
@@ -47942,10 +47942,10 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.284515476701746</v>
+        <v>-4.384640779753236</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.762699527711627</v>
+        <v>1.722649406491031</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1928210500316553</v>
@@ -47965,10 +47965,10 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.489114911564755</v>
+        <v>-4.589240214616245</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.666910955886544</v>
+        <v>1.626860834665948</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1928210500316553</v>
@@ -47988,10 +47988,10 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.741590065572479</v>
+        <v>-4.841715368623969</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.577791383338868</v>
+        <v>1.537741262118272</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1928210500316553</v>
@@ -48011,10 +48011,10 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.034485822051892</v>
+        <v>-5.134611125103381</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.461843615266047</v>
+        <v>1.421793494045451</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1928210500316553</v>
@@ -48034,10 +48034,10 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.2211499501867</v>
+        <v>-5.32127525323819</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.391299706239446</v>
+        <v>1.35124958501885</v>
       </c>
       <c r="F2021" t="n">
         <v>0.1660820792070954</v>
@@ -48057,10 +48057,10 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.367170637100662</v>
+        <v>-5.467295940152152</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.32796928421005</v>
+        <v>1.287919162989454</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1569989874132384</v>
@@ -48080,10 +48080,10 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.458884646210247</v>
+        <v>-5.559009949261737</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.45348773726526</v>
+        <v>1.413437616044664</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1569989874132384</v>
@@ -48103,10 +48103,10 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.490536305270217</v>
+        <v>-5.590661608321707</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.435673711605086</v>
+        <v>1.39562359038449</v>
       </c>
       <c r="F2024" t="n">
         <v>0.1518305301687982</v>
@@ -48126,10 +48126,10 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.559602359843153</v>
+        <v>-5.659727662894643</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.418276707344403</v>
+        <v>1.378226586123807</v>
       </c>
       <c r="F2025" t="n">
         <v>0.08945965267518818</v>
@@ -48149,10 +48149,10 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.661578482091561</v>
+        <v>-5.761703785143051</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.386411896900942</v>
+        <v>1.346361775680346</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.01251646957321939</v>
@@ -48172,10 +48172,10 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.551572198614339</v>
+        <v>-5.651697501665829</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.422567297536006</v>
+        <v>1.38251717631541</v>
       </c>
       <c r="F2027" t="n">
         <v>0.01068810234405582</v>
@@ -48195,10 +48195,10 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.408512622873413</v>
+        <v>-5.508637925924903</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.484041138554351</v>
+        <v>1.443991017333755</v>
       </c>
       <c r="F2028" t="n">
         <v>0.01870152893403509</v>
@@ -48218,10 +48218,10 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.107065897401576</v>
+        <v>-5.207191200453066</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.611880711625622</v>
+        <v>1.571830590405026</v>
       </c>
       <c r="F2029" t="n">
         <v>0.3201482544058724</v>
@@ -48241,10 +48241,10 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.13165614163676</v>
+        <v>-5.23178144468825</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.603015791684259</v>
+        <v>1.562965670463663</v>
       </c>
       <c r="F2030" t="n">
         <v>0.3201482544058724</v>
@@ -48264,10 +48264,10 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.080617765630239</v>
+        <v>-5.180743068681729</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.624274046466623</v>
+        <v>1.584223925246027</v>
       </c>
       <c r="F2031" t="n">
         <v>0.3201482544058724</v>
@@ -48287,10 +48287,10 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.051769088806779</v>
+        <v>-5.151894391858269</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.654851616070152</v>
+        <v>1.614801494849556</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3489969312293326</v>
@@ -48310,10 +48310,10 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.955134176788139</v>
+        <v>-5.055259479839629</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.509689577001543</v>
+        <v>1.469639455780947</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4456318432479726</v>
@@ -48333,10 +48333,10 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.886096165839671</v>
+        <v>-4.986221468891161</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.540806825454894</v>
+        <v>1.500756704234298</v>
       </c>
       <c r="F2034" t="n">
         <v>0.5146698541964406</v>
@@ -48356,10 +48356,10 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.721599831648709</v>
+        <v>-4.821725134700199</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.591032178207361</v>
+        <v>1.550982056986765</v>
       </c>
       <c r="F2035" t="n">
         <v>0.6791661883874025</v>
@@ -48379,10 +48379,10 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.644501230106837</v>
+        <v>-4.744626533158327</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.62105932926054</v>
+        <v>1.581009208039944</v>
       </c>
       <c r="F2036" t="n">
         <v>0.6791661883874025</v>
@@ -48402,10 +48402,10 @@
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.654886424996726</v>
+        <v>-4.755011728048216</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.626774030429657</v>
+        <v>1.586723909209061</v>
       </c>
       <c r="F2037" t="n">
         <v>0.6687809934975132</v>
@@ -48425,10 +48425,10 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.673474583718951</v>
+        <v>-4.773599886770441</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.690175772717192</v>
+        <v>1.650125651496596</v>
       </c>
       <c r="F2038" t="n">
         <v>0.6501928347752879</v>
@@ -48448,10 +48448,10 @@
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.673773130414987</v>
+        <v>-4.773898433466477</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.686925364857076</v>
+        <v>1.64687524363648</v>
       </c>
       <c r="F2039" t="n">
         <v>0.649894288079252</v>
@@ -48471,10 +48471,10 @@
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.572949996724559</v>
+        <v>-4.673075299776049</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.731785513272639</v>
+        <v>1.691735392052043</v>
       </c>
       <c r="F2040" t="n">
         <v>0.6623585035636058</v>
@@ -48494,10 +48494,10 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.382168635972151</v>
+        <v>-4.482293939023641</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.808227311052145</v>
+        <v>1.768177189831549</v>
       </c>
       <c r="F2041" t="n">
         <v>0.8531398643160132</v>
@@ -48517,10 +48517,10 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.27520527812273</v>
+        <v>-4.37533058117422</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.83084949992951</v>
+        <v>1.790799378708914</v>
       </c>
       <c r="F2042" t="n">
         <v>0.9116044722758146</v>
@@ -48540,10 +48540,10 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.219874690220967</v>
+        <v>-4.319999993272457</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.887948671702274</v>
+        <v>1.847898550481678</v>
       </c>
       <c r="F2043" t="n">
         <v>0.9669350601775768</v>
@@ -48563,10 +48563,10 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.207820563308005</v>
+        <v>-4.307945866359495</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.886456890368897</v>
+        <v>1.846406769148301</v>
       </c>
       <c r="F2044" t="n">
         <v>0.9789891870905396</v>
@@ -48586,10 +48586,10 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.248975682876226</v>
+        <v>-4.349100985927715</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.871875472725744</v>
+        <v>1.831825351505148</v>
       </c>
       <c r="F2045" t="n">
         <v>0.9378340675223187</v>
@@ -48609,10 +48609,10 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.180927120184696</v>
+        <v>-4.281052423236186</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.911945923680238</v>
+        <v>1.871895802459642</v>
       </c>
       <c r="F2046" t="n">
         <v>1.005882630213848</v>
@@ -48632,10 +48632,10 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.412527513354196</v>
+        <v>-4.512652816405686</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.839508436586032</v>
+        <v>1.799458315365436</v>
       </c>
       <c r="F2047" t="n">
         <v>1.005882630213848</v>
@@ -48655,10 +48655,10 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.462579058883415</v>
+        <v>-4.562704361934905</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.803094054441227</v>
+        <v>1.763043933220631</v>
       </c>
       <c r="F2048" t="n">
         <v>1.005882630213848</v>
@@ -48678,10 +48678,10 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.63768589145986</v>
+        <v>-4.73781119451135</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.693303235004116</v>
+        <v>1.65325311378352</v>
       </c>
       <c r="F2049" t="n">
         <v>1.005882630213848</v>
@@ -48701,10 +48701,10 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.441585738029337</v>
+        <v>-4.541711041080827</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.778765915373265</v>
+        <v>1.738715794152669</v>
       </c>
       <c r="F2050" t="n">
         <v>1.201982783644371</v>
@@ -48724,10 +48724,10 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.288560345916053</v>
+        <v>-4.388685648967543</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.939147071791483</v>
+        <v>1.899096950570887</v>
       </c>
       <c r="F2051" t="n">
         <v>1.355008175757655</v>
@@ -48747,10 +48747,10 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.316867659789323</v>
+        <v>-4.416992962840813</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.115290371150468</v>
+        <v>2.075240249929871</v>
       </c>
       <c r="F2052" t="n">
         <v>1.355008175757655</v>
@@ -48770,10 +48770,10 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.483460884902845</v>
+        <v>-4.583586187954335</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.018056032459141</v>
+        <v>1.978005911238545</v>
       </c>
       <c r="F2053" t="n">
         <v>1.188414950644133</v>
@@ -48793,10 +48793,10 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.460425091541279</v>
+        <v>-4.560550394592769</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.030946752465485</v>
+        <v>1.990896631244889</v>
       </c>
       <c r="F2054" t="n">
         <v>1.188414950644133</v>
@@ -48816,10 +48816,10 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.431179111085583</v>
+        <v>-4.531304414137073</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.040263199771259</v>
+        <v>2.000213078550663</v>
       </c>
       <c r="F2055" t="n">
         <v>1.188414950644133</v>
@@ -48839,10 +48839,10 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.538104658963434</v>
+        <v>-4.638229962014924</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.994786219777754</v>
+        <v>1.954736098557158</v>
       </c>
       <c r="F2056" t="n">
         <v>1.081489402766282</v>
@@ -48862,10 +48862,10 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.683123217470682</v>
+        <v>-4.783248520522172</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.938207598518089</v>
+        <v>1.898157477297493</v>
       </c>
       <c r="F2057" t="n">
         <v>0.936470844259033</v>
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.8014649832554</v>
+        <v>-4.876527922720239</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.990802131461955</v>
+        <v>1.960776955676019</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9471568828219231</v>
+        <v>0.9472559297650114</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.480038678771017</v>
+        <v>4.48009810693687</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.852875405576108</v>
+        <v>-4.927938345040947</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.96802365965961</v>
+        <v>1.937998483873675</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9471568828219231</v>
+        <v>0.9472559297650114</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.477824375896955</v>
+        <v>4.477883804062809</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.93229485678386</v>
+        <v>-5.007357796248699</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.936159007250799</v>
+        <v>1.906133831464863</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9471568828219231</v>
+        <v>0.9472559297650114</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.477727503971245</v>
+        <v>4.477786932137098</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.027757854701077</v>
+        <v>-5.102820794165916</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.897967701641955</v>
+        <v>1.867942525856019</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9471568828219231</v>
+        <v>0.9472559297650114</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.477721397529288</v>
+        <v>4.477780825695141</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.963381943850362</v>
+        <v>-5.038444883315202</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.921814462544852</v>
+        <v>1.891789286758916</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.011532793672638</v>
+        <v>1.011631840615727</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.514443340602328</v>
+        <v>4.51450276876818</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.018751105982556</v>
+        <v>-5.093814045447395</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.905400615439701</v>
+        <v>1.875375439653765</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.011532793672638</v>
+        <v>1.011631840615727</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.520177158350054</v>
+        <v>4.520236586515907</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.036969572980165</v>
+        <v>-5.112032512445004</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.897651591983589</v>
+        <v>1.867626416197654</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.986426356416796</v>
+        <v>0.9865254033598844</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.504651659339482</v>
+        <v>4.504711087505334</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.948762738832587</v>
+        <v>-5.023825678297426</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.952808718492939</v>
+        <v>1.922783542707004</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.986426356416796</v>
+        <v>0.9865254033598844</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.5245260521898</v>
+        <v>4.524585480355653</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.842727743627277</v>
+        <v>-4.917790683092116</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.978923417099791</v>
+        <v>1.948898241313855</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.986426356416796</v>
+        <v>0.9865254033598844</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.508226752714528</v>
+        <v>4.508286180880381</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.659516080494182</v>
+        <v>-4.734579019959021</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.054639031817075</v>
+        <v>2.024613856031139</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.986426356416796</v>
+        <v>0.9865254033598844</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.510657702178573</v>
+        <v>4.510717130344426</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.587794633480331</v>
+        <v>-4.66285757294517</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.066272016701992</v>
+        <v>2.036246840916056</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.058147803430647</v>
+        <v>1.058246850373735</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.536634976466261</v>
+        <v>4.536694404632113</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.565421607872625</v>
+        <v>-4.640484547337464</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.022136972866246</v>
+        <v>1.992111797080311</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.069403554543548</v>
+        <v>1.069502601486636</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.490304173055174</v>
+        <v>4.490363601221026</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.59843790378337</v>
+        <v>-4.673500843248209</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.194128659387304</v>
+        <v>2.164103483601368</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9999661778767968</v>
+        <v>1.000065224819885</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.633839951940478</v>
+        <v>4.633899380106331</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.586910268133761</v>
+        <v>-4.6619732075986</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.190660939475396</v>
+        <v>2.160635763689461</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.058966836078159</v>
+        <v>1.059065883021247</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.661161572689545</v>
+        <v>4.661221000855397</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.68425176947613</v>
+        <v>-4.759314708940969</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.155392451460237</v>
+        <v>2.125367275674302</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.014546653912671</v>
+        <v>1.014645700855759</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.63817757591204</v>
+        <v>4.638237004077893</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.770107798816096</v>
+        <v>-4.845170738280935</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.122301121917089</v>
+        <v>2.092275946131153</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9721705846865358</v>
+        <v>0.972269631629624</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.614003016569197</v>
+        <v>4.61406244473505</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.778944596232216</v>
+        <v>-4.854007535697055</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.101185604771143</v>
+        <v>2.071160428985207</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9647284120451851</v>
+        <v>0.9648274589882733</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.591956914804888</v>
+        <v>4.592016342970742</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.870327158797674</v>
+        <v>-4.945390098262513</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.074797090790009</v>
+        <v>2.044771915004073</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9281635273258404</v>
+        <v>0.9282625742689286</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.580182495018331</v>
+        <v>4.580241923184184</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.858620440810668</v>
+        <v>-4.933683380275507</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.18160803580908</v>
+        <v>2.151582860023144</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.9398702453128468</v>
+        <v>0.939969292255935</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.689334783634803</v>
+        <v>4.689394211800656</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.929532514552946</v>
+        <v>-5.004595454017785</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.156275545043573</v>
+        <v>2.126250369257638</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.9398702453128468</v>
+        <v>0.939969292255935</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.692367122366208</v>
+        <v>4.692426550532061</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.939848612719298</v>
+        <v>-5.014911552184137</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.365053939055091</v>
+        <v>2.335028763269155</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.9398702453128468</v>
+        <v>0.939969292255935</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.905271955644266</v>
+        <v>4.905331383810119</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.939754644701925</v>
+        <v>-5.014817584166765</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.364270193174129</v>
+        <v>2.334245017388194</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.904672539364746</v>
+        <v>4.9047319675306</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.08812087235807</v>
+        <v>-5.163183811822909</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.299155688056025</v>
+        <v>2.26913051227009</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.8989045253091</v>
+        <v>4.898963953474953</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.087172449240032</v>
+        <v>-5.162235388704871</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.29953505730324</v>
+        <v>2.269509881517305</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.8989045253091</v>
+        <v>4.898963953474953</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.187442267199053</v>
+        <v>-5.262505206663892</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.272154738100724</v>
+        <v>2.242129562314788</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.911632133290192</v>
+        <v>4.911691561456045</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.181450020410241</v>
+        <v>-5.256512959875081</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.276497635240637</v>
+        <v>2.246472459454701</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.91357813171458</v>
+        <v>4.913637559880433</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.092892059279474</v>
+        <v>-5.167954998744313</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.305574955710712</v>
+        <v>2.275549779924777</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.907232267732349</v>
+        <v>4.907291695898202</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.0751329817764</v>
+        <v>-5.150195921241239</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.311987264150938</v>
+        <v>2.281962088365002</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.9403391536032529</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.906540945171344</v>
+        <v>4.906600373337198</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.975502830727332</v>
+        <v>-5.050565770192171</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.364621510479152</v>
+        <v>2.334596334693216</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.039870257709232</v>
+        <v>1.03996930465232</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.979101221709372</v>
+        <v>4.979160649875225</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.024902339416343</v>
+        <v>-5.099965278881182</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.534015972502274</v>
+        <v>2.503990796716338</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.050129091140977</v>
+        <v>1.050228138084065</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.174410787267146</v>
+        <v>5.174470215432998</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.818217865773967</v>
+        <v>-4.893280805238806</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.603878435062086</v>
+        <v>2.57385325927615</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.256813564783353</v>
+        <v>1.256912611726441</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.285610144555433</v>
+        <v>5.285669572721286</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.740284389162541</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.852374760771493</v>
+        <v>-4.927437700236332</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.59221719071718</v>
+        <v>2.562192014931245</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.17322979524254</v>
+        <v>1.173328842185628</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.237461396485051</v>
+        <v>5.237520824650903</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.759785281710037</v>
+        <v>-4.834848221174876</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.982750096331431</v>
+        <v>2.952724920545495</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.17322979524254</v>
+        <v>1.173328842185628</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.590958510474717</v>
+        <v>5.591017938640571</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.819673909533587</v>
+        <v>-4.894736848998426</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.963357756769113</v>
+        <v>2.933332580983178</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.159107880555076</v>
+        <v>1.159206927498164</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.587048473229342</v>
+        <v>5.587107901395195</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.767457599737245</v>
+        <v>-4.842520539202084</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.034074222011178</v>
+        <v>3.004049046225242</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.159107880555076</v>
+        <v>1.159206927498164</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.63687841455287</v>
+        <v>5.636937842718723</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.735560082651999</v>
+        <v>-4.810623022116839</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.055647199055287</v>
+        <v>3.025622023269351</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.191005397640321</v>
+        <v>1.19110444458341</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.664830895014028</v>
+        <v>5.664890323179881</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.75031540685214</v>
+        <v>-4.825378346316979</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.045382653414427</v>
+        <v>3.015357477628492</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.191005397640321</v>
+        <v>1.19110444458341</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.660468479053224</v>
+        <v>5.660527907219078</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.700850783482228</v>
+        <v>-4.775913722947068</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.056093006178672</v>
+        <v>3.026067830392737</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.240470021010233</v>
+        <v>1.240569067953321</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.681071756491452</v>
+        <v>5.681131184657304</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.537742791328613</v>
+        <v>-4.612805730793452</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.117743870755053</v>
+        <v>3.087718694969118</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.403578013163848</v>
+        <v>1.403677060106936</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.775344219498555</v>
+        <v>5.775403647664408</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.404935165831446</v>
+        <v>-4.479998105296286</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.179913957645048</v>
+        <v>3.149888781859112</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.403578013163848</v>
+        <v>1.403677060106936</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.784391256189684</v>
+        <v>5.784450684355536</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.467643082306004</v>
+        <v>-4.542706021770844</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.155688256041346</v>
+        <v>3.125663080255411</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.340870096689291</v>
+        <v>1.340969143632379</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.747623971291071</v>
+        <v>5.747683399456923</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.419634958462312</v>
+        <v>-4.494697897927151</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.137800922369175</v>
+        <v>3.10777574658324</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.340870096689291</v>
+        <v>1.340969143632379</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.710533388081423</v>
+        <v>5.710592816247275</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.340809301278721</v>
+        <v>-4.41587224074356</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.173263438800562</v>
+        <v>3.143238263014626</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.419695753872881</v>
+        <v>1.419794800815969</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.761761035949528</v>
+        <v>5.76182046411538</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,45 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.877919040828481</v>
+        <v>3.868502531686403</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.148874500024847</v>
+        <v>-4.223937439489687</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.244936451909148</v>
+        <v>3.214911276123213</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.419695753872881</v>
+        <v>1.419794800815969</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.756660128556565</v>
+        <v>5.756719556722417</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="2" t="n">
+        <v>45564</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>3.82684194890652</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>4.87140640678826</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>-4.223937439489687</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>3.214911276123213</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>1.419794800815969</v>
+      </c>
+      <c r="G2102" t="n">
+        <v>4.864470203774628</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240929.xlsx
+++ b/tame_output/ON/bt/strategyON_20240929.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>60.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>112.0%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>175.5%</t>
+          <t>178.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.4%</t>
+          <t>122.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.5%</t>
+          <t>421.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-584.0%</t>
+          <t>-601.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-54.7%</t>
+          <t>-61.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-301.9%</t>
+          <t>-82.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-82.0%</t>
+          <t>-90.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176056899127509</v>
+        <v>-8.257130876618868</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1388658451497196</v>
+        <v>-0.1712954361462629</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.005067935285861</v>
+        <v>-1.08614191277722</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.528872577643516</v>
+        <v>2.480228191148701</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230128398635868</v>
+        <v>-8.311202376127227</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1576008886314906</v>
+        <v>-0.1900304796280343</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.059139434794221</v>
+        <v>-1.14021341228558</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.499323234260073</v>
+        <v>2.450678847765257</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.233704184727616</v>
+        <v>-8.314778162218975</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1535180059495476</v>
+        <v>-0.1859475969460909</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.084668356710713</v>
+        <v>-1.165742334202072</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.489519078228819</v>
+        <v>2.440874691734004</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.267357023236089</v>
+        <v>-8.348431000727448</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1624965868685009</v>
+        <v>-0.1949261778650442</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.185081724627751</v>
+        <v>-1.266155702119109</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.433753611963033</v>
+        <v>2.385109225468218</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.487517115346305</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>-0.2351889222191659</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.324167839246607</v>
+        <v>-1.405241816737966</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.36567364468514</v>
+        <v>2.317029258190325</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.662641532732849</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>-0.2906834684262667</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.58036623412451</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.275154215000731</v>
+        <v>2.226509828505915</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.897093626747338</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.3916834709336583</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.58036623412451</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.267935050099135</v>
+        <v>2.219290663604319</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.920394380282426</v>
+        <v>-9.001468357773785</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.4401055541182131</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.603666987659597</v>
+        <v>-1.684740965150956</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.198638020709291</v>
+        <v>2.149993634214475</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08290784598101</v>
+        <v>-9.163981823472369</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.5039951505590907</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.701300418078284</v>
+        <v>-1.782374395569643</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.141173752296635</v>
+        <v>2.09252936580182</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.2089446393493</v>
+        <v>-9.290018616840658</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.5517161392772918</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.7571227727599</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.159018454611595</v>
+        <v>2.11037406811678</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.151872867453369</v>
+        <v>-9.232946844944728</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.5248970948325185</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.7571227727599</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.163008790297996</v>
+        <v>2.11436440380318</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.293544709177489</v>
+        <v>-9.374618686668848</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.5830410584209083</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.7571227727599</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.161533563399254</v>
+        <v>2.112889176904439</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.243953864752655</v>
+        <v>-9.325027842244014</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.5481513104861024</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.626457950843708</v>
+        <v>-1.707531928335067</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.206341480219027</v>
+        <v>2.157697093724211</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.095035530280798</v>
+        <v>-9.176109507772157</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.5016351103440426</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.595208360108535</v>
+        <v>-1.676282337599893</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.212040101013448</v>
+        <v>2.163395714518632</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-8.950264355052747</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.4017179762200702</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.63435566201273</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.246775179401955</v>
+        <v>2.198130792907139</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.825685698715155</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.3507473691289742</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.63435566201273</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.247914323958013</v>
+        <v>2.199269937463198</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.800649017146645</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.3380989223394626</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.609026574461994</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.265745550650562</v>
+        <v>2.217101164155747</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.728515841858764</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.3035119479856738</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.609026574461994</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.271479254889199</v>
+        <v>2.222834868394384</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.644238203941597</v>
+        <v>-8.725312181432958</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2795381552126726</v>
+        <v>-0.3119677462092167</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.605822914036188</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.263664188750818</v>
+        <v>2.215019802256002</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.550779169956373</v>
+        <v>-8.631853147447734</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2520380229314902</v>
+        <v>-0.2844676139280344</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.605822914036188</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.25378070743791</v>
+        <v>2.205136320943095</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.540125988402941</v>
+        <v>-8.621199965894302</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2496113108094913</v>
+        <v>-0.2820409018060355</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.605822914036188</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.251946146938536</v>
+        <v>2.203301760443721</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.442218949726451</v>
+        <v>-8.523292927217812</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.210748810312356</v>
+        <v>-0.2431784013089002</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.456763186684273</v>
+        <v>-1.537837164175631</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.292437281881409</v>
+        <v>2.243792895386594</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.418265408750493</v>
+        <v>-8.499339386241854</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2004988877764791</v>
+        <v>-0.2329284787730233</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.432809645708315</v>
+        <v>-1.513883623199674</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.307477912612478</v>
+        <v>2.258833526117662</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.154205470427696</v>
+        <v>-8.235279447919057</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1081352286091124</v>
+        <v>-0.1405648196056566</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.168749707385519</v>
+        <v>-1.249823684876878</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.452653559444403</v>
+        <v>2.404009172949588</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.447125846922858</v>
+        <v>-7.528199824414219</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.171909587132522</v>
+        <v>0.1394799961359778</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.168749707385519</v>
+        <v>-1.249823684876878</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.449866525784102</v>
+        <v>2.401222139289287</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.406941548556667</v>
+        <v>-7.488015526048028</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1883269303668396</v>
+        <v>0.1558973393702954</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.128565409019328</v>
+        <v>-1.209639386510687</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.474320728691658</v>
+        <v>2.425676342196843</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.243541677617305</v>
+        <v>-7.324615655108666</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2530536999633415</v>
+        <v>0.2206241089667973</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9651655380799653</v>
+        <v>-1.046239515571324</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.571727472476033</v>
+        <v>2.523083085981217</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.08542429823853</v>
+        <v>-7.16649827572989</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3242250805527038</v>
+        <v>0.2917954895561596</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8070481587011898</v>
+        <v>-0.8881221361925488</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.67452232894115</v>
+        <v>2.625877942446335</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.935757907231014</v>
+        <v>-7.016831884722375</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.381199426642751</v>
+        <v>0.3487698356462063</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7141446674586539</v>
+        <v>-0.7952186449500128</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.727372213373712</v>
+        <v>2.678727826878897</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.803482433600128</v>
+        <v>-6.884556411091489</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3353704021022601</v>
+        <v>0.3029408111057159</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5818691938277673</v>
+        <v>-0.6629431713191262</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.707998283559399</v>
+        <v>2.659353897064584</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.631621218035225</v>
+        <v>-6.712695195526586</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4069299490158578</v>
+        <v>0.3745003580193136</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4100079782628644</v>
+        <v>-0.4910819557542233</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.813930073585978</v>
+        <v>2.765285687091162</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.546656551305906</v>
+        <v>-6.627730528797267</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4538221569312442</v>
+        <v>0.4213925659347</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3250433115335448</v>
+        <v>-0.4061172890249037</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.877815214847228</v>
+        <v>2.829170828352413</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.652246541079011</v>
+        <v>-6.733320518570372</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2836102314227835</v>
+        <v>0.2511806404262393</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4306333013066492</v>
+        <v>-0.5117072787980081</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.686485291384147</v>
+        <v>2.637840904889332</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.584011956453583</v>
+        <v>-6.665085933944944</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3594484071500412</v>
+        <v>0.3270188161534966</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4122179784341132</v>
+        <v>-0.4932919559254721</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.746078826984755</v>
+        <v>2.69743444048994</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.436071915045984</v>
+        <v>-6.517145892537345</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3020036150746739</v>
+        <v>0.2695740240781292</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3918970625255556</v>
+        <v>-0.4729710400169146</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.641650567891482</v>
+        <v>2.593006181396667</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.383102392791995</v>
+        <v>-6.464176370283356</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.314477437722791</v>
+        <v>0.2820478467262468</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.4200015177629257</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.664718294990398</v>
+        <v>2.616073908495582</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.217314196831705</v>
+        <v>-6.298388174323065</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.373832104011814</v>
+        <v>0.3414025130152698</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.4200015177629257</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.657757682895304</v>
+        <v>2.609113296400489</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.183950990352936</v>
+        <v>-6.265024967844297</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4016397409844648</v>
+        <v>0.3692101499879206</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.4200015177629257</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.672220037276448</v>
+        <v>2.623575650781632</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.075691853230414</v>
+        <v>-6.156765830721775</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4394755162926685</v>
+        <v>0.4070459252961243</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.4200015177629257</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.666752157735643</v>
+        <v>2.618107771240827</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.952400718413283</v>
+        <v>-6.033474695904644</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4862900642300976</v>
+        <v>0.4538604732335534</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2156364054544362</v>
+        <v>-0.2967103829457952</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.738224932636498</v>
+        <v>2.689580546141682</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.899703851281992</v>
+        <v>-5.980777828773353</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5150697893199392</v>
+        <v>0.482640198323395</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1629395383231451</v>
+        <v>-0.244013515814504</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.777544031152598</v>
+        <v>2.728899644657782</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.655938409298548</v>
+        <v>-5.737012386789909</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6083566744603677</v>
+        <v>0.5759270834638235</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1629395383231451</v>
+        <v>-0.244013515814504</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.773324739499648</v>
+        <v>2.724680353004833</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.566162736922076</v>
+        <v>-5.647236714413436</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6463912573309725</v>
+        <v>0.6139616663344283</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.182414070900194</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.81240872036825</v>
+        <v>2.763764333873435</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.316312342973001</v>
+        <v>-5.397386320464362</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7390734898943045</v>
+        <v>0.7066438988977604</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.182414070900194</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.805150795351952</v>
+        <v>2.756506408857137</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.140420250505569</v>
+        <v>-5.22149422799693</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8130294504019262</v>
+        <v>0.780599859405382</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.182414070900194</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.808749918872601</v>
+        <v>2.760105532377786</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.968973787483105</v>
+        <v>-5.050047764974466</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8949355416654652</v>
+        <v>0.862505950668921</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.07010636961362809</v>
+        <v>-0.01096760787773088</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.924945302740633</v>
+        <v>2.876300916245817</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.888951500373985</v>
+        <v>-4.970025477865345</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9259649341254106</v>
+        <v>0.8935353431288664</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1501286567227491</v>
+        <v>0.06905467923139008</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.971979152622402</v>
+        <v>2.923334766127587</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.82531575814005</v>
+        <v>-4.906389735631411</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9561140320733017</v>
+        <v>0.9236844410767575</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2137643989566836</v>
+        <v>0.1326904214653246</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.01485539901708</v>
+        <v>2.966211012522265</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.731618439923655</v>
+        <v>-4.812692417415016</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9747872181436554</v>
+        <v>0.942357627147111</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2137643989566836</v>
+        <v>0.1326904214653246</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.996049657800876</v>
+        <v>2.947405271306061</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.742121062988944</v>
+        <v>-4.823195040480305</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9723292455424173</v>
+        <v>0.9398996545458729</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2032617758913947</v>
+        <v>0.1221877984000357</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.99149116058658</v>
+        <v>2.942846774091764</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.629634802320069</v>
+        <v>-4.71070877981143</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.021253063644787</v>
+        <v>0.988823472648243</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2032617758913947</v>
+        <v>0.1221877984000357</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.9954204744214</v>
+        <v>2.946776087926585</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.611921115442204</v>
+        <v>-4.692995092933565</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.029017122313273</v>
+        <v>0.9965875313167292</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.1253691272969525</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.99800785567689</v>
+        <v>2.949363469182075</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.488446844129186</v>
+        <v>-4.569520821620547</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.075404902058474</v>
+        <v>1.04297531106193</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.1253691272969525</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.995005926896884</v>
+        <v>2.946361540402068</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.43051101213097</v>
+        <v>-4.511584989622331</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.100158271868374</v>
+        <v>1.06772868087183</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.1509310019797018</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.011922088717147</v>
+        <v>2.963277702222332</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.397768626119182</v>
+        <v>-4.378717300559053</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.129149409074913</v>
+        <v>1.136769939298965</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2320049794710608</v>
+        <v>0.1509310019797018</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.02781627151897</v>
+        <v>2.979171885024155</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.277595542754683</v>
+        <v>-4.258544217194554</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.178364486861015</v>
+        <v>1.185985017085066</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3521780628355597</v>
+        <v>0.2711040853442008</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.101065965977972</v>
+        <v>3.052421579483156</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.142342181424706</v>
+        <v>-4.123290855864577</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.242553933954445</v>
+        <v>1.250174464178497</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4874314241655369</v>
+        <v>0.4063574466741779</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.192306085337398</v>
+        <v>3.143661698842583</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.202217008782398</v>
+        <v>-4.18316568322227</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.204641494412794</v>
+        <v>1.212262024636846</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.3464826193164858</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.142418680324209</v>
+        <v>3.093774293829393</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.082396777871561</v>
+        <v>-4.063345452311433</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.267858756011337</v>
+        <v>1.275479286235389</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4275565968078447</v>
+        <v>0.3464826193164858</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.157707849558417</v>
+        <v>3.109063463063602</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.084866484333367</v>
+        <v>-4.065815158773239</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.174515072749057</v>
+        <v>1.182135602973108</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4250868903460386</v>
+        <v>0.3440129128546796</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.063870225003775</v>
+        <v>3.01522583850896</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.153236670657377</v>
+        <v>-4.134185345097249</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.066428859704754</v>
+        <v>1.074049389928805</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.3532886118908946</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.988697505910805</v>
+        <v>2.94005311941599</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.265108950283528</v>
+        <v>-4.2460576247234</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.012116656486185</v>
+        <v>1.019737186710236</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.3532886118908946</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.979134214542697</v>
+        <v>2.930489828047881</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.24913428479726</v>
+        <v>-4.230082959237132</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9850810476047196</v>
+        <v>0.9927015778287709</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.3532886118908946</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.945708739466724</v>
+        <v>2.897064352971908</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.073660025004791</v>
+        <v>-4.054608699444662</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.059837983513495</v>
+        <v>1.067458513737547</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.3532886118908946</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.950275971458512</v>
+        <v>2.901631584963696</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.065735650419877</v>
+        <v>-4.046684324859748</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.038749762108668</v>
+        <v>1.046370292332719</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4343625893822535</v>
+        <v>0.3532886118908946</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.926018000219719</v>
+        <v>2.877373613724903</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.059457447850028</v>
+        <v>-4.040406122289899</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9697993565380569</v>
+        <v>0.9774198867621087</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.3595668144607436</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.858323235163078</v>
+        <v>2.809678848668263</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.999604828646305</v>
+        <v>-3.980553503086176</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.003912790651678</v>
+        <v>1.01153332087573</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.3595668144607436</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.86849562159521</v>
+        <v>2.819851235100395</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.913361365619927</v>
+        <v>-3.894310040059798</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.03335644643609</v>
+        <v>1.040976976660142</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4406407919521026</v>
+        <v>0.3595668144607436</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.863441892169071</v>
+        <v>2.814797505674255</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.958668185018907</v>
+        <v>-3.939616859458778</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.007009494121024</v>
+        <v>1.014630024345075</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.3187566514515128</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.830731569808058</v>
+        <v>2.782087183313243</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.987701289721209</v>
+        <v>-3.96864996416108</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9959481252732045</v>
+        <v>1.003568655497256</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3998306289428718</v>
+        <v>0.3187566514515128</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.831283442841159</v>
+        <v>2.782639056346344</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.89489080827035</v>
+        <v>-3.87583948271022</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9623450097449138</v>
+        <v>0.9699655399689655</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4926411103937312</v>
+        <v>0.4115671329023722</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.816242423603041</v>
+        <v>2.767598037108225</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.939280277599777</v>
+        <v>-3.920228952039648</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9464626979377437</v>
+        <v>0.9540832281617955</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4482516410643035</v>
+        <v>0.3671776635729445</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.791482217929985</v>
+        <v>2.742837831435169</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.91877658371428</v>
+        <v>-3.899725258154151</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9497398840036655</v>
+        <v>0.9573604142277172</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.3876813574584418</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.798860142773006</v>
+        <v>2.750215756278191</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.002448680426612</v>
+        <v>-3.983397354866482</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9217623411494</v>
+        <v>0.9293828713734518</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4687553349498008</v>
+        <v>0.3876813574584418</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.804351438603673</v>
+        <v>2.755707052108858</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.030229078327965</v>
+        <v>-4.011177752767836</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9221473837573979</v>
+        <v>0.9297679139814496</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4409749370484478</v>
+        <v>0.3599009595570888</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.799180401631401</v>
+        <v>2.750536015136585</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.148609751058103</v>
+        <v>-4.129558425497974</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7131508346659958</v>
+        <v>0.7207713648900476</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.2926831074061126</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.597205410341468</v>
+        <v>2.548561023846653</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.257223829501434</v>
+        <v>-4.238172503941305</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7898548640078689</v>
+        <v>0.7974753942319206</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.2926831074061126</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.717355071060674</v>
+        <v>2.668710684565859</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.221814791253292</v>
+        <v>-4.202763465693162</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8185315054094491</v>
+        <v>0.8261520356335008</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3737570848974716</v>
+        <v>0.2926831074061126</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.731868097162997</v>
+        <v>2.683223710668182</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.230275959908752</v>
+        <v>-4.211224634348623</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8125664792896334</v>
+        <v>0.8201870095136852</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.2842219387506515</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.724210837312089</v>
+        <v>2.675566450817274</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.053159629873586</v>
+        <v>-4.034108304313457</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8801420401490023</v>
+        <v>0.8877625703730541</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3652959162420105</v>
+        <v>0.2842219387506515</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.720939866157391</v>
+        <v>2.672295479662576</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.098251874707132</v>
+        <v>-4.079200549147003</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.862788533977497</v>
+        <v>0.8704090642015487</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3033998730726207</v>
+        <v>0.2223258955812618</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.684485632017671</v>
+        <v>2.635841245522855</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.918876453468364</v>
+        <v>-3.899825127908235</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9283256777794184</v>
+        <v>0.9359462080034702</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4601766312433394</v>
+        <v>0.3791026537519804</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.772338662226516</v>
+        <v>2.723694275731701</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.96389066698897</v>
+        <v>-3.944839341428841</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8911274477027658</v>
+        <v>0.8987479779268175</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4298277359287348</v>
+        <v>0.3487537584373758</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.734936780369343</v>
+        <v>2.686292393874528</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.051901853547667</v>
+        <v>-4.032850527987538</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8616145354182327</v>
+        <v>0.8692350656422845</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3643512280695618</v>
+        <v>0.2832772505782029</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.701342437992785</v>
+        <v>2.652698051497969</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.15309963498484</v>
+        <v>-4.134048309424711</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8203393447398653</v>
+        <v>0.8279598749639168</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.2148684370328837</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.659501071762095</v>
+        <v>2.610856685267279</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.146588668370527</v>
+        <v>-4.127537342810398</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.820543692939907</v>
+        <v>0.8281642231639585</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2959424145242426</v>
+        <v>0.2148684370328837</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.657101033316412</v>
+        <v>2.608456646821596</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.12755054066323</v>
+        <v>-4.108499215103101</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8246836632310708</v>
+        <v>0.8323041934551225</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.1566848257016891</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.61871558572594</v>
+        <v>2.570071199231124</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.18006634293805</v>
+        <v>-4.161015017377921</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9229717439553329</v>
+        <v>0.9305922741793846</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2377588031930481</v>
+        <v>0.1566848257016891</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.73800998736013</v>
+        <v>2.689365600865315</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.18347465437263</v>
+        <v>-4.164423328812501</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9224417483676346</v>
+        <v>0.9300622785916863</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.1892013947110665</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.75835325775189</v>
+        <v>2.709708871257075</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.164118518478783</v>
+        <v>-4.145067192918654</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9361927331220996</v>
+        <v>0.9438132633461511</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2702753722024255</v>
+        <v>0.1892013947110665</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.764361788148816</v>
+        <v>2.715717401654001</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.237448047216875</v>
+        <v>-4.218396721656746</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8048111429040619</v>
+        <v>0.8124316731281136</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.1895960571306884</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.662548806877789</v>
+        <v>2.613904420382974</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.321269268491574</v>
+        <v>-4.302217942931445</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7740762759256636</v>
+        <v>0.7816968061497152</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2706700346220474</v>
+        <v>0.1895960571306884</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.66534242840927</v>
+        <v>2.616698041914455</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.315116562438789</v>
+        <v>-4.29606523687866</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7771997067384357</v>
+        <v>0.7848202369624873</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2768227406748317</v>
+        <v>0.1957487631834727</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.669696400432599</v>
+        <v>2.621052013937784</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.331925860589291</v>
+        <v>-4.312874535029162</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7695564642183452</v>
+        <v>0.7771769944423967</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2600134425243301</v>
+        <v>0.1789394650329711</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.658691298282408</v>
+        <v>2.610046911787593</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.269627861813169</v>
+        <v>-4.25057653625304</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8608112175256148</v>
+        <v>0.8684317477496666</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3053077067987721</v>
+        <v>0.2242337293074131</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.752203410643894</v>
+        <v>2.703559024149079</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.067837664148011</v>
+        <v>-4.048786338587882</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7438192983058052</v>
+        <v>0.7514398285298569</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5033258989679266</v>
+        <v>0.4222519214765675</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.673306327659514</v>
+        <v>2.624661941164698</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.118724376834206</v>
+        <v>-4.099673051274077</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7937548455535026</v>
+        <v>0.8013753757775541</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.452439186281732</v>
+        <v>0.371365208790373</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.713064532369972</v>
+        <v>2.664420145875157</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319539</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.032113634184399</v>
+        <v>-4.01306230862427</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8430268787294688</v>
+        <v>0.8506474089535205</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5310649174868902</v>
+        <v>0.4499909399955312</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.774867707209111</v>
+        <v>2.726223320714296</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.092322932189684</v>
+        <v>-4.073271606629555</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8174791403520265</v>
+        <v>0.8250996705760782</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.3897816419902467</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.737278109230612</v>
+        <v>2.688633722735796</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.043136283505333</v>
+        <v>-4.024084957945203</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8356454178656958</v>
+        <v>0.8432659480897473</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4708556194816057</v>
+        <v>0.3897816419902467</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.735769727270541</v>
+        <v>2.687125340775725</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.998763151866764</v>
+        <v>-3.979711826306635</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8532575379565595</v>
+        <v>0.860878068180611</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.4341547736288153</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.762256473689118</v>
+        <v>2.713612087194302</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.964031830548263</v>
+        <v>-3.944980504988134</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8615438606225503</v>
+        <v>0.869164390846602</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5152287511201743</v>
+        <v>0.4341547736288153</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.756650267827708</v>
+        <v>2.708005881332893</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.916376099987207</v>
+        <v>-3.897324774427078</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.886987909874777</v>
+        <v>0.8946084400988288</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.56288448168123</v>
+        <v>0.481810504189871</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.791625463192146</v>
+        <v>2.742981076697331</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.815857941488453</v>
+        <v>-3.796806615928324</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9320875466490037</v>
+        <v>0.9397080768730555</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6634026401799845</v>
+        <v>0.5823286626886255</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.856828731666124</v>
+        <v>2.808184345171308</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.7999526120561</v>
+        <v>-3.780901286495971</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9252043508978169</v>
+        <v>0.9328248811218687</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5842899794707457</v>
+        <v>0.5032160019793865</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.796115807716453</v>
+        <v>2.747471421221637</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.755114210447702</v>
+        <v>-3.736062884887573</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9472374141518047</v>
+        <v>0.9548579443758565</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5888334124156152</v>
+        <v>0.507759434924256</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.802939570094003</v>
+        <v>2.754295183599187</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.77461266668971</v>
+        <v>-3.755561341129581</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9435989712860795</v>
+        <v>0.9512195015101312</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5407487711357108</v>
+        <v>0.4596747936443517</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.778249724957139</v>
+        <v>2.729605338462323</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.73040982960381</v>
+        <v>-3.711358504043681</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9671597086482768</v>
+        <v>0.9747802388723286</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5849516082216113</v>
+        <v>0.5038776307302522</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.810651029736516</v>
+        <v>2.7620066432417</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.83819962926564</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.737969495440857</v>
+        <v>-3.718918169880728</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9625458427827056</v>
+        <v>0.9701663730067573</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.5586810347400715</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.841943072611655</v>
+        <v>2.793298686116839</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.579678077901585</v>
+        <v>-3.560626752341455</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.077110174981454</v>
+        <v>1.084730705205506</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6397550122314306</v>
+        <v>0.5586810347400715</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.893190837794695</v>
+        <v>2.844546451299879</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321018</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.372036074267108</v>
+        <v>-3.352984748706979</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.158607681029498</v>
+        <v>1.16622821125355</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8473970158659068</v>
+        <v>0.7663230383745476</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.016216744569634</v>
+        <v>2.967572358074818</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475134</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.32100398154458</v>
+        <v>-3.301952655984451</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.173968746356779</v>
+        <v>1.181589276580831</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8984291085884347</v>
+        <v>0.8173551310970756</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.04178422844142</v>
+        <v>2.993139841946605</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404848</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.255779800417375</v>
+        <v>-3.236728474857245</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.217245822900366</v>
+        <v>1.224866353124418</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9636532897156403</v>
+        <v>0.8825793122242812</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.098106141210449</v>
+        <v>3.049461754715633</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882551</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.218352780346241</v>
+        <v>-3.199301454786112</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.2281776032281</v>
+        <v>1.235798133452152</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.968904827744822</v>
+        <v>0.8878308502534629</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.097218036327238</v>
+        <v>3.048573649832422</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.216994795372695</v>
+        <v>-3.197943469812566</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.229977589548759</v>
+        <v>1.23759811977281</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.043242953282641</v>
+        <v>0.9621689757912815</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.143077703981169</v>
+        <v>3.094433317486354</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.188581532272812</v>
+        <v>-3.169530206712682</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.401900665809923</v>
+        <v>1.409521196033975</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9842673905362118</v>
+        <v>0.9031934130448527</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.268250137354523</v>
+        <v>3.219605750859707</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.113799271247799</v>
+        <v>-3.09474794568767</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.551926479437745</v>
+        <v>1.559547009661797</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.059049651561224</v>
+        <v>0.9779756740698653</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.433232403187348</v>
+        <v>3.384588016692532</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.087715186983991</v>
+        <v>-3.068663861423862</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.554068089157127</v>
+        <v>1.561688619381179</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.059049651561224</v>
+        <v>0.9779756740698653</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.424940379201207</v>
+        <v>3.376295992706391</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.999837273874871</v>
+        <v>-2.980785948314741</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.587412449984555</v>
+        <v>1.595032980208607</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.174975293984576</v>
+        <v>1.093901316493216</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.492688960238997</v>
+        <v>3.444044573744181</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.990944812481588</v>
+        <v>-2.971893486921458</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.60852384026866</v>
+        <v>1.616144370492711</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.174975293984576</v>
+        <v>1.093901316493216</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.510243365965788</v>
+        <v>3.461598979470973</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.159420929451465</v>
+        <v>-3.140369603891336</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.532988440885292</v>
+        <v>1.540608971109344</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.147027458267995</v>
+        <v>1.065953480776636</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.485329711940424</v>
+        <v>3.436685325445608</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.713164736822026</v>
+        <v>-2.694113411261896</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.69276061512493</v>
+        <v>1.700381145348982</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.052308788598362</v>
+        <v>0.9712348111070028</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.409768207326506</v>
+        <v>3.36112382083169</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.690443633138873</v>
+        <v>-2.671392307578744</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.692513079095096</v>
+        <v>1.700133609319147</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.052308788598362</v>
+        <v>0.9712348111070028</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.40043222982341</v>
+        <v>3.351787843328595</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777667</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.819645446432915</v>
+        <v>-2.800594120872786</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.799738479628648</v>
+        <v>1.807359009852699</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.92310697530432</v>
+        <v>0.8420329978129606</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.481817267698154</v>
+        <v>3.433172881203339</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.845519844906941</v>
+        <v>-2.826468519346812</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.826466542732684</v>
+        <v>1.834087072956736</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9680185840160611</v>
+        <v>0.8869446065247018</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.545842055418845</v>
+        <v>3.49719766892403</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.838465154691768</v>
+        <v>-2.819413829131638</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.825963774808299</v>
+        <v>1.83358430503235</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9750732742312349</v>
+        <v>0.8939992967398755</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.546750225537495</v>
+        <v>3.498105839042679</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.81151393036528</v>
+        <v>-2.79246260480515</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.846750418183635</v>
+        <v>1.854370948407687</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.9088796427675947</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.565684586798868</v>
+        <v>3.517040200304052</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.833058158196067</v>
+        <v>-2.814006832635938</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.022235859196281</v>
+        <v>2.029856389420332</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.9088796427675947</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.749787718943828</v>
+        <v>3.701143332449012</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.74392550571442</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.855466276000939</v>
+        <v>-2.83641495044081</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.005389306977325</v>
+        <v>2.013009837201376</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.9088796427675947</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.741904413846821</v>
+        <v>3.693260027352005</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.883690511578539</v>
+        <v>-2.86463918601841</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.996153612295922</v>
+        <v>2.003774142519974</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.007930372710263</v>
+        <v>0.9268563952189033</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.754744464867243</v>
+        <v>3.706100078372428</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161971</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.893131437467069</v>
+        <v>-2.87408011190694</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.048630959662357</v>
+        <v>2.056251489886409</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.130357490253654</v>
+        <v>1.049283512762295</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.884454453115125</v>
+        <v>3.83581006662031</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321628</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.982008068635543</v>
+        <v>-2.962956743075414</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.015971401740268</v>
+        <v>2.02359193196432</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.04148085908518</v>
+        <v>0.9604068815938209</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.834019568959342</v>
+        <v>3.785375182464526</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.058338046236449</v>
+        <v>-3.03928672067632</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.983551223593681</v>
+        <v>1.991171753817733</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.04148085908518</v>
+        <v>0.9604068815938209</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.832131381853117</v>
+        <v>3.783486995358301</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.213294831636578</v>
+        <v>-3.194243506076449</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.916388739036492</v>
+        <v>1.924009269260543</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.886524073685051</v>
+        <v>0.8054500961936917</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.733977540215902</v>
+        <v>3.685333153721086</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.374863257163833</v>
+        <v>-3.355811931603704</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.850195379035742</v>
+        <v>1.857815909259794</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7597411498871717</v>
+        <v>0.6786671723958123</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.656341796147327</v>
+        <v>3.607697409652511</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.483163919033953</v>
+        <v>-3.464112593473823</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.819948521153613</v>
+        <v>1.827569051377665</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7597411498871717</v>
+        <v>0.6786671723958123</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.669415203013245</v>
+        <v>3.62077081651843</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.500967890754697</v>
+        <v>-3.481916565194568</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.804832129248255</v>
+        <v>1.812452659472307</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6892065269819705</v>
+        <v>0.6081325494906111</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.619099626053064</v>
+        <v>3.570455239558249</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.52886867786417</v>
+        <v>-3.509817352304041</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.792195855531468</v>
+        <v>1.79981638575552</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6546096028390357</v>
+        <v>0.5735356253476763</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.596865512694305</v>
+        <v>3.54822112619949</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.651394780567064</v>
+        <v>-3.632343455006934</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.739949858427509</v>
+        <v>1.747570388651561</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5320835001361418</v>
+        <v>0.4510095226447824</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.520114295049768</v>
+        <v>3.471469908554953</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.881909276752652</v>
+        <v>-3.862857951192523</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.714450019543778</v>
+        <v>1.722070549767829</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3015690039505531</v>
+        <v>0.2204950264591937</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.448511556928918</v>
+        <v>3.399867170434103</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.230654361977096</v>
+        <v>-4.211603036416967</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.715263704455847</v>
+        <v>1.722884234679899</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1928210500316553</v>
+        <v>0.1117470725402959</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.523574503579427</v>
+        <v>3.474930117084611</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.384640779753236</v>
+        <v>-4.365589454193107</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.722649406491031</v>
+        <v>1.730269936715082</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1928210500316553</v>
+        <v>0.1117470725402959</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.592554772725067</v>
+        <v>3.543910386230251</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.589240214616245</v>
+        <v>-4.570188889056116</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.626860834665948</v>
+        <v>1.63448136489</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1928210500316553</v>
+        <v>0.1117470725402959</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.578605974845188</v>
+        <v>3.529961588350372</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.841715368623969</v>
+        <v>-4.82266404306384</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.537741262118272</v>
+        <v>1.545361792342324</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1928210500316553</v>
+        <v>0.1117470725402959</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.590476463900602</v>
+        <v>3.541832077405786</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.134611125103381</v>
+        <v>-5.115559799543252</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.421793494045451</v>
+        <v>1.429414024269503</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1928210500316553</v>
+        <v>0.1117470725402959</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.591686998419545</v>
+        <v>3.54304261192473</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.32127525323819</v>
+        <v>-5.30222392767806</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.35124958501885</v>
+        <v>1.358870115242901</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1660820792070954</v>
+        <v>0.08500810171573603</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.579765358152131</v>
+        <v>3.531120971657315</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916196</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.467295940152152</v>
+        <v>-5.448244614592022</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.287919162989454</v>
+        <v>1.295539693213506</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1569989874132384</v>
+        <v>0.07592500992187906</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.569393355812006</v>
+        <v>3.52074896931719</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830324</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.559009949261737</v>
+        <v>-5.539958623701608</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.413437616044664</v>
+        <v>1.421058146268716</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1569989874132384</v>
+        <v>0.07592500992187906</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.73159741251105</v>
+        <v>3.682953026016234</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071546</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.590661608321707</v>
+        <v>-5.571610282761577</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.39562359038449</v>
+        <v>1.403244120608542</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1518305301687982</v>
+        <v>0.07075655267743886</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.7233429761282</v>
+        <v>3.674698589633385</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868141</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.659727662894643</v>
+        <v>-5.640676337334514</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.378226586123807</v>
+        <v>1.385847116347859</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.08945965267518818</v>
+        <v>0.008385675183828822</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.696149867200525</v>
+        <v>3.64750548070571</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332686</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.761703785143051</v>
+        <v>-5.742652459582922</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.346361775680346</v>
+        <v>1.353982305904398</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.01251646957321939</v>
+        <v>-0.09359044706457875</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.643889832307383</v>
+        <v>3.595245445812568</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231803</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.651697501665829</v>
+        <v>-5.6326461761057</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.38251717631541</v>
+        <v>1.390137706539462</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.01068810234405582</v>
+        <v>-0.07038587514730354</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.649965462701924</v>
+        <v>3.601321076207108</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818517</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.508637925924903</v>
+        <v>-5.489586600364774</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.443991017333755</v>
+        <v>1.451611547557807</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.01870152893403509</v>
+        <v>-0.06237244855732427</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.659023529377885</v>
+        <v>3.61037914288307</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051783</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.207191200453066</v>
+        <v>-5.188139874892936</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.571830590405026</v>
+        <v>1.579451120629078</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3201482544058724</v>
+        <v>0.239074276914513</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.847152447543524</v>
+        <v>3.798508061048708</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679621</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.23178144468825</v>
+        <v>-5.21273011912812</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.562965670463663</v>
+        <v>1.570586200687715</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3201482544058724</v>
+        <v>0.239074276914513</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.848123625296235</v>
+        <v>3.799479238801419</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.180743068681729</v>
+        <v>-5.1616917431216</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.584223925246027</v>
+        <v>1.591844455470079</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3201482544058724</v>
+        <v>0.239074276914513</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.84896652967599</v>
+        <v>3.800322143181174</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969539</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.151894391858269</v>
+        <v>-5.13284306629814</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.614801494849556</v>
+        <v>1.622422025073608</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3489969312293326</v>
+        <v>0.2679229537379733</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.885313834644212</v>
+        <v>3.836669448149396</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700473</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.055259479839629</v>
+        <v>-5.0362081542795</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.469639455780947</v>
+        <v>1.477259986004999</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4456318432479726</v>
+        <v>0.3645578657566132</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.75947877797933</v>
+        <v>3.710834391484514</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077635</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.986221468891161</v>
+        <v>-4.967170143331032</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.500756704234298</v>
+        <v>1.50837723445835</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5146698541964406</v>
+        <v>0.4335958767050813</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.804403628622375</v>
+        <v>3.75575924212756</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.821725134700199</v>
+        <v>-4.80267380914007</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.550982056986765</v>
+        <v>1.558602587210817</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6791661883874025</v>
+        <v>0.5980922108960431</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.887528248213035</v>
+        <v>3.838883861718219</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.744626533158327</v>
+        <v>-4.725575207598197</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.581009208039944</v>
+        <v>1.588629738263996</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6791661883874025</v>
+        <v>0.5980922108960431</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.886715958649464</v>
+        <v>3.838071572154649</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.755011728048216</v>
+        <v>-4.735960402488087</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.586723909209061</v>
+        <v>1.594344439433113</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6687809934975132</v>
+        <v>0.5877070160061538</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.890353620840604</v>
+        <v>3.841709234345788</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.773599886770441</v>
+        <v>-4.754548561210312</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.650125651496596</v>
+        <v>1.657746181720648</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6501928347752879</v>
+        <v>0.5691188572839285</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.950037731383693</v>
+        <v>3.901393344888878</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.773898433466477</v>
+        <v>-4.754847107906348</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.64687524363648</v>
+        <v>1.654495773860532</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.649894288079252</v>
+        <v>0.5688203105878926</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.94672761418437</v>
+        <v>3.898083227689555</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108852</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.673075299776049</v>
+        <v>-4.65402397421592</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.691735392052043</v>
+        <v>1.699355922276094</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6623585035636058</v>
+        <v>0.5812845260722465</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.958737038414374</v>
+        <v>3.910092651919558</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121461</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.482293939023641</v>
+        <v>-4.463242613463512</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.768177189831549</v>
+        <v>1.775797720055601</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8531398643160132</v>
+        <v>0.7720658868246538</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.073335108344362</v>
+        <v>4.024690721849546</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906074</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.37533058117422</v>
+        <v>-4.356279255614091</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.790799378708914</v>
+        <v>1.798419908932966</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9116044722758146</v>
+        <v>0.8305304947844553</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.088250718857839</v>
+        <v>4.039606332363023</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.78576168591298</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.319999993272457</v>
+        <v>-4.300948667712328</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.847898550481678</v>
+        <v>1.855519080705729</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9669350601775768</v>
+        <v>0.8858610826862174</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.156416008210955</v>
+        <v>4.10777162171614</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539889</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.307945866359495</v>
+        <v>-4.288894540799365</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.846406769148301</v>
+        <v>1.854027299372352</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9789891870905396</v>
+        <v>0.8979152095991803</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.15733505226017</v>
+        <v>4.108690665765355</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.349100985927715</v>
+        <v>-4.330049660367586</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.831825351505148</v>
+        <v>1.8394458817292</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9378340675223187</v>
+        <v>0.8567600900309593</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.134522610703374</v>
+        <v>4.085878224208558</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382914</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.281052423236186</v>
+        <v>-4.262001097676056</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.871895802459642</v>
+        <v>1.879516332683694</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.005882630213848</v>
+        <v>0.9248086527224891</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.188202774196174</v>
+        <v>4.139558387701358</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013421</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.512652816405686</v>
+        <v>-4.493601490845557</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.799458315365436</v>
+        <v>1.807078845589488</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.005882630213848</v>
+        <v>0.9248086527224891</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.208405444369768</v>
+        <v>4.159761057874952</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.562704361934905</v>
+        <v>-4.543653036374776</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.763043933220631</v>
+        <v>1.770664463444682</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.005882630213848</v>
+        <v>0.9248086527224891</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.19201168043665</v>
+        <v>4.143367293941835</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.73781119451135</v>
+        <v>-4.718759868951221</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.65325311378352</v>
+        <v>1.660873644007571</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.005882630213848</v>
+        <v>0.9248086527224891</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.152263594030117</v>
+        <v>4.103619207535301</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.541711041080827</v>
+        <v>-4.522659715520698</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.738715794152669</v>
+        <v>1.74633632437672</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.201982783644371</v>
+        <v>1.120908806153012</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.276946305085371</v>
+        <v>4.228301918590555</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.388685648967543</v>
+        <v>-4.369634323407413</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.899096950570887</v>
+        <v>1.906717480794939</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.355008175757655</v>
+        <v>1.273934198266296</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.467932539926245</v>
+        <v>4.41928815343143</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.416992962840813</v>
+        <v>-4.397941637280684</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.075240249929871</v>
+        <v>2.082860780153923</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.355008175757655</v>
+        <v>1.273934198266296</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.655398764834538</v>
+        <v>4.606754378339723</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.583586187954335</v>
+        <v>-4.564534862394206</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.978005911238545</v>
+        <v>1.985626441462597</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.188414950644133</v>
+        <v>1.107340973152773</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.524845781120507</v>
+        <v>4.476201394625692</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.560550394592769</v>
+        <v>-4.54149906903264</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.990896631244889</v>
+        <v>1.998517161468941</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.188414950644133</v>
+        <v>1.107340973152773</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.528522183782225</v>
+        <v>4.47987779728741</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.531304414137073</v>
+        <v>-4.512253088576943</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.000213078550663</v>
+        <v>2.007833608774715</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.188414950644133</v>
+        <v>1.107340973152773</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.52614023890572</v>
+        <v>4.477495852410905</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.638229962014924</v>
+        <v>-4.619178636454794</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.954736098557158</v>
+        <v>1.96235662878121</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.081489402766282</v>
+        <v>1.000415425274922</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.459278149336645</v>
+        <v>4.410633762841829</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.783248520522172</v>
+        <v>-4.764197194962043</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.898157477297493</v>
+        <v>1.905778007521544</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.936470844259033</v>
+        <v>0.8553968667676737</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.37369581637553</v>
+        <v>4.325051429880714</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.876527922720239</v>
+        <v>-4.882538960746761</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.960776955676019</v>
+        <v>1.95837254046541</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9472559297650114</v>
+        <v>0.8660829053305638</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.48009810693687</v>
+        <v>4.431394292276201</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.927938345040947</v>
+        <v>-4.933949383067469</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.937998483873675</v>
+        <v>1.935594068663066</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9472559297650114</v>
+        <v>0.8660829053305638</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.477883804062809</v>
+        <v>4.42917998940214</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.704757949437327</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.007357796248699</v>
+        <v>-5.01336883427522</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.906133831464863</v>
+        <v>1.903729416254254</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9472559297650114</v>
+        <v>0.8660829053305638</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.477786932137098</v>
+        <v>4.429083117476429</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.102820794165916</v>
+        <v>-5.108831832192438</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.867942525856019</v>
+        <v>1.865538110645411</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9472559297650114</v>
+        <v>0.8660829053305638</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.477780825695141</v>
+        <v>4.429077011034472</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.038444883315202</v>
+        <v>-5.044455921341723</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.891789286758916</v>
+        <v>1.889384871548307</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.011631840615727</v>
+        <v>0.9304588161812789</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.51450276876818</v>
+        <v>4.465798954107512</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.093814045447395</v>
+        <v>-5.099825083473917</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.875375439653765</v>
+        <v>1.872971024443156</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.011631840615727</v>
+        <v>0.9304588161812789</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.520236586515907</v>
+        <v>4.471532771855238</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.112032512445004</v>
+        <v>-5.118043550471525</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.867626416197654</v>
+        <v>1.865222000987045</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9865254033598844</v>
+        <v>0.9053523789254367</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.504711087505334</v>
+        <v>4.456007272844666</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.023825678297426</v>
+        <v>-5.029836716323947</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.922783542707004</v>
+        <v>1.920379127496395</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9865254033598844</v>
+        <v>0.9053523789254367</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.524585480355653</v>
+        <v>4.475881665694985</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.917790683092116</v>
+        <v>-4.923801721118638</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.948898241313855</v>
+        <v>1.946493826103247</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9865254033598844</v>
+        <v>0.9053523789254367</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.508286180880381</v>
+        <v>4.459582366219712</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.734579019959021</v>
+        <v>-4.740590057985543</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.024613856031139</v>
+        <v>2.02220944082053</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9865254033598844</v>
+        <v>0.9053523789254367</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.510717130344426</v>
+        <v>4.462013315683758</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.66285757294517</v>
+        <v>-4.668868610971692</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.036246840916056</v>
+        <v>2.033842425705448</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.058246850373735</v>
+        <v>0.9770738259392874</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.536694404632113</v>
+        <v>4.487990589971445</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.640484547337464</v>
+        <v>-4.646495585363986</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.992111797080311</v>
+        <v>1.989707381869702</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.069502601486636</v>
+        <v>0.9883295770521889</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.490363601221026</v>
+        <v>4.441659786560358</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.673500843248209</v>
+        <v>-4.67951188127473</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.164103483601368</v>
+        <v>2.161699068390759</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.000065224819885</v>
+        <v>0.9188922003854374</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.633899380106331</v>
+        <v>4.585195565445662</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.6619732075986</v>
+        <v>-4.667984245625122</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.160635763689461</v>
+        <v>2.158231348478852</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.059065883021247</v>
+        <v>0.9778928585867999</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.661221000855397</v>
+        <v>4.612517186194729</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.759314708940969</v>
+        <v>-4.76532574696749</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.125367275674302</v>
+        <v>2.122962860463693</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.014645700855759</v>
+        <v>0.9334726764213115</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.638237004077893</v>
+        <v>4.589533189417224</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.70520107942768</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.845170738280935</v>
+        <v>-4.851181776307457</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.092275946131153</v>
+        <v>2.089871530920544</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.972269631629624</v>
+        <v>0.8910966071951765</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.61406244473505</v>
+        <v>4.565358630074382</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.854007535697055</v>
+        <v>-4.860018573723576</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.071160428985207</v>
+        <v>2.068756013774599</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9648274589882733</v>
+        <v>0.8836544345538258</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.592016342970742</v>
+        <v>4.543312528310073</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.945390098262513</v>
+        <v>-4.951401136289035</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.044771915004073</v>
+        <v>2.042367499793465</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9282625742689286</v>
+        <v>0.847089549834481</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.580241923184184</v>
+        <v>4.531538108523516</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.933683380275507</v>
+        <v>-4.939694418302029</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.151582860023144</v>
+        <v>2.149178444812535</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.939969292255935</v>
+        <v>0.8587962678214874</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.689394211800656</v>
+        <v>4.640690397139988</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.004595454017785</v>
+        <v>-5.010606492044307</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.126250369257638</v>
+        <v>2.123845954047029</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.939969292255935</v>
+        <v>0.8587962678214874</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.692426550532061</v>
+        <v>4.643722735871393</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.014911552184137</v>
+        <v>-5.020922590210659</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.335028763269155</v>
+        <v>2.332624348058546</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.939969292255935</v>
+        <v>0.8587962678214874</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.905331383810119</v>
+        <v>4.856627569149451</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.014817584166765</v>
+        <v>-5.020828622193286</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.334245017388194</v>
+        <v>2.331840602177585</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.8591661291688054</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.9047319675306</v>
+        <v>4.856028152869931</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.163183811822909</v>
+        <v>-5.169194849849431</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.26913051227009</v>
+        <v>2.266726097059481</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.8591661291688054</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.898963953474953</v>
+        <v>4.850260138814285</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.162235388704871</v>
+        <v>-5.168246426731392</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.269509881517305</v>
+        <v>2.267105466306696</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.8591661291688054</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.898963953474953</v>
+        <v>4.850260138814285</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.262505206663892</v>
+        <v>-5.268516244690414</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.242129562314788</v>
+        <v>2.23972514710418</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.8591661291688054</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.911691561456045</v>
+        <v>4.862987746795377</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.256512959875081</v>
+        <v>-5.262523997901602</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.246472459454701</v>
+        <v>2.244068044244092</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.8591661291688054</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.913637559880433</v>
+        <v>4.864933745219765</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.167954998744313</v>
+        <v>-5.173966036770834</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.275549779924777</v>
+        <v>2.273145364714168</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.8591661291688054</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.907291695898202</v>
+        <v>4.858587881237534</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.73530072138309</v>
+        <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.150195921241239</v>
+        <v>-5.15620695926776</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.281962088365002</v>
+        <v>2.279557673154394</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.9403391536032529</v>
+        <v>0.8591661291688054</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.906600373337198</v>
+        <v>4.857896558676529</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.050565770192171</v>
+        <v>-5.056576808218693</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.334596334693216</v>
+        <v>2.332191919482607</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.03996930465232</v>
+        <v>0.9587962802178729</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.979160649875225</v>
+        <v>4.930456835214557</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.77535709745527</v>
+        <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.099965278881182</v>
+        <v>-5.105976316907704</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.503990796716338</v>
+        <v>2.501586381505729</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.050228138084065</v>
+        <v>0.9690551136496176</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.174470215432998</v>
+        <v>5.12576640077233</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963131</v>
+        <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.893280805238806</v>
+        <v>-4.899291843265328</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.57385325927615</v>
+        <v>2.571448844065542</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.256912611726441</v>
+        <v>1.175739587291993</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.285669572721286</v>
+        <v>5.236965758060617</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162541</v>
+        <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.927437700236332</v>
+        <v>-4.933448738262854</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.562192014931245</v>
+        <v>2.559787599720636</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.173328842185628</v>
+        <v>1.092155817751181</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.237520824650903</v>
+        <v>5.188817009990235</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.834848221174876</v>
+        <v>-5.007966212228576</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.952724920545495</v>
+        <v>2.883477724124015</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.173328842185628</v>
+        <v>1.092155817751181</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.591017938640571</v>
+        <v>5.542314123979902</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.894736848998426</v>
+        <v>-5.067854840052126</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.933332580983178</v>
+        <v>2.864085384561698</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.159206927498164</v>
+        <v>1.078033903063716</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.587107901395195</v>
+        <v>5.538404086734526</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.83520244110356</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.842520539202084</v>
+        <v>-5.015638530255784</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.004049046225242</v>
+        <v>2.934801849803762</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.159206927498164</v>
+        <v>1.078033903063716</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.636937842718723</v>
+        <v>5.588234028058054</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047744</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.810623022116839</v>
+        <v>-4.983741013170539</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.025622023269351</v>
+        <v>2.956374826847871</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.19110444458341</v>
+        <v>1.109931420148962</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.664890323179881</v>
+        <v>5.616186508519212</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650752</v>
+        <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.825378346316979</v>
+        <v>-4.998496337370679</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.015357477628492</v>
+        <v>2.946110281207012</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.19110444458341</v>
+        <v>1.109931420148962</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.660527907219078</v>
+        <v>5.611824092558409</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135747</v>
+        <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.775913722947068</v>
+        <v>-4.949031714000768</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.026067830392737</v>
+        <v>2.956820633971256</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.240569067953321</v>
+        <v>1.159396043518874</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.681131184657304</v>
+        <v>5.632427369996636</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.82593179047922</v>
+        <v>3.825931790479219</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.612805730793452</v>
+        <v>-4.785923721847152</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.087718694969118</v>
+        <v>3.018471498547637</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.403677060106936</v>
+        <v>1.322504035672489</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.775403647664408</v>
+        <v>5.72669983300374</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844245</v>
+        <v>3.847096478844243</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.479998105296286</v>
+        <v>-4.653116096349986</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.149888781859112</v>
+        <v>3.080641585437632</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.403677060106936</v>
+        <v>1.322504035672489</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.784450684355536</v>
+        <v>5.735746869694868</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790948</v>
+        <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.542706021770844</v>
+        <v>-4.715824012824544</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.125663080255411</v>
+        <v>3.05641588383393</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.340969143632379</v>
+        <v>1.259796119197931</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.747683399456923</v>
+        <v>5.698979584796255</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578995</v>
+        <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.494697897927151</v>
+        <v>-4.667815888980851</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.10777574658324</v>
+        <v>3.03852855016176</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.340969143632379</v>
+        <v>1.259796119197931</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.710592816247275</v>
+        <v>5.661889001586607</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629883</v>
+        <v>3.872253907629881</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.41587224074356</v>
+        <v>-4.58899023179726</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.143238263014626</v>
+        <v>3.073991066593146</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.419794800815969</v>
+        <v>1.338621776381522</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.76182046411538</v>
+        <v>5.713116649454712</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686403</v>
+        <v>3.868502531686402</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.223937439489687</v>
+        <v>-4.397055430543387</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.214911276123213</v>
+        <v>3.145664079701733</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.419794800815969</v>
+        <v>1.338621776381522</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.756719556722417</v>
+        <v>5.708015742061749</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.82684194890652</v>
+        <v>3.885204719135551</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.87140640678826</v>
+        <v>4.901940634414091</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.223937439489687</v>
+        <v>-4.397055430543387</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.214911276123213</v>
+        <v>3.145664079701733</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.419794800815969</v>
+        <v>1.338621776381522</v>
       </c>
       <c r="G2102" t="n">
-        <v>4.864470203774628</v>
+        <v>4.895004431400459</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240929.xlsx
+++ b/tame_output/ON/bt/strategyON_20240929.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>48.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.2%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>178.6%</t>
+          <t>172.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.8%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.5%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.6%</t>
+          <t>421.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.3%</t>
+          <t>-590.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-61.7%</t>
+          <t>-55.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-82.2%</t>
+          <t>-263.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-90.1%</t>
+          <t>-87.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>37.2%</t>
         </is>
       </c>
     </row>
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.257130876618868</v>
+        <v>-8.176056899127509</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1712954361462629</v>
+        <v>-0.1388658451497196</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.08614191277722</v>
+        <v>-1.005067935285861</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.480228191148701</v>
+        <v>2.528872577643516</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.311202376127227</v>
+        <v>-8.230128398635868</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1900304796280343</v>
+        <v>-0.1576008886314906</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.14021341228558</v>
+        <v>-1.059139434794221</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.450678847765257</v>
+        <v>2.499323234260073</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.314778162218975</v>
+        <v>-8.233704184727616</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1859475969460909</v>
+        <v>-0.1535180059495476</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.165742334202072</v>
+        <v>-1.084668356710713</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.440874691734004</v>
+        <v>2.489519078228819</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.348431000727448</v>
+        <v>-8.267357023236089</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1949261778650442</v>
+        <v>-0.1624965868685009</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.266155702119109</v>
+        <v>-1.185081724627751</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.385109225468218</v>
+        <v>2.433753611963033</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.487517115346305</v>
+        <v>-8.406443137854946</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2351889222191659</v>
+        <v>-0.2027593312226226</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.405241816737966</v>
+        <v>-1.324167839246607</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.317029258190325</v>
+        <v>2.36567364468514</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.662641532732849</v>
+        <v>-8.58156755524149</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2906834684262667</v>
+        <v>-0.2582538774297229</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.58036623412451</v>
+        <v>-1.499292256633151</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.226509828505915</v>
+        <v>2.275154215000731</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.897093626747338</v>
+        <v>-8.816019649255979</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3916834709336583</v>
+        <v>-0.359253879937115</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.58036623412451</v>
+        <v>-1.499292256633151</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.219290663604319</v>
+        <v>2.267935050099135</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.001468357773785</v>
+        <v>-8.920394380282426</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4401055541182131</v>
+        <v>-0.4076759631216698</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.684740965150956</v>
+        <v>-1.603666987659597</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.149993634214475</v>
+        <v>2.198638020709291</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.163981823472369</v>
+        <v>-9.08290784598101</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5039951505590907</v>
+        <v>-0.471565559562547</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.782374395569643</v>
+        <v>-1.701300418078284</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.09252936580182</v>
+        <v>2.141173752296635</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.290018616840658</v>
+        <v>-9.2089446393493</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5517161392772918</v>
+        <v>-0.5192865482807481</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.7571227727599</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.11037406811678</v>
+        <v>2.159018454611595</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.232946844944728</v>
+        <v>-9.151872867453369</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5248970948325185</v>
+        <v>-0.4924675038359752</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.7571227727599</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.11436440380318</v>
+        <v>2.163008790297996</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.374618686668848</v>
+        <v>-9.293544709177489</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5830410584209083</v>
+        <v>-0.550611467424365</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.7571227727599</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.112889176904439</v>
+        <v>2.161533563399254</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.325027842244014</v>
+        <v>-9.243953864752655</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5481513104861024</v>
+        <v>-0.5157217194895587</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.707531928335067</v>
+        <v>-1.626457950843708</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.157697093724211</v>
+        <v>2.206341480219027</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.176109507772157</v>
+        <v>-9.095035530280798</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5016351103440426</v>
+        <v>-0.4692055193474993</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.676282337599893</v>
+        <v>-1.595208360108535</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.163395714518632</v>
+        <v>2.212040101013448</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.950264355052747</v>
+        <v>-8.869190377561386</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4017179762200702</v>
+        <v>-0.3692883852235256</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.63435566201273</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.198130792907139</v>
+        <v>2.246775179401955</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.825685698715155</v>
+        <v>-8.744611721223794</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3507473691289742</v>
+        <v>-0.31831777813243</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.63435566201273</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.199269937463198</v>
+        <v>2.247914323958013</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.800649017146645</v>
+        <v>-8.719575039655284</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3380989223394626</v>
+        <v>-0.3056693313429184</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.609026574461994</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.217101164155747</v>
+        <v>2.265745550650562</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.728515841858764</v>
+        <v>-8.647441864367403</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3035119479856738</v>
+        <v>-0.2710823569891296</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.609026574461994</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.222834868394384</v>
+        <v>2.271479254889199</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.725312181432958</v>
+        <v>-8.644238203941597</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3119677462092167</v>
+        <v>-0.2795381552126726</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.605822914036188</v>
+        <v>-1.524748936544829</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.215019802256002</v>
+        <v>2.263664188750818</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.631853147447734</v>
+        <v>-8.550779169956373</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2844676139280344</v>
+        <v>-0.2520380229314902</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.605822914036188</v>
+        <v>-1.524748936544829</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.205136320943095</v>
+        <v>2.25378070743791</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.621199965894302</v>
+        <v>-8.540125988402941</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2820409018060355</v>
+        <v>-0.2496113108094913</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.605822914036188</v>
+        <v>-1.524748936544829</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.203301760443721</v>
+        <v>2.251946146938536</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.523292927217812</v>
+        <v>-8.442218949726451</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2431784013089002</v>
+        <v>-0.210748810312356</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.537837164175631</v>
+        <v>-1.456763186684273</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.243792895386594</v>
+        <v>2.292437281881409</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.499339386241854</v>
+        <v>-8.418265408750493</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2329284787730233</v>
+        <v>-0.2004988877764791</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.513883623199674</v>
+        <v>-1.432809645708315</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.258833526117662</v>
+        <v>2.307477912612478</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.235279447919057</v>
+        <v>-8.154205470427696</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1405648196056566</v>
+        <v>-0.1081352286091124</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.249823684876878</v>
+        <v>-1.168749707385519</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.404009172949588</v>
+        <v>2.452653559444403</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.528199824414219</v>
+        <v>-7.447125846922858</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1394799961359778</v>
+        <v>0.171909587132522</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.249823684876878</v>
+        <v>-1.168749707385519</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.401222139289287</v>
+        <v>2.449866525784102</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.488015526048028</v>
+        <v>-7.406941548556667</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1558973393702954</v>
+        <v>0.1883269303668396</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.209639386510687</v>
+        <v>-1.128565409019328</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.425676342196843</v>
+        <v>2.474320728691658</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.324615655108666</v>
+        <v>-7.243541677617305</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2206241089667973</v>
+        <v>0.2530536999633415</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.046239515571324</v>
+        <v>-0.9651655380799653</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.523083085981217</v>
+        <v>2.571727472476033</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.16649827572989</v>
+        <v>-7.08542429823853</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2917954895561596</v>
+        <v>0.3242250805527038</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8881221361925488</v>
+        <v>-0.8070481587011898</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.625877942446335</v>
+        <v>2.67452232894115</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.016831884722375</v>
+        <v>-6.935757907231014</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3487698356462063</v>
+        <v>0.381199426642751</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7952186449500128</v>
+        <v>-0.7141446674586539</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.678727826878897</v>
+        <v>2.727372213373712</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.884556411091489</v>
+        <v>-6.803482433600128</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3029408111057159</v>
+        <v>0.3353704021022601</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6629431713191262</v>
+        <v>-0.5818691938277673</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.659353897064584</v>
+        <v>2.707998283559399</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.712695195526586</v>
+        <v>-6.631621218035225</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3745003580193136</v>
+        <v>0.4069299490158578</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4910819557542233</v>
+        <v>-0.4100079782628644</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.765285687091162</v>
+        <v>2.813930073585978</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.627730528797267</v>
+        <v>-6.546656551305906</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4213925659347</v>
+        <v>0.4538221569312442</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4061172890249037</v>
+        <v>-0.3250433115335448</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.829170828352413</v>
+        <v>2.877815214847228</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.733320518570372</v>
+        <v>-6.652246541079011</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2511806404262393</v>
+        <v>0.2836102314227835</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.5117072787980081</v>
+        <v>-0.4306333013066492</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.637840904889332</v>
+        <v>2.686485291384147</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.665085933944944</v>
+        <v>-6.584011956453583</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3270188161534966</v>
+        <v>0.3594484071500412</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4932919559254721</v>
+        <v>-0.4122179784341132</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.69743444048994</v>
+        <v>2.746078826984755</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.517145892537345</v>
+        <v>-6.436071915045984</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2695740240781292</v>
+        <v>0.3020036150746739</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.4729710400169146</v>
+        <v>-0.3918970625255556</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.593006181396667</v>
+        <v>2.641650567891482</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.464176370283356</v>
+        <v>-6.383102392791995</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2820478467262468</v>
+        <v>0.314477437722791</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.4200015177629257</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.616073908495582</v>
+        <v>2.664718294990398</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.298388174323065</v>
+        <v>-6.217314196831705</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3414025130152698</v>
+        <v>0.373832104011814</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.4200015177629257</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.609113296400489</v>
+        <v>2.657757682895304</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.265024967844297</v>
+        <v>-6.183950990352936</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3692101499879206</v>
+        <v>0.4016397409844648</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.4200015177629257</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.623575650781632</v>
+        <v>2.672220037276448</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.156765830721775</v>
+        <v>-6.075691853230414</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4070459252961243</v>
+        <v>0.4394755162926685</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.4200015177629257</v>
+        <v>-0.3389275402715667</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.618107771240827</v>
+        <v>2.666752157735643</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.033474695904644</v>
+        <v>-5.952400718413283</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4538604732335534</v>
+        <v>0.4862900642300976</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2967103829457952</v>
+        <v>-0.2156364054544362</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.689580546141682</v>
+        <v>2.738224932636498</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.980777828773353</v>
+        <v>-5.899703851281992</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.482640198323395</v>
+        <v>0.5150697893199392</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.244013515814504</v>
+        <v>-0.1629395383231451</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.728899644657782</v>
+        <v>2.777544031152598</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.737012386789909</v>
+        <v>-5.655938409298548</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5759270834638235</v>
+        <v>0.6083566744603677</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.244013515814504</v>
+        <v>-0.1629395383231451</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.724680353004833</v>
+        <v>2.773324739499648</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.647236714413436</v>
+        <v>-5.566162736922076</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6139616663344283</v>
+        <v>0.6463912573309725</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.182414070900194</v>
+        <v>-0.101340093408835</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.763764333873435</v>
+        <v>2.81240872036825</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.397386320464362</v>
+        <v>-5.316312342973001</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7066438988977604</v>
+        <v>0.7390734898943045</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.182414070900194</v>
+        <v>-0.101340093408835</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.756506408857137</v>
+        <v>2.805150795351952</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.22149422799693</v>
+        <v>-5.140420250505569</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.780599859405382</v>
+        <v>0.8130294504019262</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.182414070900194</v>
+        <v>-0.101340093408835</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.760105532377786</v>
+        <v>2.808749918872601</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.050047764974466</v>
+        <v>-4.968973787483105</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.862505950668921</v>
+        <v>0.8949355416654652</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.01096760787773088</v>
+        <v>0.07010636961362809</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.876300916245817</v>
+        <v>2.924945302740633</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.970025477865345</v>
+        <v>-4.888951500373985</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8935353431288664</v>
+        <v>0.9259649341254106</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.06905467923139008</v>
+        <v>0.1501286567227491</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.923334766127587</v>
+        <v>2.971979152622402</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.906389735631411</v>
+        <v>-4.82531575814005</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9236844410767575</v>
+        <v>0.9561140320733017</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1326904214653246</v>
+        <v>0.2137643989566836</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.966211012522265</v>
+        <v>3.01485539901708</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.812692417415016</v>
+        <v>-4.731618439923655</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.942357627147111</v>
+        <v>0.9747872181436554</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1326904214653246</v>
+        <v>0.2137643989566836</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.947405271306061</v>
+        <v>2.996049657800876</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.823195040480305</v>
+        <v>-4.742121062988944</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9398996545458729</v>
+        <v>0.9723292455424173</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1221877984000357</v>
+        <v>0.2032617758913947</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.942846774091764</v>
+        <v>2.99149116058658</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.71070877981143</v>
+        <v>-4.629634802320069</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.988823472648243</v>
+        <v>1.021253063644787</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1221877984000357</v>
+        <v>0.2032617758913947</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.946776087926585</v>
+        <v>2.9954204744214</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.692995092933565</v>
+        <v>-4.611921115442204</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9965875313167292</v>
+        <v>1.029017122313273</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1253691272969525</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.949363469182075</v>
+        <v>2.99800785567689</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.569520821620547</v>
+        <v>-4.488446844129186</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.04297531106193</v>
+        <v>1.075404902058474</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1253691272969525</v>
+        <v>0.2064431047883115</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.946361540402068</v>
+        <v>2.995005926896884</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.511584989622331</v>
+        <v>-4.43051101213097</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.06772868087183</v>
+        <v>1.100158271868374</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.1509310019797018</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.963277702222332</v>
+        <v>3.011922088717147</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.378717300559053</v>
+        <v>-4.297643323067692</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.136769939298965</v>
+        <v>1.169199530295509</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.1509310019797018</v>
+        <v>0.2320049794710608</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.979171885024155</v>
+        <v>3.02781627151897</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.258544217194554</v>
+        <v>-4.177470239703194</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.185985017085066</v>
+        <v>1.21841460808161</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.2711040853442008</v>
+        <v>0.3521780628355597</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.052421579483156</v>
+        <v>3.101065965977972</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.123290855864577</v>
+        <v>-4.042216878373217</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.250174464178497</v>
+        <v>1.282604055175041</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4063574466741779</v>
+        <v>0.4874314241655369</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.143661698842583</v>
+        <v>3.192306085337398</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.18316568322227</v>
+        <v>-4.102091705730909</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.212262024636846</v>
+        <v>1.24469161563339</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3464826193164858</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.093774293829393</v>
+        <v>3.142418680324209</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.063345452311433</v>
+        <v>-3.982271474820072</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.275479286235389</v>
+        <v>1.307908877231933</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3464826193164858</v>
+        <v>0.4275565968078447</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.109063463063602</v>
+        <v>3.157707849558417</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.065815158773239</v>
+        <v>-3.984741181281878</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.182135602973108</v>
+        <v>1.214565193969652</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.3440129128546796</v>
+        <v>0.4250868903460386</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.01522583850896</v>
+        <v>3.063870225003775</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.134185345097249</v>
+        <v>-4.053111367605887</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074049389928805</v>
+        <v>1.10647898092535</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.3532886118908946</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.94005311941599</v>
+        <v>2.988697505910805</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.2460576247234</v>
+        <v>-4.164983647232038</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.019737186710236</v>
+        <v>1.052166777706781</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.3532886118908946</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.930489828047881</v>
+        <v>2.979134214542697</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.230082959237132</v>
+        <v>-4.14900898174577</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9927015778287709</v>
+        <v>1.025131168825316</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.3532886118908946</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.897064352971908</v>
+        <v>2.945708739466724</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.054608699444662</v>
+        <v>-3.973534721953301</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.067458513737547</v>
+        <v>1.099888104734091</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.3532886118908946</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.901631584963696</v>
+        <v>2.950275971458512</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.046684324859748</v>
+        <v>-3.965610347368387</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.046370292332719</v>
+        <v>1.078799883329264</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.3532886118908946</v>
+        <v>0.4343625893822535</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.877373613724903</v>
+        <v>2.926018000219719</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.040406122289899</v>
+        <v>-3.959332144798538</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9774198867621087</v>
+        <v>1.009849477758653</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3595668144607436</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.809678848668263</v>
+        <v>2.858323235163078</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.980553503086176</v>
+        <v>-3.899479525594815</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.01153332087573</v>
+        <v>1.043962911872275</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3595668144607436</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.819851235100395</v>
+        <v>2.86849562159521</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.894310040059798</v>
+        <v>-3.813236062568437</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.040976976660142</v>
+        <v>1.073406567656686</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3595668144607436</v>
+        <v>0.4406407919521026</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.814797505674255</v>
+        <v>2.863441892169071</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.939616859458778</v>
+        <v>-3.858542881967417</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.014630024345075</v>
+        <v>1.04705961534162</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3187566514515128</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.782087183313243</v>
+        <v>2.830731569808058</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.96864996416108</v>
+        <v>-3.887575986669719</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.003568655497256</v>
+        <v>1.0359982464938</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3187566514515128</v>
+        <v>0.3998306289428718</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.782639056346344</v>
+        <v>2.831283442841159</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.87583948271022</v>
+        <v>-3.79476550521886</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9699655399689655</v>
+        <v>1.00239513096551</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.4115671329023722</v>
+        <v>0.4926411103937312</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.767598037108225</v>
+        <v>2.816242423603041</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.920228952039648</v>
+        <v>-3.839154974548287</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9540832281617955</v>
+        <v>0.9865128191583397</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3671776635729445</v>
+        <v>0.4482516410643035</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.742837831435169</v>
+        <v>2.791482217929985</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.899725258154151</v>
+        <v>-3.81865128066279</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9573604142277172</v>
+        <v>0.9897900052242616</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.3876813574584418</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.750215756278191</v>
+        <v>2.798860142773006</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.983397354866482</v>
+        <v>-3.902323377375122</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9293828713734518</v>
+        <v>0.961812462369996</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.3876813574584418</v>
+        <v>0.4687553349498008</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.755707052108858</v>
+        <v>2.804351438603673</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.011177752767836</v>
+        <v>-3.930103775276475</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9297679139814496</v>
+        <v>0.9621975049779938</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3599009595570888</v>
+        <v>0.4409749370484478</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.750536015136585</v>
+        <v>2.799180401631401</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.129558425497974</v>
+        <v>-4.048484448006613</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7207713648900476</v>
+        <v>0.7532009558865917</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.2926831074061126</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.548561023846653</v>
+        <v>2.597205410341468</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.238172503941305</v>
+        <v>-4.157098526449944</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7974753942319206</v>
+        <v>0.829904985228465</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.2926831074061126</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.668710684565859</v>
+        <v>2.717355071060674</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.202763465693162</v>
+        <v>-4.121689488201802</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8261520356335008</v>
+        <v>0.858581626630045</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.2926831074061126</v>
+        <v>0.3737570848974716</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.683223710668182</v>
+        <v>2.731868097162997</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.211224634348623</v>
+        <v>-4.130150656857262</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8201870095136852</v>
+        <v>0.8526166005102294</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.2842219387506515</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.675566450817274</v>
+        <v>2.724210837312089</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.034108304313457</v>
+        <v>-3.953034326822096</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8877625703730541</v>
+        <v>0.9201921613695982</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.2842219387506515</v>
+        <v>0.3652959162420105</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.672295479662576</v>
+        <v>2.720939866157391</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.079200549147003</v>
+        <v>-3.998126571655642</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8704090642015487</v>
+        <v>0.9028386551980931</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2223258955812618</v>
+        <v>0.3033998730726207</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.635841245522855</v>
+        <v>2.684485632017671</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.899825127908235</v>
+        <v>-3.818751150416874</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9359462080034702</v>
+        <v>0.9683757990000146</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3791026537519804</v>
+        <v>0.4601766312433394</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.723694275731701</v>
+        <v>2.772338662226516</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.944839341428841</v>
+        <v>-3.86376536393748</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8987479779268175</v>
+        <v>0.9311775689233617</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3487537584373758</v>
+        <v>0.4298277359287348</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.686292393874528</v>
+        <v>2.734936780369343</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.032850527987538</v>
+        <v>-3.951776550496178</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8692350656422845</v>
+        <v>0.9016646566388287</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2832772505782029</v>
+        <v>0.3643512280695618</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.652698051497969</v>
+        <v>2.701342437992785</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.134048309424711</v>
+        <v>-4.052974331933351</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8279598749639168</v>
+        <v>0.8603894659604607</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2148684370328837</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.610856685267279</v>
+        <v>2.659501071762095</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.127537342810398</v>
+        <v>-4.046463365319038</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8281642231639585</v>
+        <v>0.8605938141605025</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2148684370328837</v>
+        <v>0.2959424145242426</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.608456646821596</v>
+        <v>2.657101033316412</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.108499215103101</v>
+        <v>-4.027425237611741</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8323041934551225</v>
+        <v>0.8647337844516665</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1566848257016891</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.570071199231124</v>
+        <v>2.61871558572594</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.161015017377921</v>
+        <v>-4.079941039886561</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9305922741793846</v>
+        <v>0.9630218651759286</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1566848257016891</v>
+        <v>0.2377588031930481</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.689365600865315</v>
+        <v>2.73800998736013</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.164423328812501</v>
+        <v>-4.083349351321141</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9300622785916863</v>
+        <v>0.9624918695882303</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1892013947110665</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.709708871257075</v>
+        <v>2.75835325775189</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.145067192918654</v>
+        <v>-4.063993215427294</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9438132633461511</v>
+        <v>0.9762428543426951</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1892013947110665</v>
+        <v>0.2702753722024255</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.715717401654001</v>
+        <v>2.764361788148816</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.218396721656746</v>
+        <v>-4.137322744165386</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8124316731281136</v>
+        <v>0.8448612641246576</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.1895960571306884</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.613904420382974</v>
+        <v>2.662548806877789</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.302217942931445</v>
+        <v>-4.221143965440085</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7816968061497152</v>
+        <v>0.8141263971462591</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.1895960571306884</v>
+        <v>0.2706700346220474</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.616698041914455</v>
+        <v>2.66534242840927</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.29606523687866</v>
+        <v>-4.2149912593873</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7848202369624873</v>
+        <v>0.8172498279590312</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.1957487631834727</v>
+        <v>0.2768227406748317</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.621052013937784</v>
+        <v>2.669696400432599</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.50268323276781</v>
+        <v>2.525846080669123</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.312874535029162</v>
+        <v>-4.231800557537802</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7771769944423967</v>
+        <v>0.832769433340254</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.1789394650329711</v>
+        <v>0.2600134425243301</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.610046911787593</v>
+        <v>2.681854146183721</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.569018786564631</v>
+        <v>2.592181634465944</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.25057653625304</v>
+        <v>-4.16950255876168</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8684317477496666</v>
+        <v>0.9240241866475238</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2242337293074131</v>
+        <v>0.3053077067987721</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.703559024149079</v>
+        <v>2.775366258545207</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.371310788278758</v>
+        <v>2.394473636180071</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.048786338587882</v>
+        <v>-3.967712361096522</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7514398285298569</v>
+        <v>0.8070322674277142</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4222519214765675</v>
+        <v>0.5033258989679266</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.624661941164698</v>
+        <v>2.696469175560827</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.441601020600933</v>
+        <v>2.464763868502246</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.099673051274077</v>
+        <v>-4.018599073782717</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8013753757775541</v>
+        <v>0.8569678146754114</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.371365208790373</v>
+        <v>0.452439186281732</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.664420145875157</v>
+        <v>2.736227380271286</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319539</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.456228756716976</v>
+        <v>2.47939160461829</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.01306230862427</v>
+        <v>-3.93198833113291</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8506474089535205</v>
+        <v>0.906239847851378</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4499909399955312</v>
+        <v>0.5310649174868902</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.726223320714296</v>
+        <v>2.798030555110424</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.454764737541648</v>
+        <v>2.477927585442961</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.073271606629555</v>
+        <v>-3.992197629138194</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8250996705760782</v>
+        <v>0.8806921094739359</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3897816419902467</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.688633722735796</v>
+        <v>2.760440957131925</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.453256355581577</v>
+        <v>2.47641920348289</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.024084957945203</v>
+        <v>-3.943010980453843</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8432659480897473</v>
+        <v>0.898858386987605</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3897816419902467</v>
+        <v>0.4708556194816057</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.687125340775725</v>
+        <v>2.758932575171854</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316244</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.453119223017013</v>
+        <v>2.476282070918326</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.979711826306635</v>
+        <v>-3.898637848815274</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.860878068180611</v>
+        <v>0.9164705070784687</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4341547736288153</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.713612087194302</v>
+        <v>2.785419321590431</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.447513017155603</v>
+        <v>2.470675865056917</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.944980504988134</v>
+        <v>-3.863906527496773</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.869164390846602</v>
+        <v>0.9247568297444595</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4341547736288153</v>
+        <v>0.5152287511201743</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.708005881332893</v>
+        <v>2.779813115729022</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.453894774183408</v>
+        <v>2.477057622084721</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.897324774427078</v>
+        <v>-3.816250796935718</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8946084400988288</v>
+        <v>0.9502008789966858</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.481810504189871</v>
+        <v>0.56288448168123</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.742981076697331</v>
+        <v>2.814788311093459</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569612</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.458787147558133</v>
+        <v>2.481949995459446</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.796806615928324</v>
+        <v>-3.715732638436963</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9397080768730555</v>
+        <v>0.9953005157709125</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5823286626886255</v>
+        <v>0.6634026401799845</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.808184345171308</v>
+        <v>2.879991579567437</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.445541820034005</v>
+        <v>2.468704667935318</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.780901286495971</v>
+        <v>-3.69982730900461</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9328248811218687</v>
+        <v>0.9884173200197259</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5032160019793865</v>
+        <v>0.5842899794707457</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.747471421221637</v>
+        <v>2.819278655617766</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.449639522644634</v>
+        <v>2.472802370545947</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.736062884887573</v>
+        <v>-3.654988907396212</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9548579443758565</v>
+        <v>1.010450383273714</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.507759434924256</v>
+        <v>0.5888334124156152</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.754295183599187</v>
+        <v>2.826102417995316</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.453800462275712</v>
+        <v>2.476963310177025</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.755561341129581</v>
+        <v>-3.67448736363822</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9512195015101312</v>
+        <v>1.006811940407988</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4596747936443517</v>
+        <v>0.5407487711357108</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.729605338462323</v>
+        <v>2.801412572858451</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.459680064803549</v>
+        <v>2.482842912704862</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.711358504043681</v>
+        <v>-3.63028452655232</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9747802388723286</v>
+        <v>1.030372677770186</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5038776307302522</v>
+        <v>0.5849516082216113</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.7620066432417</v>
+        <v>2.833813877637829</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83819962926564</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.458090065272796</v>
+        <v>2.481252913174109</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.718918169880728</v>
+        <v>-3.637844192389367</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9701663730067573</v>
+        <v>1.025758811904614</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5586810347400715</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.793298686116839</v>
+        <v>2.865105920512968</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.509337830455836</v>
+        <v>2.532500678357149</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.560626752341455</v>
+        <v>-3.479552774850095</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.084730705205506</v>
+        <v>1.140323144103363</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5586810347400715</v>
+        <v>0.6397550122314306</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.844546451299879</v>
+        <v>2.916353685696008</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321018</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.507778535050089</v>
+        <v>2.530941382951402</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.352984748706979</v>
+        <v>-3.271910771215619</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.16622821125355</v>
+        <v>1.221820650151407</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7663230383745476</v>
+        <v>0.8473970158659068</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.967572358074818</v>
+        <v>3.039379592470946</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475134</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.502726763288359</v>
+        <v>2.525889611189672</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.301952655984451</v>
+        <v>-3.220878678493091</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.181589276580831</v>
+        <v>1.237181715478688</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8173551310970756</v>
+        <v>0.8984291085884347</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.993139841946605</v>
+        <v>3.064947076342733</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404848</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.519914167381064</v>
+        <v>2.543077015282377</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.236728474857245</v>
+        <v>-3.155654497365885</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.224866353124418</v>
+        <v>1.280458792022275</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8825793122242812</v>
+        <v>0.9636532897156403</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.049461754715633</v>
+        <v>3.121268989111762</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882551</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.515875139680344</v>
+        <v>2.539037987581657</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.199301454786112</v>
+        <v>-3.118227477294751</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.235798133452152</v>
+        <v>1.291390572350009</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8878308502534629</v>
+        <v>0.968904827744822</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.048573649832422</v>
+        <v>3.120380884228551</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992655</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.517131932011585</v>
+        <v>2.540294779912898</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.197943469812566</v>
+        <v>-3.116869492321205</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.23759811977281</v>
+        <v>1.293190558670668</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9621689757912815</v>
+        <v>1.043242953282641</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.094433317486354</v>
+        <v>3.166240551882482</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636281</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.677689703032796</v>
+        <v>2.700852550934108</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.169530206712682</v>
+        <v>-3.088456229221322</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.409521196033975</v>
+        <v>1.465113634931832</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9031934130448527</v>
+        <v>0.9842673905362118</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.219605750859707</v>
+        <v>3.291412985255836</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.797802612250613</v>
+        <v>2.820965460151926</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.09474794568767</v>
+        <v>-3.013673968196309</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.559547009661797</v>
+        <v>1.615139448559654</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9779756740698653</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.384588016692532</v>
+        <v>3.456395251088661</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.789510588264472</v>
+        <v>2.812673436165785</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.068663861423862</v>
+        <v>-2.987589883932501</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.561688619381179</v>
+        <v>1.617281058279036</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9779756740698653</v>
+        <v>1.059049651561224</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.376295992706391</v>
+        <v>3.44810322710252</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.787703783848251</v>
+        <v>2.810866631749564</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.980785948314741</v>
+        <v>-2.899711970823381</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.595032980208607</v>
+        <v>1.650625419106464</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.093901316493216</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.444044573744181</v>
+        <v>3.51585180814031</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.805258189575043</v>
+        <v>2.828421037476355</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.971893486921458</v>
+        <v>-2.890819509430098</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.616144370492711</v>
+        <v>1.671736809390568</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.093901316493216</v>
+        <v>1.174975293984576</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.461598979470973</v>
+        <v>3.533406213867101</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.797113236979627</v>
+        <v>2.820276084880939</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.140369603891336</v>
+        <v>-3.059295626399976</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.540608971109344</v>
+        <v>1.596201410007201</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.065953480776636</v>
+        <v>1.147027458267995</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.436685325445608</v>
+        <v>3.508492559841736</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.778382934167488</v>
+        <v>2.801545782068801</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.694113411261896</v>
+        <v>-2.613039433770536</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.700381145348982</v>
+        <v>1.755973584246839</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9712348111070028</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.36112382083169</v>
+        <v>3.432931055227819</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.769046956664393</v>
+        <v>2.792209804565706</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.671392307578744</v>
+        <v>-2.590318330087383</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.700133609319147</v>
+        <v>1.755726048217005</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9712348111070028</v>
+        <v>1.052308788598362</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.351787843328595</v>
+        <v>3.423595077724723</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777667</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.927953082515562</v>
+        <v>2.951115930416875</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.800594120872786</v>
+        <v>-2.719520143381426</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.807359009852699</v>
+        <v>1.862951448750557</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8420329978129606</v>
+        <v>0.92310697530432</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.433172881203339</v>
+        <v>3.504980115599467</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.965030905009209</v>
+        <v>2.988193752910521</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.826468519346812</v>
+        <v>-2.745394541855451</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.834087072956736</v>
+        <v>1.889679511854593</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8869446065247018</v>
+        <v>0.9680185840160611</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.49719766892403</v>
+        <v>3.569004903320158</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.961706260998754</v>
+        <v>2.984869108900067</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.819413829131638</v>
+        <v>-2.738339851640278</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.83358430503235</v>
+        <v>1.889176743930207</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8939992967398755</v>
+        <v>0.9750732742312349</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.498105839042679</v>
+        <v>3.569913073438808</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.971712414643495</v>
+        <v>2.994875262544808</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.79246260480515</v>
+        <v>-2.71138862731379</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.854370948407687</v>
+        <v>1.909963387305544</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9088796427675947</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.517040200304052</v>
+        <v>3.588847434700181</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.155815546788455</v>
+        <v>3.178978394689768</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.814006832635938</v>
+        <v>-2.732932855144577</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.029856389420332</v>
+        <v>2.085448828318189</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9088796427675947</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.701143332449012</v>
+        <v>3.77295056684514</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571442</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.147932241691448</v>
+        <v>3.171095089592761</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.83641495044081</v>
+        <v>-2.755340972949449</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.013009837201376</v>
+        <v>2.068602276099234</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9088796427675947</v>
+        <v>0.9899536202589541</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.693260027352005</v>
+        <v>3.765067261748134</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.149986241241086</v>
+        <v>3.173149089142398</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.86463918601841</v>
+        <v>-2.783565208527049</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.003774142519974</v>
+        <v>2.059366581417831</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9268563952189033</v>
+        <v>1.007930372710263</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.706100078372428</v>
+        <v>3.777907312768556</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161971</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.206239958962933</v>
+        <v>3.229402806864246</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.87408011190694</v>
+        <v>-2.793006134415579</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.056251489886409</v>
+        <v>2.111843928784266</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.049283512762295</v>
+        <v>1.130357490253654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.83581006662031</v>
+        <v>3.907617301016438</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321628</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.209131053508234</v>
+        <v>3.232293901409546</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.962956743075414</v>
+        <v>-2.881882765584053</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.02359193196432</v>
+        <v>2.079184370862177</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9604068815938209</v>
+        <v>1.04148085908518</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.785375182464526</v>
+        <v>3.857182416860655</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.207242866402009</v>
+        <v>3.230405714303322</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.03928672067632</v>
+        <v>-2.958212743184959</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.991171753817733</v>
+        <v>2.04676419271559</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9604068815938209</v>
+        <v>1.04148085908518</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.783486995358301</v>
+        <v>3.85529422975443</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.202063096004871</v>
+        <v>3.225225943906184</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.194243506076449</v>
+        <v>-3.113169528585088</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.924009269260543</v>
+        <v>1.979601708158401</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8054500961936917</v>
+        <v>0.886524073685051</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.685333153721086</v>
+        <v>3.757140388117215</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.200497106215023</v>
+        <v>3.223659954116336</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.355811931603704</v>
+        <v>-3.274737954112343</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.857815909259794</v>
+        <v>1.913408348157651</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6786671723958123</v>
+        <v>0.7597411498871717</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.607697409652511</v>
+        <v>3.679504644048639</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.213570513080942</v>
+        <v>3.236733360982255</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.464112593473823</v>
+        <v>-3.383038615982463</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.827569051377665</v>
+        <v>1.883161490275522</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6786671723958123</v>
+        <v>0.7597411498871717</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.62077081651843</v>
+        <v>3.692578050914558</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.205575709863882</v>
+        <v>3.228738557765195</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.481916565194568</v>
+        <v>-3.400842587703207</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.812452659472307</v>
+        <v>1.868045098370164</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6081325494906111</v>
+        <v>0.6892065269819705</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.570455239558249</v>
+        <v>3.642262473954377</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.204099750990884</v>
+        <v>3.227262598892197</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.509817352304041</v>
+        <v>-3.42874337481268</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.79981638575552</v>
+        <v>1.855408824653377</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5735356253476763</v>
+        <v>0.6546096028390357</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.54822112619949</v>
+        <v>3.620028360595618</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.200864194968083</v>
+        <v>3.224027042869396</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.632343455006934</v>
+        <v>-3.551269477515574</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.747570388651561</v>
+        <v>1.803162827549418</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4510095226447824</v>
+        <v>0.5320835001361418</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.471469908554953</v>
+        <v>3.543277142951081</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.267570154558586</v>
+        <v>3.290733002459899</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.862857951192523</v>
+        <v>-3.781783973701162</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.722070549767829</v>
+        <v>1.777662988665687</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2204950264591937</v>
+        <v>0.3015690039505531</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.399867170434103</v>
+        <v>3.471674404830231</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.407881873560433</v>
+        <v>3.431044721461746</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.211603036416967</v>
+        <v>-4.130529058925606</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.722884234679899</v>
+        <v>1.778476673577756</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1117470725402959</v>
+        <v>0.1928210500316553</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.474930117084611</v>
+        <v>3.54673735148074</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.476862142706073</v>
+        <v>3.500024990607386</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.365589454193107</v>
+        <v>-4.284515476701746</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.730269936715082</v>
+        <v>1.78586237561294</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1117470725402959</v>
+        <v>0.1928210500316553</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.543910386230251</v>
+        <v>3.61571762062638</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.462913344826194</v>
+        <v>3.486076192727507</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.570188889056116</v>
+        <v>-4.489114911564755</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.63448136489</v>
+        <v>1.690073803787857</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1117470725402959</v>
+        <v>0.1928210500316553</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.529961588350372</v>
+        <v>3.601768822746501</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.474783833881608</v>
+        <v>3.497946681782921</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.82266404306384</v>
+        <v>-4.741590065572479</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.545361792342324</v>
+        <v>1.600954231240181</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1117470725402959</v>
+        <v>0.1928210500316553</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.541832077405786</v>
+        <v>3.613639311801915</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.475994368400552</v>
+        <v>3.499157216301865</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.115559799543252</v>
+        <v>-5.034485822051892</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.429414024269503</v>
+        <v>1.48500646316736</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1117470725402959</v>
+        <v>0.1928210500316553</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.54304261192473</v>
+        <v>3.614849846320858</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.480116110627873</v>
+        <v>3.503278958529186</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.30222392767806</v>
+        <v>-5.2211499501867</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.358870115242901</v>
+        <v>1.414462554140758</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.08500810171573603</v>
+        <v>0.1660820792070954</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.531120971657315</v>
+        <v>3.602928206053444</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916196</v>
+        <v>3.652149152916197</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.475193963364063</v>
+        <v>3.498356811265376</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.448244614592022</v>
+        <v>-5.367170637100662</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.295539693213506</v>
+        <v>1.351132132111363</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.07592500992187906</v>
+        <v>0.1569989874132384</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.52074896931719</v>
+        <v>3.592556203713319</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830324</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.637398020063107</v>
+        <v>3.66056086796442</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.539958623701608</v>
+        <v>-5.458884646210247</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.421058146268716</v>
+        <v>1.476650585166573</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.07592500992187906</v>
+        <v>0.1569989874132384</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.682953026016234</v>
+        <v>3.754760260412363</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071546</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.632244658026921</v>
+        <v>3.655407505928234</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.571610282761577</v>
+        <v>-5.634548572289529</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.403244120608542</v>
+        <v>1.401231652698674</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.07075655267743886</v>
+        <v>0.09445723622959329</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.674698589633385</v>
+        <v>3.71208184766599</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868141</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.642474075595412</v>
+        <v>3.665636923496725</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.640676337334514</v>
+        <v>-5.703614626862466</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.385847116347859</v>
+        <v>1.383834648437991</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.008385675183828822</v>
+        <v>0.03208635873598326</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.64750548070571</v>
+        <v>3.684888738738315</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332686</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.651399714051315</v>
+        <v>3.674562561952627</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.742652459582922</v>
+        <v>-5.805590749110873</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.353982305904398</v>
+        <v>1.35196983799453</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.09359044706457875</v>
+        <v>-0.06988976351242432</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.595245445812568</v>
+        <v>3.632628703845173</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231803</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.64355260129549</v>
+        <v>3.666715449196803</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.6326461761057</v>
+        <v>-5.695584465633652</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.390137706539462</v>
+        <v>1.388125238629594</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.07038587514730354</v>
+        <v>-0.04668519159514911</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.601321076207108</v>
+        <v>3.638704334239713</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818517</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.647802612017464</v>
+        <v>3.670965459918777</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.489586600364774</v>
+        <v>-5.552524889892727</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.451611547557807</v>
+        <v>1.449599079647939</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.06237244855732427</v>
+        <v>-0.03867176500516983</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.61037914288307</v>
+        <v>3.647762400915675</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051783</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.6550634949</v>
+        <v>3.678226342801313</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.188139874892936</v>
+        <v>-5.251078164420889</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.579451120629078</v>
+        <v>1.57743865271921</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.239074276914513</v>
+        <v>0.2627749604666674</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.798508061048708</v>
+        <v>3.835891319081314</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679621</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.656034672652711</v>
+        <v>3.679197520554024</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.21273011912812</v>
+        <v>-5.275668408656073</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.570586200687715</v>
+        <v>1.568573732777847</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.239074276914513</v>
+        <v>0.2627749604666674</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.799479238801419</v>
+        <v>3.836862496834025</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.656877577032466</v>
+        <v>3.680040424933779</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.1616917431216</v>
+        <v>-5.224630032649553</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.591844455470079</v>
+        <v>1.58983198756021</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.239074276914513</v>
+        <v>0.2627749604666674</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.800322143181174</v>
+        <v>3.83770540121378</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969539</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.675915675906612</v>
+        <v>3.699078523807925</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.13284306629814</v>
+        <v>-5.195781355826092</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.622422025073608</v>
+        <v>1.62040955716374</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2679229537379733</v>
+        <v>0.2916236372901277</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.836669448149396</v>
+        <v>3.874052706182002</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700473</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.492099672030546</v>
+        <v>3.515262519931859</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.0362081542795</v>
+        <v>-5.099146443807452</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.477259986004999</v>
+        <v>1.47524751809513</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3645578657566132</v>
+        <v>0.3882585493087676</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.710834391484514</v>
+        <v>3.74821764951712</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077635</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.495601716104511</v>
+        <v>3.518764564005823</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.967170143331032</v>
+        <v>-5.030108432858984</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.50837723445835</v>
+        <v>1.506364766548482</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4335958767050813</v>
+        <v>0.4572965602572357</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.75575924212756</v>
+        <v>3.793142500160165</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.480028535180593</v>
+        <v>3.503191383081906</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.80267380914007</v>
+        <v>-4.865612098668023</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.558602587210817</v>
+        <v>1.556590119300949</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5980922108960431</v>
+        <v>0.6217928944481976</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.838883861718219</v>
+        <v>3.876267119750825</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.479216245617023</v>
+        <v>3.502379093518336</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.725575207598197</v>
+        <v>-4.78851349712615</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.588629738263996</v>
+        <v>1.586617270354128</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5980922108960431</v>
+        <v>0.6217928944481976</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.838071572154649</v>
+        <v>3.875454830187254</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.489085024742095</v>
+        <v>3.512247872643408</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.735960402488087</v>
+        <v>-4.798898692016039</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.594344439433113</v>
+        <v>1.592331971523244</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5877070160061538</v>
+        <v>0.6114076995583083</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.841709234345788</v>
+        <v>3.879092492378393</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735279</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.55992203051852</v>
+        <v>3.583084878419833</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.754548561210312</v>
+        <v>-4.817486850738264</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.657746181720648</v>
+        <v>1.655733713810779</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5691188572839285</v>
+        <v>0.592819540836083</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.901393344888878</v>
+        <v>3.938776602921483</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.556791041336819</v>
+        <v>3.579953889238132</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.754847107906348</v>
+        <v>-4.8177853974343</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.654495773860532</v>
+        <v>1.652483305950664</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5688203105878926</v>
+        <v>0.5925209941400471</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.898083227689555</v>
+        <v>3.93546648572216</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108852</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.56132193627621</v>
+        <v>3.584484784177523</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.65402397421592</v>
+        <v>-4.716962263743873</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.699355922276094</v>
+        <v>1.697343454366226</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5812845260722465</v>
+        <v>0.6049852096244009</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.910092651919558</v>
+        <v>3.947475909952164</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121461</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.561451189754754</v>
+        <v>3.584614037656066</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.463242613463512</v>
+        <v>-4.526180902991465</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.775797720055601</v>
+        <v>1.773785252145732</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7720658868246538</v>
+        <v>0.7957665703768083</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.024690721849546</v>
+        <v>4.062073979882152</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906074</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.54128803549235</v>
+        <v>3.564450883393663</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.356279255614091</v>
+        <v>-4.419217545142043</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.798419908932966</v>
+        <v>1.796407441023098</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8305304947844553</v>
+        <v>0.8542311783366098</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.039606332363023</v>
+        <v>4.076989590395629</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.78576168591298</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.576254972104409</v>
+        <v>3.599417820005721</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.300948667712328</v>
+        <v>-4.363886957240281</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.855519080705729</v>
+        <v>1.853506612795861</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8858610826862174</v>
+        <v>0.9095617662383719</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.10777162171614</v>
+        <v>4.145154879748745</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539889</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.569941540005846</v>
+        <v>3.593104387907159</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.288894540799365</v>
+        <v>-4.351832830327318</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.854027299372352</v>
+        <v>1.852014831462484</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8979152095991803</v>
+        <v>0.9216158931513347</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.108690665765355</v>
+        <v>4.14607392379796</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811007</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.571822170189982</v>
+        <v>3.594985018091295</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.330049660367586</v>
+        <v>-4.392987949895539</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.8394458817292</v>
+        <v>1.837433413819332</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8567600900309593</v>
+        <v>0.8804607735831138</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.085878224208558</v>
+        <v>4.123261482241164</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382914</v>
+        <v>3.612322444382918</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.584673196067865</v>
+        <v>3.607836043969177</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.262001097676056</v>
+        <v>-4.324939387204009</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.879516332683694</v>
+        <v>1.877503864773826</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9248086527224891</v>
+        <v>0.9485093362746436</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.139558387701358</v>
+        <v>4.176941645733963</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013421</v>
+        <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.604875866241459</v>
+        <v>3.628038714142772</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.493601490845557</v>
+        <v>-4.55653978037351</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.807078845589488</v>
+        <v>1.80506637767962</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9248086527224891</v>
+        <v>0.9485093362746436</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.159761057874952</v>
+        <v>4.197144315907558</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498967</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.588482102308341</v>
+        <v>3.611644950209654</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.543653036374776</v>
+        <v>-4.606591325902729</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.770664463444682</v>
+        <v>1.768651995534814</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9248086527224891</v>
+        <v>0.9485093362746436</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.143367293941835</v>
+        <v>4.18075055197444</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800095</v>
+        <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.548734015901807</v>
+        <v>3.57189686380312</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.718759868951221</v>
+        <v>-4.781698158479173</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.660873644007571</v>
+        <v>1.658861176097703</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9248086527224891</v>
+        <v>0.9485093362746436</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.103619207535301</v>
+        <v>4.141002465567906</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.555756634898747</v>
+        <v>3.57891948280006</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.522659715520698</v>
+        <v>-4.58559800504865</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.74633632437672</v>
+        <v>1.744323856466852</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.120908806153012</v>
+        <v>1.144609489705167</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.228301918590555</v>
+        <v>4.265685176623161</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.654927634471652</v>
+        <v>3.678090482372965</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.369634323407413</v>
+        <v>-4.432572612935366</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.906717480794939</v>
+        <v>1.90470501288507</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.273934198266296</v>
+        <v>1.297634881818451</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.41928815343143</v>
+        <v>4.456671411464035</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.842393859379944</v>
+        <v>3.865556707281257</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.397941637280684</v>
+        <v>-4.460879926808636</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.082860780153923</v>
+        <v>2.080848312244055</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.273934198266296</v>
+        <v>1.297634881818451</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.606754378339723</v>
+        <v>4.644137636372328</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.811796810734027</v>
+        <v>3.83495965863534</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.564534862394206</v>
+        <v>-4.627473151922159</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.985626441462597</v>
+        <v>1.983613973552729</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.107340973152773</v>
+        <v>1.131041656704928</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.476201394625692</v>
+        <v>4.513584652658297</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.815473213395745</v>
+        <v>3.838636061297058</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.54149906903264</v>
+        <v>-4.604437358560593</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.998517161468941</v>
+        <v>1.996504693559073</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.107340973152773</v>
+        <v>1.131041656704928</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.47987779728741</v>
+        <v>4.517261055320015</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.81309126851924</v>
+        <v>3.836254116420553</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.512253088576943</v>
+        <v>-4.575191378104896</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.007833608774715</v>
+        <v>2.005821140864847</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.107340973152773</v>
+        <v>1.131041656704928</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.477495852410905</v>
+        <v>4.51487911044351</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.810384507676875</v>
+        <v>3.833547355578188</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.619178636454794</v>
+        <v>-4.682116925982747</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.96235662878121</v>
+        <v>1.960344160871341</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.000415425274922</v>
+        <v>1.024116108827077</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.410633762841829</v>
+        <v>4.448017020874435</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.811813309820109</v>
+        <v>3.834976157721422</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.764197194962043</v>
+        <v>-4.827135484489996</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.905778007521544</v>
+        <v>1.903765539611676</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.8553968667676737</v>
+        <v>0.8790975503198284</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.325051429880714</v>
+        <v>4.36243468791332</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687011</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.911744549077862</v>
+        <v>3.934907396979175</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.882538960746761</v>
+        <v>-4.945477250274713</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.95837254046541</v>
+        <v>1.956360072555541</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.8660829053305638</v>
+        <v>0.8897835888827185</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.431394292276201</v>
+        <v>4.468777550308806</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790801</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.909530246203802</v>
+        <v>3.932693094105113</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.933949383067469</v>
+        <v>-4.996887672595421</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.935594068663066</v>
+        <v>1.933581600753197</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.8660829053305638</v>
+        <v>0.8897835888827185</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.42917998940214</v>
+        <v>4.466563247434745</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437327</v>
+        <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.909433374278091</v>
+        <v>3.932596222179403</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.01336883427522</v>
+        <v>-5.076307123803173</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.903729416254254</v>
+        <v>1.901716948344386</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.8660829053305638</v>
+        <v>0.8897835888827185</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.429083117476429</v>
+        <v>4.466466375509034</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.909427267836134</v>
+        <v>3.932590115737447</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.108831832192438</v>
+        <v>-5.171770121720391</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.865538110645411</v>
+        <v>1.863525642735542</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.8660829053305638</v>
+        <v>0.8897835888827185</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.429077011034472</v>
+        <v>4.466460269067078</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.907523664398744</v>
+        <v>3.930686512300057</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.044455921341723</v>
+        <v>-5.107394210869676</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.889384871548307</v>
+        <v>1.887372403638439</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.9304588161812789</v>
+        <v>0.9541594997334336</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.465798954107512</v>
+        <v>4.503182212140118</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.913257482146471</v>
+        <v>3.936420330047784</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.099825083473917</v>
+        <v>-5.162763373001869</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.872971024443156</v>
+        <v>1.870958556533288</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.9304588161812789</v>
+        <v>0.9541594997334336</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.471532771855238</v>
+        <v>4.508916029887844</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.912795845489403</v>
+        <v>3.935958693390717</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.118043550471525</v>
+        <v>-5.180981839999478</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.865222000987045</v>
+        <v>1.863209533077177</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9053523789254367</v>
+        <v>0.9290530624775915</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.456007272844666</v>
+        <v>4.493390530877272</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.932670238339722</v>
+        <v>3.955833086241036</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.029836716323947</v>
+        <v>-5.0927750058519</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.920379127496395</v>
+        <v>1.918366659586528</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9053523789254367</v>
+        <v>0.9290530624775915</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.475881665694985</v>
+        <v>4.513264923727591</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.91637093886445</v>
+        <v>3.939533786765764</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.923801721118638</v>
+        <v>-4.98674001064659</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.946493826103247</v>
+        <v>1.94448135819338</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9053523789254367</v>
+        <v>0.9290530624775915</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.459582366219712</v>
+        <v>4.496965624252319</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.918801888328495</v>
+        <v>3.941964736229809</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.740590057985543</v>
+        <v>-4.803528347513495</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.02220944082053</v>
+        <v>2.020196972910663</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9053523789254367</v>
+        <v>0.9290530624775915</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.462013315683758</v>
+        <v>4.499396573716364</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.901746294407872</v>
+        <v>3.924909142309186</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.668868610971692</v>
+        <v>-4.731806900499644</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.033842425705448</v>
+        <v>2.031829957795581</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.9770738259392874</v>
+        <v>1.000774509491442</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.487990589971445</v>
+        <v>4.525373848004052</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.848662040329044</v>
+        <v>3.871824888230358</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.646495585363986</v>
+        <v>-4.709433874891938</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.989707381869702</v>
+        <v>1.987694913959834</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.9883295770521889</v>
+        <v>1.012030260604344</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.441659786560358</v>
+        <v>4.479043044592965</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.0338602452144</v>
+        <v>4.057023093115713</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.67951188127473</v>
+        <v>-4.742450170802683</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.161699068390759</v>
+        <v>2.159686600480892</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9188922003854374</v>
+        <v>0.9425928839375921</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.585195565445662</v>
+        <v>4.622578823478269</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.025781471042649</v>
+        <v>4.048944318943962</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.667984245625122</v>
+        <v>-4.730922535153074</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.158231348478852</v>
+        <v>2.156218880568985</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.9778928585867999</v>
+        <v>1.001593542138955</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.612517186194729</v>
+        <v>4.649900444227336</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.029449583564437</v>
+        <v>4.052612431465751</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.76532574696749</v>
+        <v>-4.828264036495443</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.122962860463693</v>
+        <v>2.120950392553826</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.9334726764213115</v>
+        <v>0.9571733599734662</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.589533189417224</v>
+        <v>4.626916447449831</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942768</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.030700665757275</v>
+        <v>4.053863513658589</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.851181776307457</v>
+        <v>-4.91412006583541</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.089871530920544</v>
+        <v>2.087859063010677</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.8910966071951765</v>
+        <v>0.9147972907473312</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.565358630074382</v>
+        <v>4.602741888106988</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.013119867577777</v>
+        <v>4.036282715479091</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.860018573723576</v>
+        <v>-4.922956863251529</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.068756013774599</v>
+        <v>2.066743545864731</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.8836544345538258</v>
+        <v>0.9073551181059805</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.543312528310073</v>
+        <v>4.580695786342679</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.023284378622827</v>
+        <v>4.04644722652414</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.951401136289035</v>
+        <v>-5.014339425816988</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.042367499793465</v>
+        <v>2.040355031883597</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.847089549834481</v>
+        <v>0.8707902333866357</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.531538108523516</v>
+        <v>4.568921366556122</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889187</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.125412636447095</v>
+        <v>4.148575484348408</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.939694418302029</v>
+        <v>-5.002632707829981</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.149178444812535</v>
+        <v>2.147165976902667</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.8587962678214874</v>
+        <v>0.8824969513736421</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.640690397139988</v>
+        <v>4.678073655172593</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409565</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.1284449751785</v>
+        <v>4.151607823079813</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.010606492044307</v>
+        <v>-5.073544781572259</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.123845954047029</v>
+        <v>2.121833486137161</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.8587962678214874</v>
+        <v>0.8824969513736421</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.643722735871393</v>
+        <v>4.681105993903998</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.341349808456558</v>
+        <v>4.364512656357871</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.020922590210659</v>
+        <v>-5.083860879738611</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.332624348058546</v>
+        <v>2.330611880148678</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.8587962678214874</v>
+        <v>0.8824969513736421</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.856627569149451</v>
+        <v>4.894010827182056</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.340528475368647</v>
+        <v>4.36369132326996</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.020828622193286</v>
+        <v>-5.083766911721239</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.331840602177585</v>
+        <v>2.329828134267717</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.8591661291688054</v>
+        <v>0.8828668127209601</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.856028152869931</v>
+        <v>4.893411410902536</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988013</v>
+        <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.334760461313001</v>
+        <v>4.357923309214314</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.169194849849431</v>
+        <v>-5.232133139377384</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.266726097059481</v>
+        <v>2.264713629149613</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.8591661291688054</v>
+        <v>0.8828668127209601</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.850260138814285</v>
+        <v>4.88764339684689</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.334760461313001</v>
+        <v>4.357923309214314</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.168246426731392</v>
+        <v>-5.231184716259345</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.267105466306696</v>
+        <v>2.265092998396828</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.8591661291688054</v>
+        <v>0.8828668127209601</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.850260138814285</v>
+        <v>4.88764339684689</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.347488069294093</v>
+        <v>4.370650917195406</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.268516244690414</v>
+        <v>-5.331454534218366</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.23972514710418</v>
+        <v>2.237712679194312</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.8591661291688054</v>
+        <v>0.8828668127209601</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.862987746795377</v>
+        <v>4.900371004827982</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.349434067718481</v>
+        <v>4.372596915619794</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.262523997901602</v>
+        <v>-5.325462287429555</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.244068044244092</v>
+        <v>2.242055576334224</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.8591661291688054</v>
+        <v>0.8828668127209601</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.864933745219765</v>
+        <v>4.90231700325237</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.34308820373625</v>
+        <v>4.366251051637563</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.173966036770834</v>
+        <v>-5.236904326298787</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.273145364714168</v>
+        <v>2.2711328968043</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.8591661291688054</v>
+        <v>0.8828668127209601</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.858587881237534</v>
+        <v>4.895971139270139</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.342396881175246</v>
+        <v>4.365559729076558</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.15620695926776</v>
+        <v>-5.219145248795713</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.279557673154394</v>
+        <v>2.277545205244525</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.8591661291688054</v>
+        <v>0.8828668127209601</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.857896558676529</v>
+        <v>4.895279816709134</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.355179067083832</v>
+        <v>4.378341914985145</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.056576808218693</v>
+        <v>-5.119515097746645</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.332191919482607</v>
+        <v>2.330179451572739</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.9587962802178729</v>
+        <v>0.9824969637700276</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.930456835214557</v>
+        <v>4.967840093247162</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.544333332582559</v>
+        <v>4.567496180483872</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.105976316907704</v>
+        <v>-5.168914606435656</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.501586381505729</v>
+        <v>2.499573913595861</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.9690551136496176</v>
+        <v>0.9927557972017724</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.12576640077233</v>
+        <v>5.163149658804936</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.531522005685421</v>
+        <v>4.554684853586734</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.899291843265328</v>
+        <v>-4.96223013279328</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.571448844065542</v>
+        <v>2.569436376155673</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.175739587291993</v>
+        <v>1.199440270844148</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.236965758060617</v>
+        <v>5.274349016093223</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.533523519339526</v>
+        <v>4.556686367240839</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.933448738262854</v>
+        <v>-4.996387027790806</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.559787599720636</v>
+        <v>2.557775131810768</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.092155817751181</v>
+        <v>1.115856501303336</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.188817009990235</v>
+        <v>5.22620026802284</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652381</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.887020633329193</v>
+        <v>4.910183481230506</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.007966212228576</v>
+        <v>-4.90379754872935</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.883477724124015</v>
+        <v>2.948308037425018</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.092155817751181</v>
+        <v>1.115856501303336</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.542314123979902</v>
+        <v>5.579697382012508</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108669</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.891583744896296</v>
+        <v>4.914746592797609</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.067854840052126</v>
+        <v>-4.9636861765529</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.864085384561698</v>
+        <v>2.928915697862701</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.078033903063716</v>
+        <v>1.101734586615871</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.538404086734526</v>
+        <v>5.575787344767132</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.83520244110356</v>
+        <v>3.835202441103562</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.941413686219824</v>
+        <v>4.964576534121137</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.015638530255784</v>
+        <v>-4.911469866756558</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.934801849803762</v>
+        <v>2.999632163104765</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.078033903063716</v>
+        <v>1.101734586615871</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.588234028058054</v>
+        <v>5.62561728609066</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.950227656429835</v>
+        <v>4.973390504331148</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.983741013170539</v>
+        <v>-4.879572349671313</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.956374826847871</v>
+        <v>3.021205140148875</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.109931420148962</v>
+        <v>1.133632103701117</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.616186508519212</v>
+        <v>5.653569766551818</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650751</v>
+        <v>3.825268416650753</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.945865240469032</v>
+        <v>4.969028088370345</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.998496337370679</v>
+        <v>-4.894327673871453</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.946110281207012</v>
+        <v>3.010940594508015</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.109931420148962</v>
+        <v>1.133632103701117</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.611824092558409</v>
+        <v>5.649207350591015</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135745</v>
+        <v>3.845044666135748</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.936789743885312</v>
+        <v>4.959952591786625</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.949031714000768</v>
+        <v>-4.844863050501542</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.956820633971256</v>
+        <v>3.02165094727226</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.159396043518874</v>
+        <v>1.183096727071028</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.632427369996636</v>
+        <v>5.669810628029242</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479219</v>
+        <v>3.825931790479221</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.933197411600246</v>
+        <v>4.956360259501559</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.785923721847152</v>
+        <v>-4.681755058347926</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.018471498547637</v>
+        <v>3.08330181184864</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.322504035672489</v>
+        <v>1.346204719224644</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.72669983300374</v>
+        <v>5.764083091036346</v>
       </c>
     </row>
     <row r="2097">
@@ -49779,19 +49779,19 @@
         <v>3.847096478844243</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.942244448291374</v>
+        <v>4.965407296192687</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.653116096349986</v>
+        <v>-4.54894743285076</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.080641585437632</v>
+        <v>3.145471898738635</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.322504035672489</v>
+        <v>1.346204719224644</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.735746869694868</v>
+        <v>5.773130127727473</v>
       </c>
     </row>
     <row r="2098">
@@ -49802,19 +49802,19 @@
         <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.943101913277496</v>
+        <v>4.966264761178809</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.715824012824544</v>
+        <v>-4.611655349325318</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.05641588383393</v>
+        <v>3.121246197134933</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.259796119197931</v>
+        <v>1.283496802750086</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.698979584796255</v>
+        <v>5.736362842828861</v>
       </c>
     </row>
     <row r="2099">
@@ -49825,19 +49825,19 @@
         <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.906011330067848</v>
+        <v>4.929174177969161</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.667815888980851</v>
+        <v>-4.563647225481625</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.03852855016176</v>
+        <v>3.103358863462763</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.259796119197931</v>
+        <v>1.283496802750086</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.661889001586607</v>
+        <v>5.699272259619213</v>
       </c>
     </row>
     <row r="2100">
@@ -49848,19 +49848,19 @@
         <v>3.872253907629881</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.909943583625799</v>
+        <v>4.933106431527111</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.58899023179726</v>
+        <v>-4.484821568298035</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.073991066593146</v>
+        <v>3.13882137989415</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.338621776381522</v>
+        <v>1.362322459933676</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.713116649454712</v>
+        <v>5.750499907487318</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686402</v>
+        <v>3.868502531686403</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.904842676232835</v>
+        <v>4.928005524134148</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.397055430543387</v>
+        <v>-4.292886767044161</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.145664079701733</v>
+        <v>3.210494393002736</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.338621776381522</v>
+        <v>1.362322459933676</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.708015742061749</v>
+        <v>5.745399000094355</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.885204719135551</v>
+        <v>3.763036575344223</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.901940634414091</v>
+        <v>4.839643911352353</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.397055430543387</v>
+        <v>-4.292886767044161</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.145664079701733</v>
+        <v>3.210494393002736</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.338621776381522</v>
+        <v>1.362322459933676</v>
       </c>
       <c r="G2102" t="n">
-        <v>4.895004431400459</v>
+        <v>4.832707708338721</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240929.xlsx
+++ b/tame_output/ON/bt/strategyON_20240929.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>109.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>172.3%</t>
+          <t>169.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>122.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-70.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.9%</t>
+          <t>422.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-590.9%</t>
+          <t>-585.5%</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-55.2%</t>
+          <t>-55.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-263.3%</t>
+          <t>-301.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-87.8%</t>
+          <t>-82.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,21 +1433,21 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>34.5%</t>
         </is>
       </c>
     </row>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.525846080669123</v>
+        <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.231800557537802</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.832769433340254</v>
+        <v>0.8096065854389407</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2600134425243301</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.681854146183721</v>
+        <v>2.658691298282408</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.592181634465944</v>
+        <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.16950255876168</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9240241866475238</v>
+        <v>0.9008613387462105</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3053077067987721</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.775366258545207</v>
+        <v>2.752203410643894</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.394473636180071</v>
+        <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.967712361096522</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8070322674277142</v>
+        <v>0.7838694195264009</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5033258989679266</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.696469175560827</v>
+        <v>2.673306327659514</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.464763868502246</v>
+        <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.018599073782717</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8569678146754114</v>
+        <v>0.8338049667740981</v>
       </c>
       <c r="F1972" t="n">
         <v>0.452439186281732</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.736227380271286</v>
+        <v>2.713064532369972</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.47939160461829</v>
+        <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
         <v>-3.93198833113291</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.906239847851378</v>
+        <v>0.8830769999500647</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5310649174868902</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.798030555110424</v>
+        <v>2.774867707209111</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.477927585442961</v>
+        <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
         <v>-3.992197629138194</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8806921094739359</v>
+        <v>0.8575292615726227</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4708556194816057</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.760440957131925</v>
+        <v>2.737278109230612</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.47641920348289</v>
+        <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.943010980453843</v>
+        <v>-4.033503754937939</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.898858386987605</v>
+        <v>0.8394984292926531</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4708556194816057</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.758932575171854</v>
+        <v>2.735769727270541</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.476282070918326</v>
+        <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.898637848815274</v>
+        <v>-3.989130623299371</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9164705070784687</v>
+        <v>0.8571105493835167</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5152287511201743</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.785419321590431</v>
+        <v>2.762256473689118</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.470675865056917</v>
+        <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.863906527496773</v>
+        <v>-3.95439930198087</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9247568297444595</v>
+        <v>0.8653968720495075</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5152287511201743</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.779813115729022</v>
+        <v>2.756650267827708</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.477057622084721</v>
+        <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.816250796935718</v>
+        <v>-3.906743571419814</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9502008789966858</v>
+        <v>0.8908409213017343</v>
       </c>
       <c r="F1978" t="n">
         <v>0.56288448168123</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.814788311093459</v>
+        <v>2.791625463192146</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.481949995459446</v>
+        <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.715732638436963</v>
+        <v>-3.80622541292106</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9953005157709125</v>
+        <v>0.935940558075961</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6634026401799845</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.879991579567437</v>
+        <v>2.856828731666124</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.468704667935318</v>
+        <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.69982730900461</v>
+        <v>-3.790320083488707</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9884173200197259</v>
+        <v>0.9290573623247744</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5842899794707457</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.819278655617766</v>
+        <v>2.796115807716453</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.472802370545947</v>
+        <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.654988907396212</v>
+        <v>-3.745481681880309</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.010450383273714</v>
+        <v>0.9510904255787622</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5888334124156152</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.826102417995316</v>
+        <v>2.802939570094003</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.476963310177025</v>
+        <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.67448736363822</v>
+        <v>-3.764980138122317</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.006811940407988</v>
+        <v>0.9474519827130368</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5407487711357108</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.801412572858451</v>
+        <v>2.778249724957139</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.482842912704862</v>
+        <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.63028452655232</v>
+        <v>-3.720777301036417</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.030372677770186</v>
+        <v>0.9710127200752341</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5849516082216113</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.833813877637829</v>
+        <v>2.810651029736516</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.481252913174109</v>
+        <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.637844192389367</v>
+        <v>-3.728336966873464</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.025758811904614</v>
+        <v>0.9663988542096629</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6397550122314306</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.865105920512968</v>
+        <v>2.841943072611655</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.532500678357149</v>
+        <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.479552774850095</v>
+        <v>-3.570045549334191</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.140323144103363</v>
+        <v>1.080963186408411</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6397550122314306</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.916353685696008</v>
+        <v>2.893190837794695</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.530941382951402</v>
+        <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.271910771215619</v>
+        <v>-3.362403545699715</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.221820650151407</v>
+        <v>1.162460692456455</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8473970158659068</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.039379592470946</v>
+        <v>3.016216744569634</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.525889611189672</v>
+        <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.220878678493091</v>
+        <v>-3.311371452977187</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.237181715478688</v>
+        <v>1.177821757783736</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8984291085884347</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.064947076342733</v>
+        <v>3.04178422844142</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.543077015282377</v>
+        <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.155654497365885</v>
+        <v>-3.246147271849981</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.280458792022275</v>
+        <v>1.221098834327324</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9636532897156403</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.121268989111762</v>
+        <v>3.098106141210449</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.539037987581657</v>
+        <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.118227477294751</v>
+        <v>-3.208720251778848</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.291390572350009</v>
+        <v>1.232030614655057</v>
       </c>
       <c r="F1989" t="n">
         <v>0.968904827744822</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.120380884228551</v>
+        <v>3.097218036327238</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992655</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.540294779912898</v>
+        <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.116869492321205</v>
+        <v>-3.207362266805302</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.293190558670668</v>
+        <v>1.233830600975716</v>
       </c>
       <c r="F1990" t="n">
         <v>1.043242953282641</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.166240551882482</v>
+        <v>3.143077703981169</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.700852550934108</v>
+        <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.088456229221322</v>
+        <v>-3.178949003705418</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.465113634931832</v>
+        <v>1.40575367723688</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9842673905362118</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.291412985255836</v>
+        <v>3.268250137354523</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.820965460151926</v>
+        <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.013673968196309</v>
+        <v>-3.104166742680406</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.615139448559654</v>
+        <v>1.555779490864702</v>
       </c>
       <c r="F1992" t="n">
         <v>1.059049651561224</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.456395251088661</v>
+        <v>3.433232403187348</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.812673436165785</v>
+        <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.987589883932501</v>
+        <v>-3.078082658416598</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.617281058279036</v>
+        <v>1.557921100584085</v>
       </c>
       <c r="F1993" t="n">
         <v>1.059049651561224</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.44810322710252</v>
+        <v>3.424940379201207</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.810866631749564</v>
+        <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.899711970823381</v>
+        <v>-2.990204745307477</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.650625419106464</v>
+        <v>1.591265461411512</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174975293984576</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.51585180814031</v>
+        <v>3.492688960238997</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.828421037476355</v>
+        <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.890819509430098</v>
+        <v>-2.981312283914194</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.671736809390568</v>
+        <v>1.612376851695617</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174975293984576</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.533406213867101</v>
+        <v>3.510243365965788</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.820276084880939</v>
+        <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.059295626399976</v>
+        <v>-3.149788400884072</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.596201410007201</v>
+        <v>1.53684145231225</v>
       </c>
       <c r="F1996" t="n">
         <v>1.147027458267995</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.508492559841736</v>
+        <v>3.485329711940424</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.801545782068801</v>
+        <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.613039433770536</v>
+        <v>-2.703532208254632</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.755973584246839</v>
+        <v>1.696613626551888</v>
       </c>
       <c r="F1997" t="n">
         <v>1.052308788598362</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.432931055227819</v>
+        <v>3.409768207326506</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.792209804565706</v>
+        <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.590318330087383</v>
+        <v>-2.68081110457148</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.755726048217005</v>
+        <v>1.696366090522053</v>
       </c>
       <c r="F1998" t="n">
         <v>1.052308788598362</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.423595077724723</v>
+        <v>3.40043222982341</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.951115930416875</v>
+        <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.719520143381426</v>
+        <v>-2.810012917865522</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.862951448750557</v>
+        <v>1.803591491055605</v>
       </c>
       <c r="F1999" t="n">
         <v>0.92310697530432</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.504980115599467</v>
+        <v>3.481817267698154</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.988193752910521</v>
+        <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.745394541855451</v>
+        <v>-2.835887316339548</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.889679511854593</v>
+        <v>1.830319554159641</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9680185840160611</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.569004903320158</v>
+        <v>3.545842055418845</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.984869108900067</v>
+        <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.738339851640278</v>
+        <v>-2.828832626124374</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.889176743930207</v>
+        <v>1.829816786235256</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9750732742312349</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.569913073438808</v>
+        <v>3.546750225537495</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.994875262544808</v>
+        <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.71138862731379</v>
+        <v>-2.801881401797886</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.909963387305544</v>
+        <v>1.850603429610593</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9899536202589541</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.588847434700181</v>
+        <v>3.565684586798868</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.178978394689768</v>
+        <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.732932855144577</v>
+        <v>-2.823425629628673</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.085448828318189</v>
+        <v>2.026088870623238</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9899536202589541</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.77295056684514</v>
+        <v>3.749787718943828</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.171095089592761</v>
+        <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.755340972949449</v>
+        <v>-2.845833747433546</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.068602276099234</v>
+        <v>2.009242318404282</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9899536202589541</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.765067261748134</v>
+        <v>3.741904413846821</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.173149089142398</v>
+        <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.783565208527049</v>
+        <v>-2.874057983011146</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.059366581417831</v>
+        <v>2.00000662372288</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007930372710263</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.777907312768556</v>
+        <v>3.754744464867243</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.229402806864246</v>
+        <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.793006134415579</v>
+        <v>-2.883498908899676</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.111843928784266</v>
+        <v>2.052483971089314</v>
       </c>
       <c r="F2006" t="n">
         <v>1.130357490253654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.907617301016438</v>
+        <v>3.884454453115125</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.232293901409546</v>
+        <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.881882765584053</v>
+        <v>-2.97237554006815</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.079184370862177</v>
+        <v>2.019824413167226</v>
       </c>
       <c r="F2007" t="n">
         <v>1.04148085908518</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.857182416860655</v>
+        <v>3.834019568959342</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.230405714303322</v>
+        <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.958212743184959</v>
+        <v>-3.048705517669056</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.04676419271559</v>
+        <v>1.987404235020638</v>
       </c>
       <c r="F2008" t="n">
         <v>1.04148085908518</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.85529422975443</v>
+        <v>3.832131381853117</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.225225943906184</v>
+        <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.113169528585088</v>
+        <v>-3.203662303069185</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.979601708158401</v>
+        <v>1.920241750463449</v>
       </c>
       <c r="F2009" t="n">
         <v>0.886524073685051</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.757140388117215</v>
+        <v>3.733977540215902</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.223659954116336</v>
+        <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.274737954112343</v>
+        <v>-3.36523072859644</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.913408348157651</v>
+        <v>1.854048390462699</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7597411498871717</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.679504644048639</v>
+        <v>3.656341796147327</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.236733360982255</v>
+        <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.383038615982463</v>
+        <v>-3.473531390466559</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.883161490275522</v>
+        <v>1.82380153258057</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7597411498871717</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.692578050914558</v>
+        <v>3.669415203013245</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.228738557765195</v>
+        <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.400842587703207</v>
+        <v>-3.491335362187304</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.868045098370164</v>
+        <v>1.808685140675212</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6892065269819705</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.642262473954377</v>
+        <v>3.619099626053064</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.227262598892197</v>
+        <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.42874337481268</v>
+        <v>-3.519236149296777</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.855408824653377</v>
+        <v>1.796048866958425</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6546096028390357</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.620028360595618</v>
+        <v>3.596865512694305</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.224027042869396</v>
+        <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.551269477515574</v>
+        <v>-3.64176225199967</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.803162827549418</v>
+        <v>1.743802869854467</v>
       </c>
       <c r="F2014" t="n">
         <v>0.5320835001361418</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.543277142951081</v>
+        <v>3.520114295049768</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.290733002459899</v>
+        <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.781783973701162</v>
+        <v>-3.872276748185259</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.777662988665687</v>
+        <v>1.718303030970735</v>
       </c>
       <c r="F2015" t="n">
         <v>0.3015690039505531</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.471674404830231</v>
+        <v>3.448511556928918</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.431044721461746</v>
+        <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.130529058925606</v>
+        <v>-4.221021833409702</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.778476673577756</v>
+        <v>1.719116715882804</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1928210500316553</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.54673735148074</v>
+        <v>3.523574503579427</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.500024990607386</v>
+        <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.284515476701746</v>
+        <v>-4.375008251185843</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.78586237561294</v>
+        <v>1.726502417917988</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1928210500316553</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.61571762062638</v>
+        <v>3.592554772725067</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.486076192727507</v>
+        <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.489114911564755</v>
+        <v>-4.579607686048852</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.690073803787857</v>
+        <v>1.630713846092906</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1928210500316553</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.601768822746501</v>
+        <v>3.578605974845188</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.497946681782921</v>
+        <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.741590065572479</v>
+        <v>-4.832082840056576</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.600954231240181</v>
+        <v>1.54159427354523</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1928210500316553</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.613639311801915</v>
+        <v>3.590476463900602</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.499157216301865</v>
+        <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.034485822051892</v>
+        <v>-5.124978596535988</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.48500646316736</v>
+        <v>1.425646505472409</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1928210500316553</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.614849846320858</v>
+        <v>3.591686998419545</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.503278958529186</v>
+        <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.2211499501867</v>
+        <v>-5.311642724670796</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.414462554140758</v>
+        <v>1.355102596445807</v>
       </c>
       <c r="F2021" t="n">
         <v>0.1660820792070954</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.602928206053444</v>
+        <v>3.579765358152131</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916197</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.498356811265376</v>
+        <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.367170637100662</v>
+        <v>-5.457663411584758</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.351132132111363</v>
+        <v>1.291772174416411</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1569989874132384</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.592556203713319</v>
+        <v>3.569393355812006</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.66056086796442</v>
+        <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.458884646210247</v>
+        <v>-5.549377420694343</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.476650585166573</v>
+        <v>1.417290627471622</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1569989874132384</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.754760260412363</v>
+        <v>3.73159741251105</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.655407505928234</v>
+        <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.634548572289529</v>
+        <v>-5.581029079754313</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.401231652698674</v>
+        <v>1.399476601811448</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.09445723622959329</v>
+        <v>0.1518305301687982</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.71208184766599</v>
+        <v>3.7233429761282</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.665636923496725</v>
+        <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.703614626862466</v>
+        <v>-5.650095134327249</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.383834648437991</v>
+        <v>1.382079597550764</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.03208635873598326</v>
+        <v>0.08945965267518818</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.684888738738315</v>
+        <v>3.696149867200525</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.674562561952627</v>
+        <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.805590749110873</v>
+        <v>-5.752071256575657</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.35196983799453</v>
+        <v>1.350214787107304</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.06988976351242432</v>
+        <v>-0.01251646957321939</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.632628703845173</v>
+        <v>3.643889832307383</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231808</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.666715449196803</v>
+        <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.695584465633652</v>
+        <v>-5.642064973098435</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.388125238629594</v>
+        <v>1.386370187742368</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.04668519159514911</v>
+        <v>0.01068810234405582</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.638704334239713</v>
+        <v>3.649965462701924</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.670965459918777</v>
+        <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.552524889892727</v>
+        <v>-5.499005397357509</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.449599079647939</v>
+        <v>1.447844028760713</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.03867176500516983</v>
+        <v>0.01870152893403509</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.647762400915675</v>
+        <v>3.659023529377885</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.678226342801313</v>
+        <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.251078164420889</v>
+        <v>-5.197558671885671</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.57743865271921</v>
+        <v>1.575683601831984</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2627749604666674</v>
+        <v>0.3201482544058724</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.835891319081314</v>
+        <v>3.847152447543524</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.679197520554024</v>
+        <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.275668408656073</v>
+        <v>-5.222148916120855</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.568573732777847</v>
+        <v>1.566818681890621</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2627749604666674</v>
+        <v>0.3201482544058724</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.836862496834025</v>
+        <v>3.848123625296235</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.680040424933779</v>
+        <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.224630032649553</v>
+        <v>-5.171110540114335</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.58983198756021</v>
+        <v>1.588076936672985</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2627749604666674</v>
+        <v>0.3201482544058724</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.83770540121378</v>
+        <v>3.84896652967599</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.699078523807925</v>
+        <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.195781355826092</v>
+        <v>-5.142261863290875</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.62040955716374</v>
+        <v>1.618654506276514</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2916236372901277</v>
+        <v>0.3489969312293326</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.874052706182002</v>
+        <v>3.885313834644212</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.515262519931859</v>
+        <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.099146443807452</v>
+        <v>-5.045626951272235</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.47524751809513</v>
+        <v>1.473492467207905</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3882585493087676</v>
+        <v>0.4456318432479726</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.74821764951712</v>
+        <v>3.75947877797933</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.518764564005823</v>
+        <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.030108432858984</v>
+        <v>-4.976588940323767</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.506364766548482</v>
+        <v>1.504609715661256</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4572965602572357</v>
+        <v>0.5146698541964406</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.793142500160165</v>
+        <v>3.804403628622375</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.503191383081906</v>
+        <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.865612098668023</v>
+        <v>-4.812092606132805</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.556590119300949</v>
+        <v>1.554835068413723</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6217928944481976</v>
+        <v>0.6791661883874025</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.876267119750825</v>
+        <v>3.887528248213035</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.502379093518336</v>
+        <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.78851349712615</v>
+        <v>-4.734994004590932</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.586617270354128</v>
+        <v>1.584862219466902</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6217928944481976</v>
+        <v>0.6791661883874025</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.875454830187254</v>
+        <v>3.886715958649464</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.512247872643408</v>
+        <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.798898692016039</v>
+        <v>-4.745379199480822</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.592331971523244</v>
+        <v>1.590576920636019</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6114076995583083</v>
+        <v>0.6687809934975132</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.879092492378393</v>
+        <v>3.890353620840604</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735279</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.583084878419833</v>
+        <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.817486850738264</v>
+        <v>-4.763967358203047</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.655733713810779</v>
+        <v>1.653978662923554</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.592819540836083</v>
+        <v>0.6501928347752879</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.938776602921483</v>
+        <v>3.950037731383693</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.579953889238132</v>
+        <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.8177853974343</v>
+        <v>-4.764265904899083</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.652483305950664</v>
+        <v>1.650728255063438</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5925209941400471</v>
+        <v>0.649894288079252</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.93546648572216</v>
+        <v>3.94672761418437</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.584484784177523</v>
+        <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.716962263743873</v>
+        <v>-4.663442771208655</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.697343454366226</v>
+        <v>1.695588403479</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6049852096244009</v>
+        <v>0.6623585035636058</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.947475909952164</v>
+        <v>3.958737038414374</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.584614037656066</v>
+        <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.526180902991465</v>
+        <v>-4.472661410456247</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.773785252145732</v>
+        <v>1.772030201258507</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7957665703768083</v>
+        <v>0.8531398643160132</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.062073979882152</v>
+        <v>4.073335108344362</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.564450883393663</v>
+        <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.419217545142043</v>
+        <v>-4.365698052606826</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.796407441023098</v>
+        <v>1.794652390135872</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8542311783366098</v>
+        <v>0.9116044722758146</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.076989590395629</v>
+        <v>4.088250718857839</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.599417820005721</v>
+        <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.363886957240281</v>
+        <v>-4.310367464705063</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.853506612795861</v>
+        <v>1.851751561908635</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9095617662383719</v>
+        <v>0.9669350601775768</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.145154879748745</v>
+        <v>4.156416008210955</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.593104387907159</v>
+        <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.351832830327318</v>
+        <v>-4.2983133377921</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.852014831462484</v>
+        <v>1.850259780575258</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9216158931513347</v>
+        <v>0.9789891870905396</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.14607392379796</v>
+        <v>4.15733505226017</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.594985018091295</v>
+        <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.392987949895539</v>
+        <v>-4.339468457360321</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.837433413819332</v>
+        <v>1.835678362932106</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8804607735831138</v>
+        <v>0.9378340675223187</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.123261482241164</v>
+        <v>4.134522610703374</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.607836043969177</v>
+        <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.324939387204009</v>
+        <v>-4.271419894668791</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.877503864773826</v>
+        <v>1.8757488138866</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9485093362746436</v>
+        <v>1.005882630213848</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.176941645733963</v>
+        <v>4.188202774196174</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013425</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.628038714142772</v>
+        <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.55653978037351</v>
+        <v>-4.503020287838292</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.80506637767962</v>
+        <v>1.803311326792394</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9485093362746436</v>
+        <v>1.005882630213848</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.197144315907558</v>
+        <v>4.208405444369768</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.611644950209654</v>
+        <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.606591325902729</v>
+        <v>-4.553071833367511</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.768651995534814</v>
+        <v>1.766896944647588</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9485093362746436</v>
+        <v>1.005882630213848</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.18075055197444</v>
+        <v>4.19201168043665</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.57189686380312</v>
+        <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.781698158479173</v>
+        <v>-4.728178665943956</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.658861176097703</v>
+        <v>1.657106125210477</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9485093362746436</v>
+        <v>1.005882630213848</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.141002465567906</v>
+        <v>4.152263594030117</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.57891948280006</v>
+        <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.58559800504865</v>
+        <v>-4.532078512513433</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.744323856466852</v>
+        <v>1.742568805579626</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.144609489705167</v>
+        <v>1.201982783644371</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.265685176623161</v>
+        <v>4.276946305085371</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.678090482372965</v>
+        <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.432572612935366</v>
+        <v>-4.379053120400148</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.90470501288507</v>
+        <v>1.902949961997844</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.297634881818451</v>
+        <v>1.355008175757655</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.456671411464035</v>
+        <v>4.467932539926245</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.865556707281257</v>
+        <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.460879926808636</v>
+        <v>-4.407360434273419</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.080848312244055</v>
+        <v>2.079093261356829</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.297634881818451</v>
+        <v>1.355008175757655</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.644137636372328</v>
+        <v>4.655398764834538</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.83495965863534</v>
+        <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.627473151922159</v>
+        <v>-4.573953659386941</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.983613973552729</v>
+        <v>1.981858922665503</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.131041656704928</v>
+        <v>1.188414950644133</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.513584652658297</v>
+        <v>4.524845781120507</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.838636061297058</v>
+        <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.604437358560593</v>
+        <v>-4.550917866025375</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.996504693559073</v>
+        <v>1.994749642671847</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.131041656704928</v>
+        <v>1.188414950644133</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.517261055320015</v>
+        <v>4.528522183782225</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.836254116420553</v>
+        <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.575191378104896</v>
+        <v>-4.521671885569678</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.005821140864847</v>
+        <v>2.004066089977621</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.131041656704928</v>
+        <v>1.188414950644133</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.51487911044351</v>
+        <v>4.52614023890572</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.833547355578188</v>
+        <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.682116925982747</v>
+        <v>-4.628597433447529</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.960344160871341</v>
+        <v>1.958589109984116</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.024116108827077</v>
+        <v>1.081489402766282</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.448017020874435</v>
+        <v>4.459278149336645</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.834976157721422</v>
+        <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.827135484489996</v>
+        <v>-4.773615991954778</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.903765539611676</v>
+        <v>1.90201048872445</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.8790975503198284</v>
+        <v>0.936470844259033</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.36243468791332</v>
+        <v>4.37369581637553</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687011</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.934907396979175</v>
+        <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.945477250274713</v>
+        <v>-4.891957757739496</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.956360072555541</v>
+        <v>1.954605021668316</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.8897835888827185</v>
+        <v>0.9471568828219231</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.468777550308806</v>
+        <v>4.480038678771017</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790801</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.932693094105113</v>
+        <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.996887672595421</v>
+        <v>-4.943368180060204</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.933581600753197</v>
+        <v>1.931826549865972</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.8897835888827185</v>
+        <v>0.9471568828219231</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.466563247434745</v>
+        <v>4.477824375896955</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.932596222179403</v>
+        <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.076307123803173</v>
+        <v>-5.022787631267955</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.901716948344386</v>
+        <v>1.89996189745716</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.8897835888827185</v>
+        <v>0.9471568828219231</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.466466375509034</v>
+        <v>4.477727503971245</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298399</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.932590115737447</v>
+        <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.171770121720391</v>
+        <v>-5.118250629185173</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.863525642735542</v>
+        <v>1.861770591848317</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.8897835888827185</v>
+        <v>0.9471568828219231</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.466460269067078</v>
+        <v>4.477721397529288</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960218001</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.930686512300057</v>
+        <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.107394210869676</v>
+        <v>-5.053874718334458</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.887372403638439</v>
+        <v>1.885617352751213</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.9541594997334336</v>
+        <v>1.011532793672638</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.503182212140118</v>
+        <v>4.514443340602328</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353536</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.936420330047784</v>
+        <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.162763373001869</v>
+        <v>-5.109243880466652</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.870958556533288</v>
+        <v>1.869203505646062</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.9541594997334336</v>
+        <v>1.011532793672638</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.508916029887844</v>
+        <v>4.520177158350054</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113279</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.935958693390717</v>
+        <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.180981839999478</v>
+        <v>-5.12746234746426</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.863209533077177</v>
+        <v>1.861454482189951</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9290530624775915</v>
+        <v>0.986426356416796</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.493390530877272</v>
+        <v>4.504651659339482</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113688</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.955833086241036</v>
+        <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.0927750058519</v>
+        <v>-5.039255513316682</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.918366659586528</v>
+        <v>1.916611608699301</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9290530624775915</v>
+        <v>0.986426356416796</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.513264923727591</v>
+        <v>4.5245260521898</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016436</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.939533786765764</v>
+        <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.98674001064659</v>
+        <v>-4.933220518111373</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.94448135819338</v>
+        <v>1.942726307306152</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9290530624775915</v>
+        <v>0.986426356416796</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.496965624252319</v>
+        <v>4.508226752714528</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307668</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.941964736229809</v>
+        <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.803528347513495</v>
+        <v>-4.750008854978278</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.020196972910663</v>
+        <v>2.018441922023436</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9290530624775915</v>
+        <v>0.986426356416796</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.499396573716364</v>
+        <v>4.510657702178573</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.924909142309186</v>
+        <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.731806900499644</v>
+        <v>-4.678287407964427</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.031829957795581</v>
+        <v>2.030074906908354</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.000774509491442</v>
+        <v>1.058147803430647</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.525373848004052</v>
+        <v>4.536634976466261</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.871824888230358</v>
+        <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.709433874891938</v>
+        <v>-4.655914382356721</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.987694913959834</v>
+        <v>1.985939863072608</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.012030260604344</v>
+        <v>1.069403554543548</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.479043044592965</v>
+        <v>4.490304173055174</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.71560744645673</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.057023093115713</v>
+        <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.742450170802683</v>
+        <v>-4.688930678267465</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.159686600480892</v>
+        <v>2.157931549593665</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9425928839375921</v>
+        <v>0.9999661778767968</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.622578823478269</v>
+        <v>4.633839951940478</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883678</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.048944318943962</v>
+        <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.730922535153074</v>
+        <v>-4.677403042617857</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.156218880568985</v>
+        <v>2.154463829681758</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.001593542138955</v>
+        <v>1.058966836078159</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.649900444227336</v>
+        <v>4.661161572689545</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236298</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.052612431465751</v>
+        <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.828264036495443</v>
+        <v>-4.774744543960225</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.120950392553826</v>
+        <v>2.119195341666599</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.9571733599734662</v>
+        <v>1.014546653912671</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.626916447449831</v>
+        <v>4.63817757591204</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427685</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.053863513658589</v>
+        <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.91412006583541</v>
+        <v>-4.860600573300192</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.087859063010677</v>
+        <v>2.08610401212345</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9147972907473312</v>
+        <v>0.9721705846865358</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.602741888106988</v>
+        <v>4.614003016569197</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.036282715479091</v>
+        <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.922956863251529</v>
+        <v>-4.869437370716311</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.066743545864731</v>
+        <v>2.064988494977505</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9073551181059805</v>
+        <v>0.9647284120451851</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.580695786342679</v>
+        <v>4.591956914804888</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667455</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.04644722652414</v>
+        <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.014339425816988</v>
+        <v>-4.96081993328177</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.040355031883597</v>
+        <v>2.038599980996371</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.8707902333866357</v>
+        <v>0.9281635273258404</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.568921366556122</v>
+        <v>4.580182495018331</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889192</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.148575484348408</v>
+        <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.002632707829981</v>
+        <v>-4.949113215294764</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.147165976902667</v>
+        <v>2.145410926015441</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.8824969513736421</v>
+        <v>0.9398702453128468</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.678073655172593</v>
+        <v>4.689334783634803</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409565</v>
+        <v>3.682476099409568</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.151607823079813</v>
+        <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.073544781572259</v>
+        <v>-5.020025289037042</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.121833486137161</v>
+        <v>2.120078435249935</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.8824969513736421</v>
+        <v>0.9398702453128468</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.681105993903998</v>
+        <v>4.692367122366208</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452572</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.364512656357871</v>
+        <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.083860879738611</v>
+        <v>-5.030341387203394</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.330611880148678</v>
+        <v>2.328856829261452</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.8824969513736421</v>
+        <v>0.9398702453128468</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.894010827182056</v>
+        <v>4.905271955644266</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762288</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.36369132326996</v>
+        <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.083766911721239</v>
+        <v>-5.030247419186021</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.329828134267717</v>
+        <v>2.328073083380491</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.8828668127209601</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.893411410902536</v>
+        <v>4.904672539364746</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988019</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.357923309214314</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.232133139377384</v>
+        <v>-5.178613646842166</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.264713629149613</v>
+        <v>2.262958578262387</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.8828668127209601</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.88764339684689</v>
+        <v>4.8989045253091</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.357923309214314</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.231184716259345</v>
+        <v>-5.177665223724127</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.265092998396828</v>
+        <v>2.263337947509602</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.8828668127209601</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.88764339684689</v>
+        <v>4.8989045253091</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.370650917195406</v>
+        <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.331454534218366</v>
+        <v>-5.277935041683149</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.237712679194312</v>
+        <v>2.235957628307086</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.8828668127209601</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.900371004827982</v>
+        <v>4.911632133290192</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.372596915619794</v>
+        <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.325462287429555</v>
+        <v>-5.271942794894337</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.242055576334224</v>
+        <v>2.240300525446998</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.8828668127209601</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.90231700325237</v>
+        <v>4.91357813171458</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.366251051637563</v>
+        <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.236904326298787</v>
+        <v>-5.18338483376357</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.2711328968043</v>
+        <v>2.269377845917074</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.8828668127209601</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.895971139270139</v>
+        <v>4.907232267732349</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383088</v>
+        <v>3.73530072138309</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.365559729076558</v>
+        <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.219145248795713</v>
+        <v>-5.165625756260495</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.277545205244525</v>
+        <v>2.2757901543573</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.8828668127209601</v>
+        <v>0.9402401066601648</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.895279816709134</v>
+        <v>4.906540945171344</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.378341914985145</v>
+        <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.119515097746645</v>
+        <v>-5.065995605211428</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.330179451572739</v>
+        <v>2.328424400685513</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.9824969637700276</v>
+        <v>1.039870257709232</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.967840093247162</v>
+        <v>4.979101221709372</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455268</v>
+        <v>3.77535709745527</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.567496180483872</v>
+        <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.168914606435656</v>
+        <v>-5.115395113900439</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.499573913595861</v>
+        <v>2.497818862708635</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.9927557972017724</v>
+        <v>1.050129091140977</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.163149658804936</v>
+        <v>5.174410787267146</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963129</v>
+        <v>3.749078058963131</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.554684853586734</v>
+        <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.96223013279328</v>
+        <v>-4.908710640258063</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.569436376155673</v>
+        <v>2.567681325268448</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.199440270844148</v>
+        <v>1.256813564783353</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.274349016093223</v>
+        <v>5.285610144555433</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162539</v>
+        <v>3.740284389162541</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.556686367240839</v>
+        <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.996387027790806</v>
+        <v>-4.942867535255589</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.557775131810768</v>
+        <v>2.556020080923542</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.115856501303336</v>
+        <v>1.17322979524254</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.22620026802284</v>
+        <v>5.237461396485051</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652381</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.910183481230506</v>
+        <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.90379754872935</v>
+        <v>-4.850278056194132</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.948308037425018</v>
+        <v>2.946552986537792</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.115856501303336</v>
+        <v>1.17322979524254</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.579697382012508</v>
+        <v>5.590958510474717</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.914746592797609</v>
+        <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.9636861765529</v>
+        <v>-4.910166684017683</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.928915697862701</v>
+        <v>2.927160646975476</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.101734586615871</v>
+        <v>1.159107880555076</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.575787344767132</v>
+        <v>5.587048473229342</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103562</v>
+        <v>3.835202441103563</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.964576534121137</v>
+        <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.911469866756558</v>
+        <v>-4.857950374221341</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.999632163104765</v>
+        <v>2.99787711221754</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.101734586615871</v>
+        <v>1.159107880555076</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.62561728609066</v>
+        <v>5.63687841455287</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047744</v>
+        <v>3.821827147047745</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.973390504331148</v>
+        <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.879572349671313</v>
+        <v>-4.826052857136095</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.021205140148875</v>
+        <v>3.019450089261649</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.133632103701117</v>
+        <v>1.191005397640321</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.653569766551818</v>
+        <v>5.664830895014028</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650753</v>
+        <v>3.825268416650754</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.969028088370345</v>
+        <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.894327673871453</v>
+        <v>-4.840808181336236</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.010940594508015</v>
+        <v>3.00918554362079</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.133632103701117</v>
+        <v>1.191005397640321</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.649207350591015</v>
+        <v>5.660468479053224</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135748</v>
+        <v>3.845044666135749</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.959952591786625</v>
+        <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.844863050501542</v>
+        <v>-4.791343557966324</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.02165094727226</v>
+        <v>3.019895896385034</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.183096727071028</v>
+        <v>1.240470021010233</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.669810628029242</v>
+        <v>5.681071756491452</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479221</v>
+        <v>3.825931790479222</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.956360259501559</v>
+        <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.681755058347926</v>
+        <v>-4.628235565812709</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.08330181184864</v>
+        <v>3.081546760961415</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.346204719224644</v>
+        <v>1.403578013163848</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.764083091036346</v>
+        <v>5.775344219498555</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844243</v>
+        <v>3.847096478844244</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.965407296192687</v>
+        <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.54894743285076</v>
+        <v>-4.495427940315542</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.145471898738635</v>
+        <v>3.143716847851409</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.346204719224644</v>
+        <v>1.403578013163848</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.773130127727473</v>
+        <v>5.784391256189684</v>
       </c>
     </row>
     <row r="2098">
@@ -49802,19 +49802,19 @@
         <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.966264761178809</v>
+        <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.611655349325318</v>
+        <v>-4.5581358567901</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.121246197134933</v>
+        <v>3.119491146247708</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.283496802750086</v>
+        <v>1.340870096689291</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.736362842828861</v>
+        <v>5.747623971291071</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578993</v>
+        <v>3.861579399578995</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.929174177969161</v>
+        <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.563647225481625</v>
+        <v>-4.510127732946407</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.103358863462763</v>
+        <v>3.101603812575537</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.283496802750086</v>
+        <v>1.340870096689291</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.699272259619213</v>
+        <v>5.710533388081423</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629881</v>
+        <v>3.872253907629883</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.933106431527111</v>
+        <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.484821568298035</v>
+        <v>-4.431302075762817</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.13882137989415</v>
+        <v>3.137066329006924</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.362322459933676</v>
+        <v>1.419695753872881</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.750499907487318</v>
+        <v>5.761761035949528</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686403</v>
+        <v>3.868502531686406</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.928005524134148</v>
+        <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.292886767044161</v>
+        <v>-4.239367274508943</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.210494393002736</v>
+        <v>3.20873934211551</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.362322459933676</v>
+        <v>1.419695753872881</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.745399000094355</v>
+        <v>5.756660128556565</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.763036575344223</v>
+        <v>3.7654723078485</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.839643911352353</v>
+        <v>4.81204498014471</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.292886767044161</v>
+        <v>-4.239367274508943</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.210494393002736</v>
+        <v>3.20873934211551</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.362322459933676</v>
+        <v>1.419695753872881</v>
       </c>
       <c r="G2102" t="n">
-        <v>4.832707708338721</v>
+        <v>4.805108777131077</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240929.xlsx
+++ b/tame_output/ON/bt/strategyON_20240929.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>61.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>109.7%</t>
+          <t>111.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>169.6%</t>
+          <t>175.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.4%</t>
+          <t>122.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-43.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-71.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.0%</t>
+          <t>421.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-585.5%</t>
+          <t>-588.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-55.3%</t>
+          <t>-60.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-301.9%</t>
+          <t>-300.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-82.0%</t>
+          <t>-96.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,31 +1423,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>117.2%</t>
         </is>
       </c>
     </row>
@@ -47571,19 +47571,19 @@
         <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.961706260998754</v>
+        <v>2.984257052831226</v>
       </c>
       <c r="D2001" t="n">
         <v>-2.828832626124374</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.829816786235256</v>
+        <v>1.852367578067729</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9750732742312349</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.546750225537495</v>
+        <v>3.569301017369968</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.971712414643495</v>
+        <v>2.994263206475968</v>
       </c>
       <c r="D2002" t="n">
         <v>-2.801881401797886</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.850603429610593</v>
+        <v>1.873154221443065</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9899536202589541</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.565684586798868</v>
+        <v>3.588235378631341</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.155815546788455</v>
+        <v>3.178366338620928</v>
       </c>
       <c r="D2003" t="n">
         <v>-2.823425629628673</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.026088870623238</v>
+        <v>2.04863966245571</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9899536202589541</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.749787718943828</v>
+        <v>3.7723385107763</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.147932241691448</v>
+        <v>3.17048303352392</v>
       </c>
       <c r="D2004" t="n">
         <v>-2.845833747433546</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.009242318404282</v>
+        <v>2.031793110236754</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9899536202589541</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.741904413846821</v>
+        <v>3.764455205679293</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.149986241241086</v>
+        <v>3.172537033073558</v>
       </c>
       <c r="D2005" t="n">
         <v>-2.874057983011146</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.00000662372288</v>
+        <v>2.022557415555352</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007930372710263</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.754744464867243</v>
+        <v>3.777295256699716</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.206239958962933</v>
+        <v>3.228790750795405</v>
       </c>
       <c r="D2006" t="n">
         <v>-2.883498908899676</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.052483971089314</v>
+        <v>2.075034762921787</v>
       </c>
       <c r="F2006" t="n">
         <v>1.130357490253654</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.884454453115125</v>
+        <v>3.907005244947598</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.209131053508234</v>
+        <v>3.231681845340706</v>
       </c>
       <c r="D2007" t="n">
         <v>-2.97237554006815</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.019824413167226</v>
+        <v>2.042375204999698</v>
       </c>
       <c r="F2007" t="n">
         <v>1.04148085908518</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.834019568959342</v>
+        <v>3.856570360791814</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.207242866402009</v>
+        <v>3.229793658234481</v>
       </c>
       <c r="D2008" t="n">
         <v>-3.048705517669056</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.987404235020638</v>
+        <v>2.009955026853111</v>
       </c>
       <c r="F2008" t="n">
         <v>1.04148085908518</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.832131381853117</v>
+        <v>3.854682173685589</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.202063096004871</v>
+        <v>3.224613887837343</v>
       </c>
       <c r="D2009" t="n">
         <v>-3.203662303069185</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.920241750463449</v>
+        <v>1.942792542295921</v>
       </c>
       <c r="F2009" t="n">
         <v>0.886524073685051</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.733977540215902</v>
+        <v>3.756528332048374</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.200497106215023</v>
+        <v>3.223047898047496</v>
       </c>
       <c r="D2010" t="n">
         <v>-3.36523072859644</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.854048390462699</v>
+        <v>1.876599182295172</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7597411498871717</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.656341796147327</v>
+        <v>3.678892587979799</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.213570513080942</v>
+        <v>3.236121304913414</v>
       </c>
       <c r="D2011" t="n">
         <v>-3.473531390466559</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.82380153258057</v>
+        <v>1.846352324413043</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7597411498871717</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.669415203013245</v>
+        <v>3.691965994845718</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.205575709863882</v>
+        <v>3.228126501696354</v>
       </c>
       <c r="D2012" t="n">
         <v>-3.491335362187304</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.808685140675212</v>
+        <v>1.831235932507685</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6892065269819705</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.619099626053064</v>
+        <v>3.641650417885537</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.204099750990884</v>
+        <v>3.226650542823356</v>
       </c>
       <c r="D2013" t="n">
         <v>-3.519236149296777</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.796048866958425</v>
+        <v>1.818599658790898</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6546096028390357</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.596865512694305</v>
+        <v>3.619416304526778</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.200864194968083</v>
+        <v>3.223414986800555</v>
       </c>
       <c r="D2014" t="n">
         <v>-3.64176225199967</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.743802869854467</v>
+        <v>1.766353661686939</v>
       </c>
       <c r="F2014" t="n">
         <v>0.5320835001361418</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.520114295049768</v>
+        <v>3.54266508688224</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.267570154558586</v>
+        <v>3.290120946391059</v>
       </c>
       <c r="D2015" t="n">
         <v>-3.872276748185259</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.718303030970735</v>
+        <v>1.740853822803207</v>
       </c>
       <c r="F2015" t="n">
         <v>0.3015690039505531</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.448511556928918</v>
+        <v>3.471062348761391</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.407881873560433</v>
+        <v>3.430432665392906</v>
       </c>
       <c r="D2016" t="n">
         <v>-4.221021833409702</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.719116715882804</v>
+        <v>1.741667507715277</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1928210500316553</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.523574503579427</v>
+        <v>3.546125295411899</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.476862142706073</v>
+        <v>3.499412934538546</v>
       </c>
       <c r="D2017" t="n">
         <v>-4.375008251185843</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.726502417917988</v>
+        <v>1.749053209750461</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1928210500316553</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.592554772725067</v>
+        <v>3.615105564557539</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.462913344826194</v>
+        <v>3.485464136658667</v>
       </c>
       <c r="D2018" t="n">
         <v>-4.579607686048852</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.630713846092906</v>
+        <v>1.653264637925378</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1928210500316553</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.578605974845188</v>
+        <v>3.60115676667766</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.474783833881608</v>
+        <v>3.49733462571408</v>
       </c>
       <c r="D2019" t="n">
         <v>-4.832082840056576</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.54159427354523</v>
+        <v>1.564145065377702</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1928210500316553</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.590476463900602</v>
+        <v>3.613027255733074</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.475994368400552</v>
+        <v>3.498545160233024</v>
       </c>
       <c r="D2020" t="n">
         <v>-5.124978596535988</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.425646505472409</v>
+        <v>1.448197297304881</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1928210500316553</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.591686998419545</v>
+        <v>3.614237790252018</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.480116110627873</v>
+        <v>3.502666902460346</v>
       </c>
       <c r="D2021" t="n">
         <v>-5.311642724670796</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.355102596445807</v>
+        <v>1.377653388278279</v>
       </c>
       <c r="F2021" t="n">
         <v>0.1660820792070954</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.579765358152131</v>
+        <v>3.602316149984603</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.475193963364063</v>
+        <v>3.497744755196535</v>
       </c>
       <c r="D2022" t="n">
         <v>-5.457663411584758</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.291772174416411</v>
+        <v>1.314322966248884</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1569989874132384</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.569393355812006</v>
+        <v>3.591944147644478</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.637398020063107</v>
+        <v>3.659948811895579</v>
       </c>
       <c r="D2023" t="n">
         <v>-5.549377420694343</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.417290627471622</v>
+        <v>1.439841419304094</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1569989874132384</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.73159741251105</v>
+        <v>3.754148204343522</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.632244658026921</v>
+        <v>3.654795449859393</v>
       </c>
       <c r="D2024" t="n">
         <v>-5.581029079754313</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.399476601811448</v>
+        <v>1.422027393643921</v>
       </c>
       <c r="F2024" t="n">
         <v>0.1518305301687982</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.7233429761282</v>
+        <v>3.745893767960673</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.642474075595412</v>
+        <v>3.665024867427884</v>
       </c>
       <c r="D2025" t="n">
         <v>-5.650095134327249</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.382079597550764</v>
+        <v>1.404630389383237</v>
       </c>
       <c r="F2025" t="n">
         <v>0.08945965267518818</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.696149867200525</v>
+        <v>3.718700659032998</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.651399714051315</v>
+        <v>3.673950505883787</v>
       </c>
       <c r="D2026" t="n">
         <v>-5.752071256575657</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.350214787107304</v>
+        <v>1.372765578939776</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.01251646957321939</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.643889832307383</v>
+        <v>3.666440624139855</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231808</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.64355260129549</v>
+        <v>3.666103393127962</v>
       </c>
       <c r="D2027" t="n">
         <v>-5.642064973098435</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.386370187742368</v>
+        <v>1.40892097957484</v>
       </c>
       <c r="F2027" t="n">
         <v>0.01068810234405582</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.649965462701924</v>
+        <v>3.672516254534396</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.647802612017464</v>
+        <v>3.670353403849937</v>
       </c>
       <c r="D2028" t="n">
         <v>-5.499005397357509</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.447844028760713</v>
+        <v>1.470394820593185</v>
       </c>
       <c r="F2028" t="n">
         <v>0.01870152893403509</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.659023529377885</v>
+        <v>3.681574321210358</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.6550634949</v>
+        <v>3.677614286732473</v>
       </c>
       <c r="D2029" t="n">
         <v>-5.197558671885671</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.575683601831984</v>
+        <v>1.598234393664456</v>
       </c>
       <c r="F2029" t="n">
         <v>0.3201482544058724</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.847152447543524</v>
+        <v>3.869703239375996</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.656034672652711</v>
+        <v>3.678585464485183</v>
       </c>
       <c r="D2030" t="n">
         <v>-5.222148916120855</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.566818681890621</v>
+        <v>1.589369473723093</v>
       </c>
       <c r="F2030" t="n">
         <v>0.3201482544058724</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.848123625296235</v>
+        <v>3.870674417128707</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.656877577032466</v>
+        <v>3.679428368864939</v>
       </c>
       <c r="D2031" t="n">
         <v>-5.171110540114335</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.588076936672985</v>
+        <v>1.610627728505457</v>
       </c>
       <c r="F2031" t="n">
         <v>0.3201482544058724</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.84896652967599</v>
+        <v>3.871517321508462</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.675915675906612</v>
+        <v>3.698466467739084</v>
       </c>
       <c r="D2032" t="n">
         <v>-5.142261863290875</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.618654506276514</v>
+        <v>1.641205298108986</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3489969312293326</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.885313834644212</v>
+        <v>3.907864626476684</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.492099672030546</v>
+        <v>3.514650463863019</v>
       </c>
       <c r="D2033" t="n">
         <v>-5.045626951272235</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.473492467207905</v>
+        <v>1.496043259040377</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4456318432479726</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.75947877797933</v>
+        <v>3.782029569811803</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.495601716104511</v>
+        <v>3.518152507936983</v>
       </c>
       <c r="D2034" t="n">
         <v>-4.976588940323767</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.504609715661256</v>
+        <v>1.527160507493728</v>
       </c>
       <c r="F2034" t="n">
         <v>0.5146698541964406</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.804403628622375</v>
+        <v>3.826954420454848</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.480028535180593</v>
+        <v>3.502579327013065</v>
       </c>
       <c r="D2035" t="n">
         <v>-4.812092606132805</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.554835068413723</v>
+        <v>1.577385860246195</v>
       </c>
       <c r="F2035" t="n">
         <v>0.6791661883874025</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.887528248213035</v>
+        <v>3.910079040045507</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.479216245617023</v>
+        <v>3.501767037449495</v>
       </c>
       <c r="D2036" t="n">
         <v>-4.734994004590932</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.584862219466902</v>
+        <v>1.607413011299374</v>
       </c>
       <c r="F2036" t="n">
         <v>0.6791661883874025</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.886715958649464</v>
+        <v>3.909266750481937</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.489085024742095</v>
+        <v>3.511635816574568</v>
       </c>
       <c r="D2037" t="n">
         <v>-4.745379199480822</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.590576920636019</v>
+        <v>1.613127712468491</v>
       </c>
       <c r="F2037" t="n">
         <v>0.6687809934975132</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.890353620840604</v>
+        <v>3.912904412673075</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.55992203051852</v>
+        <v>3.582472822350993</v>
       </c>
       <c r="D2038" t="n">
         <v>-4.763967358203047</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.653978662923554</v>
+        <v>1.676529454756026</v>
       </c>
       <c r="F2038" t="n">
         <v>0.6501928347752879</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.950037731383693</v>
+        <v>3.972588523216166</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.556791041336819</v>
+        <v>3.579341833169291</v>
       </c>
       <c r="D2039" t="n">
         <v>-4.764265904899083</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.650728255063438</v>
+        <v>1.67327904689591</v>
       </c>
       <c r="F2039" t="n">
         <v>0.649894288079252</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.94672761418437</v>
+        <v>3.969278406016842</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.56132193627621</v>
+        <v>3.583872728108683</v>
       </c>
       <c r="D2040" t="n">
         <v>-4.663442771208655</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.695588403479</v>
+        <v>1.718139195311473</v>
       </c>
       <c r="F2040" t="n">
         <v>0.6623585035636058</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.958737038414374</v>
+        <v>3.981287830246846</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.561451189754754</v>
+        <v>3.584001981587226</v>
       </c>
       <c r="D2041" t="n">
         <v>-4.472661410456247</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.772030201258507</v>
+        <v>1.794580993090979</v>
       </c>
       <c r="F2041" t="n">
         <v>0.8531398643160132</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.073335108344362</v>
+        <v>4.095885900176834</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.54128803549235</v>
+        <v>3.563838827324822</v>
       </c>
       <c r="D2042" t="n">
         <v>-4.365698052606826</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.794652390135872</v>
+        <v>1.817203181968344</v>
       </c>
       <c r="F2042" t="n">
         <v>0.9116044722758146</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.088250718857839</v>
+        <v>4.110801510690312</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.576254972104409</v>
+        <v>3.598805763936881</v>
       </c>
       <c r="D2043" t="n">
         <v>-4.310367464705063</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.851751561908635</v>
+        <v>1.874302353741108</v>
       </c>
       <c r="F2043" t="n">
         <v>0.9669350601775768</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.156416008210955</v>
+        <v>4.178966800043427</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.569941540005846</v>
+        <v>3.592492331838319</v>
       </c>
       <c r="D2044" t="n">
         <v>-4.2983133377921</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.850259780575258</v>
+        <v>1.87281057240773</v>
       </c>
       <c r="F2044" t="n">
         <v>0.9789891870905396</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.15733505226017</v>
+        <v>4.179885844092643</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.571822170189982</v>
+        <v>3.594372962022454</v>
       </c>
       <c r="D2045" t="n">
         <v>-4.339468457360321</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.835678362932106</v>
+        <v>1.858229154764578</v>
       </c>
       <c r="F2045" t="n">
         <v>0.9378340675223187</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.134522610703374</v>
+        <v>4.157073402535846</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.584673196067865</v>
+        <v>3.607223987900337</v>
       </c>
       <c r="D2046" t="n">
         <v>-4.271419894668791</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.8757488138866</v>
+        <v>1.898299605719072</v>
       </c>
       <c r="F2046" t="n">
         <v>1.005882630213848</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.188202774196174</v>
+        <v>4.210753566028647</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.645256780013425</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.604875866241459</v>
+        <v>3.627426658073931</v>
       </c>
       <c r="D2047" t="n">
         <v>-4.503020287838292</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.803311326792394</v>
+        <v>1.825862118624866</v>
       </c>
       <c r="F2047" t="n">
         <v>1.005882630213848</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.208405444369768</v>
+        <v>4.230956236202241</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.588482102308341</v>
+        <v>3.611032894140813</v>
       </c>
       <c r="D2048" t="n">
         <v>-4.553071833367511</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.766896944647588</v>
+        <v>1.789447736480061</v>
       </c>
       <c r="F2048" t="n">
         <v>1.005882630213848</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.19201168043665</v>
+        <v>4.214562472269122</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.548734015901807</v>
+        <v>3.57128480773428</v>
       </c>
       <c r="D2049" t="n">
         <v>-4.728178665943956</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.657106125210477</v>
+        <v>1.67965691704295</v>
       </c>
       <c r="F2049" t="n">
         <v>1.005882630213848</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.152263594030117</v>
+        <v>4.174814385862589</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.555756634898747</v>
+        <v>3.57830742673122</v>
       </c>
       <c r="D2050" t="n">
         <v>-4.532078512513433</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.742568805579626</v>
+        <v>1.765119597412099</v>
       </c>
       <c r="F2050" t="n">
         <v>1.201982783644371</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.276946305085371</v>
+        <v>4.299497096917843</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.654927634471652</v>
+        <v>3.677478426304124</v>
       </c>
       <c r="D2051" t="n">
         <v>-4.379053120400148</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.902949961997844</v>
+        <v>1.925500753830317</v>
       </c>
       <c r="F2051" t="n">
         <v>1.355008175757655</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.467932539926245</v>
+        <v>4.490483331758718</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.842393859379944</v>
+        <v>3.864944651212417</v>
       </c>
       <c r="D2052" t="n">
         <v>-4.407360434273419</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.079093261356829</v>
+        <v>2.101644053189301</v>
       </c>
       <c r="F2052" t="n">
         <v>1.355008175757655</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.655398764834538</v>
+        <v>4.67794955666701</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.811796810734027</v>
+        <v>3.8343476025665</v>
       </c>
       <c r="D2053" t="n">
         <v>-4.573953659386941</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.981858922665503</v>
+        <v>2.004409714497975</v>
       </c>
       <c r="F2053" t="n">
         <v>1.188414950644133</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.524845781120507</v>
+        <v>4.547396572952979</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.815473213395745</v>
+        <v>3.838024005228217</v>
       </c>
       <c r="D2054" t="n">
         <v>-4.550917866025375</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.994749642671847</v>
+        <v>2.017300434504319</v>
       </c>
       <c r="F2054" t="n">
         <v>1.188414950644133</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.528522183782225</v>
+        <v>4.551072975614697</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.81309126851924</v>
+        <v>3.835642060351713</v>
       </c>
       <c r="D2055" t="n">
         <v>-4.521671885569678</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.004066089977621</v>
+        <v>2.026616881810093</v>
       </c>
       <c r="F2055" t="n">
         <v>1.188414950644133</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.52614023890572</v>
+        <v>4.548691030738192</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.810384507676875</v>
+        <v>3.832935299509348</v>
       </c>
       <c r="D2056" t="n">
         <v>-4.628597433447529</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.958589109984116</v>
+        <v>1.981139901816588</v>
       </c>
       <c r="F2056" t="n">
         <v>1.081489402766282</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.459278149336645</v>
+        <v>4.481828941169117</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.811813309820109</v>
+        <v>3.834364101652582</v>
       </c>
       <c r="D2057" t="n">
         <v>-4.773615991954778</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.90201048872445</v>
+        <v>1.924561280556922</v>
       </c>
       <c r="F2057" t="n">
         <v>0.936470844259033</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.37369581637553</v>
+        <v>4.396246608208002</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.911744549077862</v>
+        <v>3.934295340910334</v>
       </c>
       <c r="D2058" t="n">
         <v>-4.891957757739496</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.954605021668316</v>
+        <v>1.977155813500788</v>
       </c>
       <c r="F2058" t="n">
         <v>0.9471568828219231</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.480038678771017</v>
+        <v>4.502589470603488</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.909530246203802</v>
+        <v>3.932081038036273</v>
       </c>
       <c r="D2059" t="n">
         <v>-4.943368180060204</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.931826549865972</v>
+        <v>1.954377341698444</v>
       </c>
       <c r="F2059" t="n">
         <v>0.9471568828219231</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.477824375896955</v>
+        <v>4.500375167729427</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.909433374278091</v>
+        <v>3.931984166110563</v>
       </c>
       <c r="D2060" t="n">
         <v>-5.022787631267955</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.89996189745716</v>
+        <v>1.922512689289632</v>
       </c>
       <c r="F2060" t="n">
         <v>0.9471568828219231</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.477727503971245</v>
+        <v>4.500278295803716</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736804952298399</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.909427267836134</v>
+        <v>3.931978059668606</v>
       </c>
       <c r="D2061" t="n">
         <v>-5.118250629185173</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.861770591848317</v>
+        <v>1.884321383680789</v>
       </c>
       <c r="F2061" t="n">
         <v>0.9471568828219231</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.477721397529288</v>
+        <v>4.50027218936176</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715372960218001</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.907523664398744</v>
+        <v>3.930074456231217</v>
       </c>
       <c r="D2062" t="n">
         <v>-5.053874718334458</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.885617352751213</v>
+        <v>1.908168144583685</v>
       </c>
       <c r="F2062" t="n">
         <v>1.011532793672638</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.514443340602328</v>
+        <v>4.5369941324348</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353536</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.913257482146471</v>
+        <v>3.935808273978943</v>
       </c>
       <c r="D2063" t="n">
         <v>-5.109243880466652</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.869203505646062</v>
+        <v>1.891754297478534</v>
       </c>
       <c r="F2063" t="n">
         <v>1.011532793672638</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.520177158350054</v>
+        <v>4.542727950182527</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736822870113279</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.912795845489403</v>
+        <v>3.935346637321876</v>
       </c>
       <c r="D2064" t="n">
         <v>-5.12746234746426</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.861454482189951</v>
+        <v>1.884005274022424</v>
       </c>
       <c r="F2064" t="n">
         <v>0.986426356416796</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.504651659339482</v>
+        <v>4.527202451171954</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790272500113688</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.932670238339722</v>
+        <v>3.955221030172195</v>
       </c>
       <c r="D2065" t="n">
         <v>-5.039255513316682</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.916611608699301</v>
+        <v>1.939162400531774</v>
       </c>
       <c r="F2065" t="n">
         <v>0.986426356416796</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.5245260521898</v>
+        <v>4.547076844022273</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.91637093886445</v>
+        <v>3.938921730696923</v>
       </c>
       <c r="D2066" t="n">
         <v>-4.933220518111373</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.942726307306152</v>
+        <v>1.965277099138626</v>
       </c>
       <c r="F2066" t="n">
         <v>0.986426356416796</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.508226752714528</v>
+        <v>4.530777544547001</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.918801888328495</v>
+        <v>3.941352680160969</v>
       </c>
       <c r="D2067" t="n">
         <v>-4.750008854978278</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.018441922023436</v>
+        <v>2.04099271385591</v>
       </c>
       <c r="F2067" t="n">
         <v>0.986426356416796</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.510657702178573</v>
+        <v>4.533208494011046</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.901746294407872</v>
+        <v>3.924297086240346</v>
       </c>
       <c r="D2068" t="n">
         <v>-4.678287407964427</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.030074906908354</v>
+        <v>2.052625698740827</v>
       </c>
       <c r="F2068" t="n">
         <v>1.058147803430647</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.536634976466261</v>
+        <v>4.559185768298734</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.848662040329044</v>
+        <v>3.871212832161517</v>
       </c>
       <c r="D2069" t="n">
         <v>-4.655914382356721</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.985939863072608</v>
+        <v>2.008490654905081</v>
       </c>
       <c r="F2069" t="n">
         <v>1.069403554543548</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.490304173055174</v>
+        <v>4.512854964887646</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.71560744645673</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.0338602452144</v>
+        <v>4.056411037046873</v>
       </c>
       <c r="D2070" t="n">
         <v>-4.688930678267465</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.157931549593665</v>
+        <v>2.180482341426139</v>
       </c>
       <c r="F2070" t="n">
         <v>0.9999661778767968</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.633839951940478</v>
+        <v>4.656390743772951</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.713762536883678</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.025781471042649</v>
+        <v>4.048332262875122</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.677403042617857</v>
+        <v>-4.819960106118248</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.154463829681758</v>
+        <v>2.119991796114075</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.058966836078159</v>
+        <v>0.923955850806472</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.661161572689545</v>
+        <v>4.602705773359006</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236298</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.029449583564437</v>
+        <v>4.05200037539691</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.774744543960225</v>
+        <v>-4.917301607460617</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.119195341666599</v>
+        <v>2.084723308098916</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.014546653912671</v>
+        <v>0.8795356686409836</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.63817757591204</v>
+        <v>4.579721776581501</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427685</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.030700665757275</v>
+        <v>4.053251457589749</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.860600573300192</v>
+        <v>-5.003157636800584</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.08610401212345</v>
+        <v>2.051631978555768</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9721705846865358</v>
+        <v>0.8371595994148486</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.614003016569197</v>
+        <v>4.555547217238658</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.013119867577777</v>
+        <v>4.03567065941025</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.869437370716311</v>
+        <v>-5.011994434216703</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.064988494977505</v>
+        <v>2.030516461409821</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9647284120451851</v>
+        <v>0.8297174267734979</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.591956914804888</v>
+        <v>4.533501115474349</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667455</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.023284378622827</v>
+        <v>4.0458351704553</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.96081993328177</v>
+        <v>-5.103376996782162</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.038599980996371</v>
+        <v>2.004127947428687</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9281635273258404</v>
+        <v>0.7931525420541532</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.580182495018331</v>
+        <v>4.521726695687792</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889192</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.125412636447095</v>
+        <v>4.147963428279567</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.949113215294764</v>
+        <v>-5.091670278795156</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.145410926015441</v>
+        <v>2.110938892447757</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.9398702453128468</v>
+        <v>0.8048592600411596</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.689334783634803</v>
+        <v>4.630878984304263</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409568</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.1284449751785</v>
+        <v>4.150995767010972</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.020025289037042</v>
+        <v>-5.162582352537433</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.120078435249935</v>
+        <v>2.085606401682251</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.9398702453128468</v>
+        <v>0.8048592600411596</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.692367122366208</v>
+        <v>4.633911323035668</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452572</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.341349808456558</v>
+        <v>4.36390060028903</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.030341387203394</v>
+        <v>-5.172898450703785</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.328856829261452</v>
+        <v>2.294384795693768</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.9398702453128468</v>
+        <v>0.8048592600411596</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.905271955644266</v>
+        <v>4.846816156313726</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762288</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.340528475368647</v>
+        <v>4.36307926720112</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.030247419186021</v>
+        <v>-5.172804482686412</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.328073083380491</v>
+        <v>2.293601049812807</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.8052291213884776</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.904672539364746</v>
+        <v>4.846216740034206</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988019</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.334760461313001</v>
+        <v>4.357311253145474</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.178613646842166</v>
+        <v>-5.321170710342557</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.262958578262387</v>
+        <v>2.228486544694703</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.8052291213884776</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.8989045253091</v>
+        <v>4.84044872597856</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.334760461313001</v>
+        <v>4.357311253145474</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.177665223724127</v>
+        <v>-5.320222287224518</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.263337947509602</v>
+        <v>2.228865913941918</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.8052291213884776</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.8989045253091</v>
+        <v>4.84044872597856</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.347488069294093</v>
+        <v>4.370038861126566</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.277935041683149</v>
+        <v>-5.42049210518354</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.235957628307086</v>
+        <v>2.201485594739402</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.8052291213884776</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.911632133290192</v>
+        <v>4.853176333959652</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.349434067718481</v>
+        <v>4.371984859550953</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.271942794894337</v>
+        <v>-5.414499858394728</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.240300525446998</v>
+        <v>2.205828491879314</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.8052291213884776</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.91357813171458</v>
+        <v>4.85512233238404</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.34308820373625</v>
+        <v>4.365638995568722</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.18338483376357</v>
+        <v>-5.32594189726396</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.269377845917074</v>
+        <v>2.23490581234939</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.8052291213884776</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.907232267732349</v>
+        <v>4.848776468401809</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.73530072138309</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.342396881175246</v>
+        <v>4.364947673007718</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.165625756260495</v>
+        <v>-5.308182819760886</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.2757901543573</v>
+        <v>2.241318120789615</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.9402401066601648</v>
+        <v>0.8052291213884776</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.906540945171344</v>
+        <v>4.848085145840805</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.355179067083832</v>
+        <v>4.377729858916305</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.065995605211428</v>
+        <v>-5.208552668711818</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.328424400685513</v>
+        <v>2.293952367117829</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.039870257709232</v>
+        <v>0.904859272437545</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.979101221709372</v>
+        <v>4.920645422378832</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.77535709745527</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.544333332582559</v>
+        <v>4.566884124415031</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.115395113900439</v>
+        <v>-5.25795217740083</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.497818862708635</v>
+        <v>2.463346829140951</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.050129091140977</v>
+        <v>0.9151181058692898</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.174410787267146</v>
+        <v>5.115954987936605</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963131</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.531522005685421</v>
+        <v>4.554072797517893</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.908710640258063</v>
+        <v>-5.051267703758453</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.567681325268448</v>
+        <v>2.533209291700764</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.256813564783353</v>
+        <v>1.121802579511666</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.285610144555433</v>
+        <v>5.227154345224893</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162541</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.533523519339526</v>
+        <v>4.556074311171998</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.942867535255589</v>
+        <v>-5.08542459875598</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.556020080923542</v>
+        <v>2.521548047355858</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.17322979524254</v>
+        <v>1.038218809970853</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.237461396485051</v>
+        <v>5.17900559715451</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.887020633329193</v>
+        <v>4.909571425161666</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.850278056194132</v>
+        <v>-4.992835119694523</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.946552986537792</v>
+        <v>2.912080952970109</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.17322979524254</v>
+        <v>1.038218809970853</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.590958510474717</v>
+        <v>5.532502711144177</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.891583744896296</v>
+        <v>4.914134536728769</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.910166684017683</v>
+        <v>-5.052723747518074</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.927160646975476</v>
+        <v>2.892688613407791</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.159107880555076</v>
+        <v>1.024096895283388</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.587048473229342</v>
+        <v>5.528592673898802</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.835202441103563</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.941413686219824</v>
+        <v>4.963964478052296</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.857950374221341</v>
+        <v>-5.000507437721732</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.99787711221754</v>
+        <v>2.963405078649855</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.159107880555076</v>
+        <v>1.024096895283388</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.63687841455287</v>
+        <v>5.57842261522233</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047745</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.950227656429835</v>
+        <v>4.972778448262307</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.826052857136095</v>
+        <v>-4.968609920636486</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.019450089261649</v>
+        <v>2.984978055693965</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.191005397640321</v>
+        <v>1.055994412368634</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.664830895014028</v>
+        <v>5.606375095683488</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650754</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.945865240469032</v>
+        <v>4.968416032301504</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.840808181336236</v>
+        <v>-4.983365244836627</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.00918554362079</v>
+        <v>2.974713510053105</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.191005397640321</v>
+        <v>1.055994412368634</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.660468479053224</v>
+        <v>5.602012679722685</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.845044666135749</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.936789743885312</v>
+        <v>4.959340535717784</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.791343557966324</v>
+        <v>-4.933900621466715</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.019895896385034</v>
+        <v>2.98542386281735</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.240470021010233</v>
+        <v>1.105459035738546</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.681071756491452</v>
+        <v>5.622615957160912</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.825931790479222</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.933197411600246</v>
+        <v>4.955748203432718</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.628235565812709</v>
+        <v>-4.7707926293131</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.081546760961415</v>
+        <v>3.04707472739373</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.403578013163848</v>
+        <v>1.268567027892161</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.775344219498555</v>
+        <v>5.716888420168015</v>
       </c>
     </row>
     <row r="2097">
@@ -49779,19 +49779,19 @@
         <v>3.847096478844244</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.942244448291374</v>
+        <v>4.964795240123847</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.495427940315542</v>
+        <v>-4.637985003815933</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.143716847851409</v>
+        <v>3.109244814283725</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.403578013163848</v>
+        <v>1.268567027892161</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.784391256189684</v>
+        <v>5.725935456859143</v>
       </c>
     </row>
     <row r="2098">
@@ -49802,19 +49802,19 @@
         <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.943101913277496</v>
+        <v>4.965652705109968</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.5581358567901</v>
+        <v>-4.700692920290491</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.119491146247708</v>
+        <v>3.085019112680023</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.340870096689291</v>
+        <v>1.205859111417603</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.747623971291071</v>
+        <v>5.689168171960531</v>
       </c>
     </row>
     <row r="2099">
@@ -49825,19 +49825,19 @@
         <v>3.861579399578995</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.906011330067848</v>
+        <v>4.92856212190032</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.510127732946407</v>
+        <v>-4.652684796446798</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.101603812575537</v>
+        <v>3.067131779007853</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.340870096689291</v>
+        <v>1.205859111417603</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.710533388081423</v>
+        <v>5.652077588750883</v>
       </c>
     </row>
     <row r="2100">
@@ -49848,19 +49848,19 @@
         <v>3.872253907629883</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.909943583625799</v>
+        <v>4.932494375458271</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.431302075762817</v>
+        <v>-4.573859139263208</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.137066329006924</v>
+        <v>3.10259429543924</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.419695753872881</v>
+        <v>1.284684768601194</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.761761035949528</v>
+        <v>5.703305236618988</v>
       </c>
     </row>
     <row r="2101">
@@ -49871,19 +49871,19 @@
         <v>3.868502531686406</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.904842676232835</v>
+        <v>4.927393468065308</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.239367274508943</v>
+        <v>-4.381924338009334</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.20873934211551</v>
+        <v>3.174267308547826</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.419695753872881</v>
+        <v>1.284684768601194</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.756660128556565</v>
+        <v>5.698204329226025</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.7654723078485</v>
+        <v>3.891267537058207</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.81204498014471</v>
+        <v>4.868154895504267</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.239367274508943</v>
+        <v>-4.267888936510598</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.20873934211551</v>
+        <v>3.16064289658628</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.419695753872881</v>
+        <v>1.272785590660677</v>
       </c>
       <c r="G2102" t="n">
-        <v>4.805108777131077</v>
+        <v>5.631826249900674</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240929.xlsx
+++ b/tame_output/ON/bt/strategyON_20240929.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>111.9%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>175.2%</t>
+          <t>178.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-43.3%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.0%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.4%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-588.4%</t>
+          <t>-576.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-60.2%</t>
+          <t>-52.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-300.1%</t>
+          <t>-368.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.7%</t>
+          <t>-91.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>115.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>117.2%</t>
+          <t>123.7%</t>
         </is>
       </c>
     </row>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.033503754937939</v>
+        <v>-3.943010980453843</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8394984292926531</v>
+        <v>0.8756955390862917</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4708556194816057</v>
@@ -46999,10 +46999,10 @@
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.989130623299371</v>
+        <v>-3.898637848815274</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8571105493835167</v>
+        <v>0.8933076591771554</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5152287511201743</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.95439930198087</v>
+        <v>-3.863906527496773</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8653968720495075</v>
+        <v>0.9015939818431462</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5152287511201743</v>
@@ -47045,10 +47045,10 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.906743571419814</v>
+        <v>-3.816250796935718</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8908409213017343</v>
+        <v>0.927038031095373</v>
       </c>
       <c r="F1978" t="n">
         <v>0.56288448168123</v>
@@ -47068,10 +47068,10 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.80622541292106</v>
+        <v>-3.715732638436963</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.935940558075961</v>
+        <v>0.9721376678695997</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6634026401799845</v>
@@ -47091,10 +47091,10 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.790320083488707</v>
+        <v>-3.69982730900461</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9290573623247744</v>
+        <v>0.9652544721184131</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5842899794707457</v>
@@ -47114,10 +47114,10 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.745481681880309</v>
+        <v>-3.654988907396212</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9510904255787622</v>
+        <v>0.9872875353724009</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5888334124156152</v>
@@ -47137,10 +47137,10 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.764980138122317</v>
+        <v>-3.67448736363822</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9474519827130368</v>
+        <v>0.9836490925066754</v>
       </c>
       <c r="F1982" t="n">
         <v>0.5407487711357108</v>
@@ -47160,10 +47160,10 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.720777301036417</v>
+        <v>-3.63028452655232</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9710127200752341</v>
+        <v>1.007209829868873</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5849516082216113</v>
@@ -47183,10 +47183,10 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.728336966873464</v>
+        <v>-3.637844192389367</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9663988542096629</v>
+        <v>1.002595964003302</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6397550122314306</v>
@@ -47206,10 +47206,10 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.570045549334191</v>
+        <v>-3.479552774850095</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.080963186408411</v>
+        <v>1.11716029620205</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6397550122314306</v>
@@ -47229,10 +47229,10 @@
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.362403545699715</v>
+        <v>-3.271910771215619</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.162460692456455</v>
+        <v>1.198657802250094</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8473970158659068</v>
@@ -47252,10 +47252,10 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.311371452977187</v>
+        <v>-3.220878678493091</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.177821757783736</v>
+        <v>1.214018867577375</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8984291085884347</v>
@@ -47275,10 +47275,10 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.246147271849981</v>
+        <v>-3.155654497365885</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.221098834327324</v>
+        <v>1.257295944120962</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9636532897156403</v>
@@ -47298,10 +47298,10 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.208720251778848</v>
+        <v>-3.118227477294751</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.232030614655057</v>
+        <v>1.268227724448696</v>
       </c>
       <c r="F1989" t="n">
         <v>0.968904827744822</v>
@@ -47321,10 +47321,10 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.207362266805302</v>
+        <v>-3.116869492321205</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.233830600975716</v>
+        <v>1.270027710769355</v>
       </c>
       <c r="F1990" t="n">
         <v>1.043242953282641</v>
@@ -47344,10 +47344,10 @@
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.178949003705418</v>
+        <v>-3.088456229221322</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.40575367723688</v>
+        <v>1.441950787030519</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9842673905362118</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.104166742680406</v>
+        <v>-3.013673968196309</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.555779490864702</v>
+        <v>1.591976600658341</v>
       </c>
       <c r="F1992" t="n">
         <v>1.059049651561224</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.078082658416598</v>
+        <v>-2.987589883932501</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.557921100584085</v>
+        <v>1.594118210377723</v>
       </c>
       <c r="F1993" t="n">
         <v>1.059049651561224</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.990204745307477</v>
+        <v>-2.899711970823381</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.591265461411512</v>
+        <v>1.627462571205151</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174975293984576</v>
@@ -47436,10 +47436,10 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.981312283914194</v>
+        <v>-2.890819509430098</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.612376851695617</v>
+        <v>1.648573961489256</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174975293984576</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.149788400884072</v>
+        <v>-3.059295626399976</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.53684145231225</v>
+        <v>1.573038562105888</v>
       </c>
       <c r="F1996" t="n">
         <v>1.147027458267995</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.703532208254632</v>
+        <v>-2.613039433770536</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.696613626551888</v>
+        <v>1.732810736345526</v>
       </c>
       <c r="F1997" t="n">
         <v>1.052308788598362</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.68081110457148</v>
+        <v>-2.590318330087383</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.696366090522053</v>
+        <v>1.732563200315692</v>
       </c>
       <c r="F1998" t="n">
         <v>1.052308788598362</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.810012917865522</v>
+        <v>-2.719520143381426</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.803591491055605</v>
+        <v>1.839788600849244</v>
       </c>
       <c r="F1999" t="n">
         <v>0.92310697530432</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.835887316339548</v>
+        <v>-2.745394541855451</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.830319554159641</v>
+        <v>1.86651666395328</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9680185840160611</v>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.984257052831226</v>
+        <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.828832626124374</v>
+        <v>-2.87978880267344</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.852367578067729</v>
+        <v>1.80943431561563</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9750732742312349</v>
+        <v>0.8336243231980721</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.569301017369968</v>
+        <v>3.461880854917597</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.994263206475968</v>
+        <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.801881401797886</v>
+        <v>-2.852837578346952</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.873154221443065</v>
+        <v>1.830220958990966</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.8485046692257913</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.588235378631341</v>
+        <v>3.48081521617897</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.178366338620928</v>
+        <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.823425629628673</v>
+        <v>-2.874381806177739</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.04863966245571</v>
+        <v>2.005706400003612</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.8485046692257913</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.7723385107763</v>
+        <v>3.66491834832393</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.17048303352392</v>
+        <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.845833747433546</v>
+        <v>-2.896789923982611</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.031793110236754</v>
+        <v>1.988859847784656</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9899536202589541</v>
+        <v>0.8485046692257913</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.764455205679293</v>
+        <v>3.657035043226923</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.172537033073558</v>
+        <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.874057983011146</v>
+        <v>-2.925014159560212</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.022557415555352</v>
+        <v>1.979624153103253</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.007930372710263</v>
+        <v>0.8664814216770999</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.777295256699716</v>
+        <v>3.669875094247346</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.228790750795405</v>
+        <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.883498908899676</v>
+        <v>-2.934455085448742</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.075034762921787</v>
+        <v>2.032101500469688</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.130357490253654</v>
+        <v>0.9889085392204913</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.907005244947598</v>
+        <v>3.799585082495228</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.231681845340706</v>
+        <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.97237554006815</v>
+        <v>-3.023331716617216</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.042375204999698</v>
+        <v>1.999441942547599</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.04148085908518</v>
+        <v>0.9000319080520174</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.856570360791814</v>
+        <v>3.749150198339444</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.229793658234481</v>
+        <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.048705517669056</v>
+        <v>-3.099661694218121</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.009955026853111</v>
+        <v>1.967021764401012</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.04148085908518</v>
+        <v>0.9000319080520174</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.854682173685589</v>
+        <v>3.747262011233219</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.224613887837343</v>
+        <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.203662303069185</v>
+        <v>-3.254618479618251</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.942792542295921</v>
+        <v>1.899859279843823</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.886524073685051</v>
+        <v>0.7450751226518881</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.756528332048374</v>
+        <v>3.649108169596004</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.223047898047496</v>
+        <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.36523072859644</v>
+        <v>-3.416186905145506</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.876599182295172</v>
+        <v>1.833665919843073</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7597411498871717</v>
+        <v>0.6182921988540088</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.678892587979799</v>
+        <v>3.571472425527429</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.236121304913414</v>
+        <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.473531390466559</v>
+        <v>-3.524487567015625</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.846352324413043</v>
+        <v>1.803419061960944</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7597411498871717</v>
+        <v>0.6182921988540088</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.691965994845718</v>
+        <v>3.584545832393347</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.228126501696354</v>
+        <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.491335362187304</v>
+        <v>-3.542291538736369</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.831235932507685</v>
+        <v>1.788302670055586</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6892065269819705</v>
+        <v>0.5477575759488076</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.641650417885537</v>
+        <v>3.534230255433167</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.226650542823356</v>
+        <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.519236149296777</v>
+        <v>-3.570192325845842</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.818599658790898</v>
+        <v>1.775666396338799</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6546096028390357</v>
+        <v>0.5131606518058728</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.619416304526778</v>
+        <v>3.511996142074408</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.223414986800555</v>
+        <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.64176225199967</v>
+        <v>-3.692718428548736</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.766353661686939</v>
+        <v>1.72342039923484</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5320835001361418</v>
+        <v>0.3906345491029789</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.54266508688224</v>
+        <v>3.43524492442987</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.290120946391059</v>
+        <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.872276748185259</v>
+        <v>-3.923232924734325</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.740853822803207</v>
+        <v>1.697920560351108</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3015690039505531</v>
+        <v>0.1601200529173902</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.471062348761391</v>
+        <v>3.363642186309021</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.430432665392906</v>
+        <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.221021833409702</v>
+        <v>-4.271978009958769</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.741667507715277</v>
+        <v>1.698734245263178</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1928210500316553</v>
+        <v>0.05137209899849238</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.546125295411899</v>
+        <v>3.438705132959529</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.499412934538546</v>
+        <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.375008251185843</v>
+        <v>-4.425964427734909</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.749053209750461</v>
+        <v>1.706119947298362</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1928210500316553</v>
+        <v>0.05137209899849238</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.615105564557539</v>
+        <v>3.507685402105169</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.485464136658667</v>
+        <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.579607686048852</v>
+        <v>-4.630563862597918</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.653264637925378</v>
+        <v>1.610331375473279</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1928210500316553</v>
+        <v>0.05137209899849238</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.60115676667766</v>
+        <v>3.49373660422529</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.49733462571408</v>
+        <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.832082840056576</v>
+        <v>-4.883039016605642</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.564145065377702</v>
+        <v>1.521211802925603</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1928210500316553</v>
+        <v>0.05137209899849238</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.613027255733074</v>
+        <v>3.505607093280704</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.498545160233024</v>
+        <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.124978596535988</v>
+        <v>-5.175934773085054</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.448197297304881</v>
+        <v>1.405264034852782</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1928210500316553</v>
+        <v>0.05137209899849238</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.614237790252018</v>
+        <v>3.506817627799648</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.502666902460346</v>
+        <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.311642724670796</v>
+        <v>-5.362598901219862</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.377653388278279</v>
+        <v>1.33472012582618</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1660820792070954</v>
+        <v>0.02463312817393248</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.602316149984603</v>
+        <v>3.494895987532233</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.497744755196535</v>
+        <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.457663411584758</v>
+        <v>-5.508619588133825</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.314322966248884</v>
+        <v>1.271389703796785</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1569989874132384</v>
+        <v>0.01555003638007552</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.591944147644478</v>
+        <v>3.484523985192108</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.659948811895579</v>
+        <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.549377420694343</v>
+        <v>-5.600333597243409</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.439841419304094</v>
+        <v>1.396908156851995</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1569989874132384</v>
+        <v>0.01555003638007552</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.754148204343522</v>
+        <v>3.646728041891152</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.654795449859393</v>
+        <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.581029079754313</v>
+        <v>-5.631985256303379</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.422027393643921</v>
+        <v>1.379094131191822</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1518305301687982</v>
+        <v>0.01038157913563531</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.745893767960673</v>
+        <v>3.638473605508302</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.665024867427884</v>
+        <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.650095134327249</v>
+        <v>-5.701051310876315</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.404630389383237</v>
+        <v>1.361697126931138</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.08945965267518818</v>
+        <v>-0.05198929835797472</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.718700659032998</v>
+        <v>3.611280496580628</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.673950505883787</v>
+        <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.752071256575657</v>
+        <v>-5.803027433124723</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.372765578939776</v>
+        <v>1.329832316487678</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.01251646957321939</v>
+        <v>-0.1539654206063823</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.666440624139855</v>
+        <v>3.559020461687485</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231808</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.666103393127962</v>
+        <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.642064973098435</v>
+        <v>-5.693021149647501</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.40892097957484</v>
+        <v>1.365987717122741</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.01068810234405582</v>
+        <v>-0.1307608486891071</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.672516254534396</v>
+        <v>3.565096092082026</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.670353403849937</v>
+        <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.499005397357509</v>
+        <v>-5.549961573906575</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.470394820593185</v>
+        <v>1.427461558141086</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.01870152893403509</v>
+        <v>-0.1227474220991278</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.681574321210358</v>
+        <v>3.574154158757988</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.677614286732473</v>
+        <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.197558671885671</v>
+        <v>-5.248514848434738</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.598234393664456</v>
+        <v>1.555301131212357</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3201482544058724</v>
+        <v>0.1786993033727095</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.869703239375996</v>
+        <v>3.762283076923626</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.678585464485183</v>
+        <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.222148916120855</v>
+        <v>-5.273105092669922</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.589369473723093</v>
+        <v>1.546436211270994</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3201482544058724</v>
+        <v>0.1786993033727095</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.870674417128707</v>
+        <v>3.763254254676337</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.679428368864939</v>
+        <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.171110540114335</v>
+        <v>-5.222066716663401</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.610627728505457</v>
+        <v>1.567694466053358</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3201482544058724</v>
+        <v>0.1786993033727095</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.871517321508462</v>
+        <v>3.764097159056092</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.698466467739084</v>
+        <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.142261863290875</v>
+        <v>-5.193218039839941</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.641205298108986</v>
+        <v>1.598272035656887</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3489969312293326</v>
+        <v>0.2075479801961697</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.907864626476684</v>
+        <v>3.800444464024314</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.514650463863019</v>
+        <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.045626951272235</v>
+        <v>-5.096583127821301</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.496043259040377</v>
+        <v>1.453109996588278</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4456318432479726</v>
+        <v>0.3041828922148097</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.782029569811803</v>
+        <v>3.674609407359433</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.518152507936983</v>
+        <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.976588940323767</v>
+        <v>-5.027545116872833</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.527160507493728</v>
+        <v>1.484227245041629</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5146698541964406</v>
+        <v>0.3732209031632777</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.826954420454848</v>
+        <v>3.719534258002478</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.502579327013065</v>
+        <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.812092606132805</v>
+        <v>-4.863048782681871</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.577385860246195</v>
+        <v>1.534452597794097</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6791661883874025</v>
+        <v>0.5377172373542396</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.910079040045507</v>
+        <v>3.802658877593137</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.501767037449495</v>
+        <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.734994004590932</v>
+        <v>-4.785950181139999</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.607413011299374</v>
+        <v>1.564479748847275</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6791661883874025</v>
+        <v>0.5377172373542396</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.909266750481937</v>
+        <v>3.801846588029567</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.511635816574568</v>
+        <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.745379199480822</v>
+        <v>-4.796335376029888</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.613127712468491</v>
+        <v>1.570194450016392</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6687809934975132</v>
+        <v>0.5273320424643503</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.912904412673075</v>
+        <v>3.805484250220706</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735279</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.582472822350993</v>
+        <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.763967358203047</v>
+        <v>-4.814923534752113</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.676529454756026</v>
+        <v>1.633596192303927</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6501928347752879</v>
+        <v>0.508743883742125</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.972588523216166</v>
+        <v>3.865168360763795</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.579341833169291</v>
+        <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.764265904899083</v>
+        <v>-4.815222081448149</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.67327904689591</v>
+        <v>1.630345784443811</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.649894288079252</v>
+        <v>0.5084453370460891</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.969278406016842</v>
+        <v>3.861858243564472</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.583872728108683</v>
+        <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.663442771208655</v>
+        <v>-4.714398947757721</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.718139195311473</v>
+        <v>1.675205932859374</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6623585035636058</v>
+        <v>0.5209095525304429</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.981287830246846</v>
+        <v>3.873867667794476</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.584001981587226</v>
+        <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.472661410456247</v>
+        <v>-4.523617587005313</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.794580993090979</v>
+        <v>1.75164773063888</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8531398643160132</v>
+        <v>0.7116909132828503</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.095885900176834</v>
+        <v>3.988465737724464</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.563838827324822</v>
+        <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.365698052606826</v>
+        <v>-4.416654229155892</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.817203181968344</v>
+        <v>1.774269919516245</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9116044722758146</v>
+        <v>0.7701555212426517</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.110801510690312</v>
+        <v>4.003381348237942</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.598805763936881</v>
+        <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.310367464705063</v>
+        <v>-4.361323641254129</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.874302353741108</v>
+        <v>1.831369091289009</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9669350601775768</v>
+        <v>0.8254861091444139</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.178966800043427</v>
+        <v>4.071546637591057</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.592492331838319</v>
+        <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.2983133377921</v>
+        <v>-4.349269514341167</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.87281057240773</v>
+        <v>1.829877309955632</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9789891870905396</v>
+        <v>0.8375402360573767</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.179885844092643</v>
+        <v>4.072465681640272</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.594372962022454</v>
+        <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.339468457360321</v>
+        <v>-4.390424633909388</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.858229154764578</v>
+        <v>1.815295892312479</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9378340675223187</v>
+        <v>0.7963851164891558</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.157073402535846</v>
+        <v>4.049653240083476</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.607223987900337</v>
+        <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.271419894668791</v>
+        <v>-4.322376071217858</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.898299605719072</v>
+        <v>1.855366343266974</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.005882630213848</v>
+        <v>0.8644336791806856</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.210753566028647</v>
+        <v>4.103333403576277</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013425</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.627426658073931</v>
+        <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.503020287838292</v>
+        <v>-4.553976464387358</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.825862118624866</v>
+        <v>1.782928856172767</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.005882630213848</v>
+        <v>0.8644336791806856</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.230956236202241</v>
+        <v>4.123536073749871</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.611032894140813</v>
+        <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.553071833367511</v>
+        <v>-4.604028009916577</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.789447736480061</v>
+        <v>1.746514474027962</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.005882630213848</v>
+        <v>0.8644336791806856</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.214562472269122</v>
+        <v>4.107142309816752</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.57128480773428</v>
+        <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.728178665943956</v>
+        <v>-4.779134842493022</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.67965691704295</v>
+        <v>1.636723654590851</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.005882630213848</v>
+        <v>0.8644336791806856</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.174814385862589</v>
+        <v>4.067394223410219</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.57830742673122</v>
+        <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.532078512513433</v>
+        <v>-4.583034689062499</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.765119597412099</v>
+        <v>1.72218633496</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.201982783644371</v>
+        <v>1.060533832611208</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.299497096917843</v>
+        <v>4.192076934465473</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.677478426304124</v>
+        <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.379053120400148</v>
+        <v>-4.430009296949215</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.925500753830317</v>
+        <v>1.882567491378218</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.355008175757655</v>
+        <v>1.213559224724492</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.490483331758718</v>
+        <v>4.383063169306348</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.864944651212417</v>
+        <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.407360434273419</v>
+        <v>-4.458316610822485</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.101644053189301</v>
+        <v>2.058710790737202</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.355008175757655</v>
+        <v>1.213559224724492</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.67794955666701</v>
+        <v>4.57052939421464</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.8343476025665</v>
+        <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.573953659386941</v>
+        <v>-4.624909835936007</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.004409714497975</v>
+        <v>1.961476452045877</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.188414950644133</v>
+        <v>1.04696599961097</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.547396572952979</v>
+        <v>4.439976410500609</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.838024005228217</v>
+        <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.550917866025375</v>
+        <v>-4.601874042574441</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.017300434504319</v>
+        <v>1.97436717205222</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.188414950644133</v>
+        <v>1.04696599961097</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.551072975614697</v>
+        <v>4.443652813162327</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.835642060351713</v>
+        <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.521671885569678</v>
+        <v>-4.572628062118745</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.026616881810093</v>
+        <v>1.983683619357994</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.188414950644133</v>
+        <v>1.04696599961097</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.548691030738192</v>
+        <v>4.441270868285822</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.832935299509348</v>
+        <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.628597433447529</v>
+        <v>-4.679553609996596</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.981139901816588</v>
+        <v>1.938206639364489</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.081489402766282</v>
+        <v>0.9400404517331186</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.481828941169117</v>
+        <v>4.374408778716747</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.834364101652582</v>
+        <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.773615991954778</v>
+        <v>-4.824572168503845</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.924561280556922</v>
+        <v>1.881628018104824</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.936470844259033</v>
+        <v>0.79502189322587</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.396246608208002</v>
+        <v>4.288826445755632</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.934295340910334</v>
+        <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.891957757739496</v>
+        <v>-4.942913934288562</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.977155813500788</v>
+        <v>1.934222551048689</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9471568828219231</v>
+        <v>0.8057079317887601</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.502589470603488</v>
+        <v>4.395169308151119</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.932081038036273</v>
+        <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.943368180060204</v>
+        <v>-4.99432435660927</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.954377341698444</v>
+        <v>1.911444079246346</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9471568828219231</v>
+        <v>0.8057079317887601</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.500375167729427</v>
+        <v>4.392955005277058</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.931984166110563</v>
+        <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.022787631267955</v>
+        <v>-5.073743807817022</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.922512689289632</v>
+        <v>1.879579426837534</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9471568828219231</v>
+        <v>0.8057079317887601</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.500278295803716</v>
+        <v>4.392858133351347</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298399</v>
+        <v>3.736804952298397</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.931978059668606</v>
+        <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.118250629185173</v>
+        <v>-5.169206805734239</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.884321383680789</v>
+        <v>1.84138812122869</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9471568828219231</v>
+        <v>0.8057079317887601</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.50027218936176</v>
+        <v>4.39285202690939</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218001</v>
+        <v>3.715372960217999</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.930074456231217</v>
+        <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.053874718334458</v>
+        <v>-5.104830894883524</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.908168144583685</v>
+        <v>1.865234882131587</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.011532793672638</v>
+        <v>0.8700838426394752</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.5369941324348</v>
+        <v>4.42957396998243</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353536</v>
+        <v>3.736089413353534</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.935808273978943</v>
+        <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.109243880466652</v>
+        <v>-5.160200057015718</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.891754297478534</v>
+        <v>1.848821035026436</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.011532793672638</v>
+        <v>0.8700838426394752</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.542727950182527</v>
+        <v>4.435307787730157</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113279</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.935346637321876</v>
+        <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.12746234746426</v>
+        <v>-5.178418524013327</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.884005274022424</v>
+        <v>1.841072011570325</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.986426356416796</v>
+        <v>0.8449774053836331</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.527202451171954</v>
+        <v>4.419782288719583</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113688</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.955221030172195</v>
+        <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.039255513316682</v>
+        <v>-5.090211689865749</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.939162400531774</v>
+        <v>1.896229138079675</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.986426356416796</v>
+        <v>0.8449774053836331</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.547076844022273</v>
+        <v>4.439656681569902</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.938921730696923</v>
+        <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.933220518111373</v>
+        <v>-4.984176694660439</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.965277099138626</v>
+        <v>1.922343836686526</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.986426356416796</v>
+        <v>0.8449774053836331</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.530777544547001</v>
+        <v>4.42335738209463</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.941352680160969</v>
+        <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.750008854978278</v>
+        <v>-4.800965031527344</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.04099271385591</v>
+        <v>1.99805945140381</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.986426356416796</v>
+        <v>0.8449774053836331</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.533208494011046</v>
+        <v>4.425788331558675</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.924297086240346</v>
+        <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.678287407964427</v>
+        <v>-4.729243584513493</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.052625698740827</v>
+        <v>2.009692436288727</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.058147803430647</v>
+        <v>0.9166988523974837</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.559185768298734</v>
+        <v>4.451765605846363</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.871212832161517</v>
+        <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.655914382356721</v>
+        <v>-4.706870558905787</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.008490654905081</v>
+        <v>1.965557392452982</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.069403554543548</v>
+        <v>0.9279546035103853</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.512854964887646</v>
+        <v>4.405434802435275</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.71560744645673</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.056411037046873</v>
+        <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.688930678267465</v>
+        <v>-4.739886854816532</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.180482341426139</v>
+        <v>2.137549078974039</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9999661778767968</v>
+        <v>0.8585172268436336</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.656390743772951</v>
+        <v>4.54897058132058</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883678</v>
+        <v>3.713762536883676</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.048332262875122</v>
+        <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.819960106118248</v>
+        <v>-4.728359219166923</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.119991796114075</v>
+        <v>2.134081359062131</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.923955850806472</v>
+        <v>0.9175178850449961</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.602705773359006</v>
+        <v>4.576292202069647</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236298</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.05200037539691</v>
+        <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.917301607460617</v>
+        <v>-4.825700720509292</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.084723308098916</v>
+        <v>2.098812871046973</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.8795356686409836</v>
+        <v>0.8730977028795077</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.579721776581501</v>
+        <v>4.553308205292142</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427685</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.053251457589749</v>
+        <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.003157636800584</v>
+        <v>-4.911556749849258</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.051631978555768</v>
+        <v>2.065721541503824</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.8371595994148486</v>
+        <v>0.8307216336533727</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.555547217238658</v>
+        <v>4.529133645949299</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.03567065941025</v>
+        <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.011994434216703</v>
+        <v>-4.920393547265378</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.030516461409821</v>
+        <v>2.044606024357878</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.8297174267734979</v>
+        <v>0.823279461012022</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.533501115474349</v>
+        <v>4.507087544184991</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667455</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.0458351704553</v>
+        <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.103376996782162</v>
+        <v>-5.011776109830836</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.004127947428687</v>
+        <v>2.018217510376744</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.7931525420541532</v>
+        <v>0.7867145762926773</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.521726695687792</v>
+        <v>4.495313124398433</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889192</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.147963428279567</v>
+        <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.091670278795156</v>
+        <v>-5.00006939184383</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.110938892447757</v>
+        <v>2.125028455395815</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.8048592600411596</v>
+        <v>0.7984212942796837</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.630878984304263</v>
+        <v>4.604465413014905</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409568</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.150995767010972</v>
+        <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.162582352537433</v>
+        <v>-5.070981465586108</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.085606401682251</v>
+        <v>2.099695964630309</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.8048592600411596</v>
+        <v>0.7984212942796837</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.633911323035668</v>
+        <v>4.60749775174631</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452572</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.36390060028903</v>
+        <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.172898450703785</v>
+        <v>-5.08129756375246</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.294384795693768</v>
+        <v>2.308474358641826</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.8048592600411596</v>
+        <v>0.7984212942796837</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.846816156313726</v>
+        <v>4.820402585024368</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762288</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.36307926720112</v>
+        <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.172804482686412</v>
+        <v>-5.081203595735087</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.293601049812807</v>
+        <v>2.307690612760865</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.8052291213884776</v>
+        <v>0.7987911556270016</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.846216740034206</v>
+        <v>4.819803168744849</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988019</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.357311253145474</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.321170710342557</v>
+        <v>-5.229569823391232</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.228486544694703</v>
+        <v>2.242576107642761</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.8052291213884776</v>
+        <v>0.7987911556270016</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.84044872597856</v>
+        <v>4.814035154689202</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.357311253145474</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.320222287224518</v>
+        <v>-5.228621400273194</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.228865913941918</v>
+        <v>2.242955476889976</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.8052291213884776</v>
+        <v>0.7987911556270016</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.84044872597856</v>
+        <v>4.814035154689202</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.370038861126566</v>
+        <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.42049210518354</v>
+        <v>-5.328891218232215</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.201485594739402</v>
+        <v>2.215575157687459</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.8052291213884776</v>
+        <v>0.7987911556270016</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.853176333959652</v>
+        <v>4.826762762670294</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.371984859550953</v>
+        <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.414499858394728</v>
+        <v>-5.322898971443403</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.205828491879314</v>
+        <v>2.219918054827372</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.8052291213884776</v>
+        <v>0.7987911556270016</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.85512233238404</v>
+        <v>4.828708761094682</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.365638995568722</v>
+        <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.32594189726396</v>
+        <v>-5.234341010312636</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.23490581234939</v>
+        <v>2.248995375297448</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.8052291213884776</v>
+        <v>0.7987911556270016</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.848776468401809</v>
+        <v>4.822362897112451</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.73530072138309</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.364947673007718</v>
+        <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.308182819760886</v>
+        <v>-5.216581932809562</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.241318120789615</v>
+        <v>2.255407683737673</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.8052291213884776</v>
+        <v>0.7987911556270016</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.848085145840805</v>
+        <v>4.821671574551447</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.377729858916305</v>
+        <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.208552668711818</v>
+        <v>-5.116951781760494</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.293952367117829</v>
+        <v>2.308041930065887</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.904859272437545</v>
+        <v>0.8984213066760691</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.920645422378832</v>
+        <v>4.894231851089474</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.77535709745527</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.566884124415031</v>
+        <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.25795217740083</v>
+        <v>-5.166351290449505</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.463346829140951</v>
+        <v>2.477436392089009</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.9151181058692898</v>
+        <v>0.9086801401078138</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.115954987936605</v>
+        <v>5.089541416647247</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963131</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.554072797517893</v>
+        <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.051267703758453</v>
+        <v>-4.959666816807129</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.533209291700764</v>
+        <v>2.547298854648822</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.121802579511666</v>
+        <v>1.115364613750189</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.227154345224893</v>
+        <v>5.200740773935535</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162541</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.556074311171998</v>
+        <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.08542459875598</v>
+        <v>-4.993823711804655</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.521548047355858</v>
+        <v>2.535637610303916</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.038218809970853</v>
+        <v>1.031780844209377</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.17900559715451</v>
+        <v>5.152592025865152</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.909571425161666</v>
+        <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.992835119694523</v>
+        <v>-4.901234232743199</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.912080952970109</v>
+        <v>2.926170515918166</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.038218809970853</v>
+        <v>1.031780844209377</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.532502711144177</v>
+        <v>5.50608913985482</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.914134536728769</v>
+        <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.052723747518074</v>
+        <v>-4.961122860566749</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.892688613407791</v>
+        <v>2.906778176355849</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.024096895283388</v>
+        <v>1.017658929521912</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.528592673898802</v>
+        <v>5.502179102609444</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103563</v>
+        <v>3.835202441103562</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.963964478052296</v>
+        <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.000507437721732</v>
+        <v>-4.908906550770407</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.963405078649855</v>
+        <v>2.977494641597913</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.024096895283388</v>
+        <v>1.017658929521912</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.57842261522233</v>
+        <v>5.552009043932972</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047745</v>
+        <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.972778448262307</v>
+        <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.968609920636486</v>
+        <v>-4.877009033685161</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.984978055693965</v>
+        <v>2.999067618642022</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.055994412368634</v>
+        <v>1.049556446607158</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.606375095683488</v>
+        <v>5.57996152439413</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650754</v>
+        <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.968416032301504</v>
+        <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.983365244836627</v>
+        <v>-4.891764357885302</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.974713510053105</v>
+        <v>2.988803073001163</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.055994412368634</v>
+        <v>1.049556446607158</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.602012679722685</v>
+        <v>5.575599108433327</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135749</v>
+        <v>3.845044666135747</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.959340535717784</v>
+        <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.933900621466715</v>
+        <v>-4.84229973451539</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.98542386281735</v>
+        <v>2.999513425765407</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.105459035738546</v>
+        <v>1.09902106997707</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.622615957160912</v>
+        <v>5.596202385871553</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479222</v>
+        <v>3.82593179047922</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.955748203432718</v>
+        <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.7707926293131</v>
+        <v>-4.679191742361775</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.04707472739373</v>
+        <v>3.061164290341788</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.268567027892161</v>
+        <v>1.262129062130685</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.716888420168015</v>
+        <v>5.690474848878657</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844244</v>
+        <v>3.847096478844245</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.964795240123847</v>
+        <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.637985003815933</v>
+        <v>-4.546384116864608</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.109244814283725</v>
+        <v>3.123334377231783</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.268567027892161</v>
+        <v>1.262129062130685</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.725935456859143</v>
+        <v>5.699521885569785</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790947</v>
+        <v>3.832425987790948</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.965652705109968</v>
+        <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.700692920290491</v>
+        <v>-4.609092033339167</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.085019112680023</v>
+        <v>3.099108675628081</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.205859111417603</v>
+        <v>1.199421145656127</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.689168171960531</v>
+        <v>5.662754600671173</v>
       </c>
     </row>
     <row r="2099">
@@ -49825,19 +49825,19 @@
         <v>3.861579399578995</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.92856212190032</v>
+        <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.652684796446798</v>
+        <v>-4.561083909495474</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.067131779007853</v>
+        <v>3.081221341955911</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.205859111417603</v>
+        <v>1.199421145656127</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.652077588750883</v>
+        <v>5.625664017461524</v>
       </c>
     </row>
     <row r="2100">
@@ -49848,19 +49848,19 @@
         <v>3.872253907629883</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.932494375458271</v>
+        <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.573859139263208</v>
+        <v>-4.482258252311883</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.10259429543924</v>
+        <v>3.116683858387297</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.284684768601194</v>
+        <v>1.278246802839718</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.703305236618988</v>
+        <v>5.676891665329629</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686406</v>
+        <v>3.868502531686405</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.927393468065308</v>
+        <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.381924338009334</v>
+        <v>-4.290323451058009</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.174267308547826</v>
+        <v>3.188356871495884</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.284684768601194</v>
+        <v>1.278246802839718</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.698204329226025</v>
+        <v>5.671790757936666</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.891267537058207</v>
+        <v>3.768041746584683</v>
       </c>
       <c r="C2102" t="n">
-        <v>4.868154895504267</v>
+        <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.267888936510598</v>
+        <v>-4.149088862576128</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.16064289658628</v>
+        <v>3.240204616277731</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.272785590660677</v>
+        <v>1.328319008968663</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.631826249900674</v>
+        <v>5.697187991003129</v>
       </c>
     </row>
   </sheetData>
